--- a/공급량실적_계획_실적_MJ.xlsx
+++ b/공급량실적_계획_실적_MJ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\실천사업계획\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9A2085C2-B362-44B3-967D-4383E8D8DBD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57AC8545-600E-4640-9A0E-934C3A2A20C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1965,7 +1965,7 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2C1F99CF-9391-4872-B93D-50B931598DD3}" name="표1_3" displayName="표1_3" ref="A1:AF37" totalsRowShown="0" headerRowDxfId="94" dataDxfId="93">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2C1F99CF-9391-4872-B93D-50B931598DD3}" name="표1_3" displayName="표1_3" ref="A1:AF13" totalsRowShown="0" headerRowDxfId="94" dataDxfId="93">
   <tableColumns count="32">
     <tableColumn id="1" xr3:uid="{19685FD4-89CE-478F-94BA-7A4B1E721FD4}" name="날짜" dataDxfId="92"/>
     <tableColumn id="2" xr3:uid="{E31CA521-8EDF-4B60-95F2-6D99A2A44422}" name="연" dataDxfId="91"/>
@@ -11185,7 +11185,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{029D494F-C948-427C-AD81-22450CB874BD}">
-  <dimension ref="A1:AJ39"/>
+  <dimension ref="A1:AJ13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.75" style="3" bestFit="1" customWidth="1"/>
@@ -12179,1739 +12179,6 @@
       <c r="AD13" s="14"/>
       <c r="AE13" s="14"/>
       <c r="AF13" s="14"/>
-    </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A14" s="10">
-        <v>46388</v>
-      </c>
-      <c r="B14" s="11">
-        <v>2027</v>
-      </c>
-      <c r="C14" s="11">
-        <v>1</v>
-      </c>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11">
-        <v>23295000</v>
-      </c>
-      <c r="F14" s="11">
-        <v>5351768000</v>
-      </c>
-      <c r="G14" s="11">
-        <v>94674000</v>
-      </c>
-      <c r="H14" s="11">
-        <v>74926000</v>
-      </c>
-      <c r="I14" s="11">
-        <v>157305833</v>
-      </c>
-      <c r="J14" s="11">
-        <v>75955149</v>
-      </c>
-      <c r="K14" s="11">
-        <v>160577000</v>
-      </c>
-      <c r="L14" s="11">
-        <v>142632000</v>
-      </c>
-      <c r="M14" s="11">
-        <v>171750000</v>
-      </c>
-      <c r="N14" s="11">
-        <v>919718000</v>
-      </c>
-      <c r="O14" s="11">
-        <v>226448000</v>
-      </c>
-      <c r="P14" s="11">
-        <v>10493000</v>
-      </c>
-      <c r="Q14" s="11">
-        <v>24860000</v>
-      </c>
-      <c r="R14" s="11">
-        <v>32670000</v>
-      </c>
-      <c r="S14" s="11">
-        <v>759000</v>
-      </c>
-      <c r="T14" s="11">
-        <v>12248000</v>
-      </c>
-      <c r="U14" s="11"/>
-      <c r="V14" s="11"/>
-      <c r="W14" s="11"/>
-      <c r="X14" s="11"/>
-      <c r="Y14" s="13"/>
-      <c r="Z14" s="14"/>
-      <c r="AA14" s="14"/>
-      <c r="AB14" s="14"/>
-      <c r="AC14" s="14"/>
-      <c r="AD14" s="14"/>
-      <c r="AE14" s="14"/>
-      <c r="AF14" s="14"/>
-    </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A15" s="10">
-        <v>46419</v>
-      </c>
-      <c r="B15" s="11">
-        <v>2027</v>
-      </c>
-      <c r="C15" s="11">
-        <v>2</v>
-      </c>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11">
-        <v>20417000</v>
-      </c>
-      <c r="F15" s="11">
-        <v>4101574000</v>
-      </c>
-      <c r="G15" s="11">
-        <v>84991000</v>
-      </c>
-      <c r="H15" s="11">
-        <v>64361000</v>
-      </c>
-      <c r="I15" s="11">
-        <v>147183340</v>
-      </c>
-      <c r="J15" s="11">
-        <v>71183283</v>
-      </c>
-      <c r="K15" s="11">
-        <v>144981000</v>
-      </c>
-      <c r="L15" s="11">
-        <v>122893000</v>
-      </c>
-      <c r="M15" s="11">
-        <v>146396000</v>
-      </c>
-      <c r="N15" s="11">
-        <v>757926000</v>
-      </c>
-      <c r="O15" s="11">
-        <v>219256000</v>
-      </c>
-      <c r="P15" s="11">
-        <v>9205000</v>
-      </c>
-      <c r="Q15" s="11">
-        <v>22201000</v>
-      </c>
-      <c r="R15" s="11">
-        <v>44305000</v>
-      </c>
-      <c r="S15" s="11">
-        <v>732000</v>
-      </c>
-      <c r="T15" s="11">
-        <v>9896000</v>
-      </c>
-      <c r="U15" s="11"/>
-      <c r="V15" s="11"/>
-      <c r="W15" s="11"/>
-      <c r="X15" s="11"/>
-      <c r="Y15" s="13"/>
-      <c r="Z15" s="14"/>
-      <c r="AA15" s="14"/>
-      <c r="AB15" s="14"/>
-      <c r="AC15" s="14"/>
-      <c r="AD15" s="14"/>
-      <c r="AE15" s="14"/>
-      <c r="AF15" s="14"/>
-    </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
-      <c r="A16" s="10">
-        <v>46447</v>
-      </c>
-      <c r="B16" s="11">
-        <v>2027</v>
-      </c>
-      <c r="C16" s="11">
-        <v>3</v>
-      </c>
-      <c r="D16" s="11"/>
-      <c r="E16" s="11">
-        <v>22677000</v>
-      </c>
-      <c r="F16" s="11">
-        <v>2743951000</v>
-      </c>
-      <c r="G16" s="11">
-        <v>59299000</v>
-      </c>
-      <c r="H16" s="11">
-        <v>36480000</v>
-      </c>
-      <c r="I16" s="11">
-        <v>149327819</v>
-      </c>
-      <c r="J16" s="11">
-        <v>89571638</v>
-      </c>
-      <c r="K16" s="11">
-        <v>120771000</v>
-      </c>
-      <c r="L16" s="11">
-        <v>89984000</v>
-      </c>
-      <c r="M16" s="11">
-        <v>89040000</v>
-      </c>
-      <c r="N16" s="11">
-        <v>871416000</v>
-      </c>
-      <c r="O16" s="11">
-        <v>233165000</v>
-      </c>
-      <c r="P16" s="11">
-        <v>10959000</v>
-      </c>
-      <c r="Q16" s="11">
-        <v>23518000</v>
-      </c>
-      <c r="R16" s="11">
-        <v>99974000</v>
-      </c>
-      <c r="S16" s="11">
-        <v>605000</v>
-      </c>
-      <c r="T16" s="11">
-        <v>6858000</v>
-      </c>
-      <c r="U16" s="11"/>
-      <c r="V16" s="11"/>
-      <c r="W16" s="11"/>
-      <c r="X16" s="11"/>
-      <c r="Y16" s="13"/>
-      <c r="Z16" s="14"/>
-      <c r="AA16" s="14"/>
-      <c r="AB16" s="14"/>
-      <c r="AC16" s="14"/>
-      <c r="AD16" s="14"/>
-      <c r="AE16" s="14"/>
-      <c r="AF16" s="14"/>
-    </row>
-    <row r="17" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A17" s="10">
-        <v>46478</v>
-      </c>
-      <c r="B17" s="11">
-        <v>2027</v>
-      </c>
-      <c r="C17" s="11">
-        <v>4</v>
-      </c>
-      <c r="D17" s="11"/>
-      <c r="E17" s="11">
-        <v>16873000</v>
-      </c>
-      <c r="F17" s="11">
-        <v>1526444000</v>
-      </c>
-      <c r="G17" s="11">
-        <v>38919000</v>
-      </c>
-      <c r="H17" s="11">
-        <v>17902000</v>
-      </c>
-      <c r="I17" s="11">
-        <v>137287964</v>
-      </c>
-      <c r="J17" s="11">
-        <v>76218587</v>
-      </c>
-      <c r="K17" s="11">
-        <v>82563000</v>
-      </c>
-      <c r="L17" s="11">
-        <v>43041000</v>
-      </c>
-      <c r="M17" s="11">
-        <v>36430000</v>
-      </c>
-      <c r="N17" s="11">
-        <v>758327000</v>
-      </c>
-      <c r="O17" s="11">
-        <v>232474000</v>
-      </c>
-      <c r="P17" s="11">
-        <v>10937000</v>
-      </c>
-      <c r="Q17" s="11">
-        <v>18794000</v>
-      </c>
-      <c r="R17" s="11">
-        <v>97119000</v>
-      </c>
-      <c r="S17" s="11">
-        <v>563000</v>
-      </c>
-      <c r="T17" s="11">
-        <v>2523000</v>
-      </c>
-      <c r="U17" s="11"/>
-      <c r="V17" s="11"/>
-      <c r="W17" s="11"/>
-      <c r="X17" s="11"/>
-      <c r="Y17" s="13"/>
-      <c r="Z17" s="14"/>
-      <c r="AA17" s="14"/>
-      <c r="AB17" s="14"/>
-      <c r="AC17" s="14"/>
-      <c r="AD17" s="14"/>
-      <c r="AE17" s="14"/>
-      <c r="AF17" s="14"/>
-    </row>
-    <row r="18" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A18" s="10">
-        <v>46508</v>
-      </c>
-      <c r="B18" s="11">
-        <v>2027</v>
-      </c>
-      <c r="C18" s="11">
-        <v>5</v>
-      </c>
-      <c r="D18" s="11"/>
-      <c r="E18" s="11">
-        <v>18227000</v>
-      </c>
-      <c r="F18" s="11">
-        <v>965758000</v>
-      </c>
-      <c r="G18" s="11">
-        <v>23860000</v>
-      </c>
-      <c r="H18" s="11">
-        <v>8317000</v>
-      </c>
-      <c r="I18" s="11">
-        <v>136462098</v>
-      </c>
-      <c r="J18" s="11">
-        <v>74392832</v>
-      </c>
-      <c r="K18" s="11">
-        <v>67603000</v>
-      </c>
-      <c r="L18" s="11">
-        <v>27660000</v>
-      </c>
-      <c r="M18" s="11">
-        <v>62519000</v>
-      </c>
-      <c r="N18" s="11">
-        <v>670249000</v>
-      </c>
-      <c r="O18" s="11">
-        <v>242199000</v>
-      </c>
-      <c r="P18" s="11">
-        <v>11051000</v>
-      </c>
-      <c r="Q18" s="11">
-        <v>16157000</v>
-      </c>
-      <c r="R18" s="11">
-        <v>185537000</v>
-      </c>
-      <c r="S18" s="11">
-        <v>349000</v>
-      </c>
-      <c r="T18" s="11">
-        <v>2184000</v>
-      </c>
-      <c r="U18" s="11"/>
-      <c r="V18" s="11"/>
-      <c r="W18" s="11"/>
-      <c r="X18" s="11"/>
-      <c r="Y18" s="13"/>
-      <c r="Z18" s="14"/>
-      <c r="AA18" s="14"/>
-      <c r="AB18" s="14"/>
-      <c r="AC18" s="14"/>
-      <c r="AD18" s="14"/>
-      <c r="AE18" s="14"/>
-      <c r="AF18" s="14"/>
-    </row>
-    <row r="19" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A19" s="10">
-        <v>46539</v>
-      </c>
-      <c r="B19" s="11">
-        <v>2027</v>
-      </c>
-      <c r="C19" s="11">
-        <v>6</v>
-      </c>
-      <c r="D19" s="11"/>
-      <c r="E19" s="11">
-        <v>17357000</v>
-      </c>
-      <c r="F19" s="11">
-        <v>458474000</v>
-      </c>
-      <c r="G19" s="11">
-        <v>10030000</v>
-      </c>
-      <c r="H19" s="11">
-        <v>3416000</v>
-      </c>
-      <c r="I19" s="11">
-        <v>125733511</v>
-      </c>
-      <c r="J19" s="11">
-        <v>67872757</v>
-      </c>
-      <c r="K19" s="11">
-        <v>54578000</v>
-      </c>
-      <c r="L19" s="11">
-        <v>20441000</v>
-      </c>
-      <c r="M19" s="11">
-        <v>135692000</v>
-      </c>
-      <c r="N19" s="11">
-        <v>797330000</v>
-      </c>
-      <c r="O19" s="11">
-        <v>238252000</v>
-      </c>
-      <c r="P19" s="11">
-        <v>11296000</v>
-      </c>
-      <c r="Q19" s="11">
-        <v>12059000</v>
-      </c>
-      <c r="R19" s="11">
-        <v>181687000</v>
-      </c>
-      <c r="S19" s="11">
-        <v>343000</v>
-      </c>
-      <c r="T19" s="11">
-        <v>1831000</v>
-      </c>
-      <c r="U19" s="11"/>
-      <c r="V19" s="11"/>
-      <c r="W19" s="11"/>
-      <c r="X19" s="11"/>
-      <c r="Y19" s="13"/>
-      <c r="Z19" s="14"/>
-      <c r="AA19" s="14"/>
-      <c r="AB19" s="14"/>
-      <c r="AC19" s="14"/>
-      <c r="AD19" s="14"/>
-      <c r="AE19" s="14"/>
-      <c r="AF19" s="14"/>
-    </row>
-    <row r="20" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A20" s="10">
-        <v>46569</v>
-      </c>
-      <c r="B20" s="11">
-        <v>2027</v>
-      </c>
-      <c r="C20" s="11">
-        <v>7</v>
-      </c>
-      <c r="D20" s="11"/>
-      <c r="E20" s="11">
-        <v>18709000</v>
-      </c>
-      <c r="F20" s="11">
-        <v>460758000</v>
-      </c>
-      <c r="G20" s="11">
-        <v>11013000</v>
-      </c>
-      <c r="H20" s="11">
-        <v>3229000</v>
-      </c>
-      <c r="I20" s="11">
-        <v>127967857</v>
-      </c>
-      <c r="J20" s="11">
-        <v>57982611</v>
-      </c>
-      <c r="K20" s="11">
-        <v>48429000</v>
-      </c>
-      <c r="L20" s="11">
-        <v>18549000</v>
-      </c>
-      <c r="M20" s="11">
-        <v>199623000</v>
-      </c>
-      <c r="N20" s="11">
-        <v>654360000</v>
-      </c>
-      <c r="O20" s="11">
-        <v>258191000</v>
-      </c>
-      <c r="P20" s="11">
-        <v>10744000</v>
-      </c>
-      <c r="Q20" s="11">
-        <v>19256000</v>
-      </c>
-      <c r="R20" s="11">
-        <v>189621000</v>
-      </c>
-      <c r="S20" s="11">
-        <v>652000</v>
-      </c>
-      <c r="T20" s="11">
-        <v>1621000</v>
-      </c>
-      <c r="U20" s="11"/>
-      <c r="V20" s="11"/>
-      <c r="W20" s="11"/>
-      <c r="X20" s="11"/>
-      <c r="Y20" s="13"/>
-      <c r="Z20" s="14"/>
-      <c r="AA20" s="14"/>
-      <c r="AB20" s="14"/>
-      <c r="AC20" s="14"/>
-      <c r="AD20" s="14"/>
-      <c r="AE20" s="14"/>
-      <c r="AF20" s="14"/>
-    </row>
-    <row r="21" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A21" s="2">
-        <v>46600</v>
-      </c>
-      <c r="B21" s="11">
-        <v>2027</v>
-      </c>
-      <c r="C21" s="11">
-        <v>8</v>
-      </c>
-      <c r="D21" s="11"/>
-      <c r="E21" s="11">
-        <v>18552000</v>
-      </c>
-      <c r="F21" s="11">
-        <v>504930000</v>
-      </c>
-      <c r="G21" s="11">
-        <v>12440000</v>
-      </c>
-      <c r="H21" s="11">
-        <v>3487000</v>
-      </c>
-      <c r="I21" s="11">
-        <v>124646023</v>
-      </c>
-      <c r="J21" s="11">
-        <v>52832229</v>
-      </c>
-      <c r="K21" s="11">
-        <v>45263000</v>
-      </c>
-      <c r="L21" s="11">
-        <v>17057000</v>
-      </c>
-      <c r="M21" s="11">
-        <v>200771000</v>
-      </c>
-      <c r="N21" s="11">
-        <v>676258000</v>
-      </c>
-      <c r="O21" s="11">
-        <v>259881000</v>
-      </c>
-      <c r="P21" s="11">
-        <v>11273000</v>
-      </c>
-      <c r="Q21" s="11">
-        <v>17641000</v>
-      </c>
-      <c r="R21" s="11">
-        <v>191498000</v>
-      </c>
-      <c r="S21" s="11">
-        <v>633000</v>
-      </c>
-      <c r="T21" s="11">
-        <v>1473000</v>
-      </c>
-      <c r="U21" s="11"/>
-      <c r="V21" s="11"/>
-      <c r="W21" s="11"/>
-      <c r="X21" s="11"/>
-      <c r="Y21" s="13"/>
-      <c r="Z21" s="14"/>
-      <c r="AA21" s="14"/>
-      <c r="AB21" s="14"/>
-      <c r="AC21" s="14"/>
-      <c r="AD21" s="14"/>
-      <c r="AE21" s="14"/>
-      <c r="AF21" s="14"/>
-    </row>
-    <row r="22" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A22" s="10">
-        <v>46631</v>
-      </c>
-      <c r="B22" s="11">
-        <v>2027</v>
-      </c>
-      <c r="C22" s="11">
-        <v>9</v>
-      </c>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11">
-        <v>17629000</v>
-      </c>
-      <c r="F22" s="11">
-        <v>401855000</v>
-      </c>
-      <c r="G22" s="11">
-        <v>10282000</v>
-      </c>
-      <c r="H22" s="11">
-        <v>2118000</v>
-      </c>
-      <c r="I22" s="11">
-        <v>121366115</v>
-      </c>
-      <c r="J22" s="11">
-        <v>58367332</v>
-      </c>
-      <c r="K22" s="11">
-        <v>47481000</v>
-      </c>
-      <c r="L22" s="11">
-        <v>17287000</v>
-      </c>
-      <c r="M22" s="11">
-        <v>135369000</v>
-      </c>
-      <c r="N22" s="11">
-        <v>630677000</v>
-      </c>
-      <c r="O22" s="11">
-        <v>240763000</v>
-      </c>
-      <c r="P22" s="11">
-        <v>12225000</v>
-      </c>
-      <c r="Q22" s="11">
-        <v>19174000</v>
-      </c>
-      <c r="R22" s="11">
-        <v>185321000</v>
-      </c>
-      <c r="S22" s="11">
-        <v>636000</v>
-      </c>
-      <c r="T22" s="11">
-        <v>1406000</v>
-      </c>
-      <c r="U22" s="11"/>
-      <c r="V22" s="11"/>
-      <c r="W22" s="11"/>
-      <c r="X22" s="11"/>
-      <c r="Y22" s="13"/>
-      <c r="Z22" s="14"/>
-      <c r="AA22" s="14"/>
-      <c r="AB22" s="14"/>
-      <c r="AC22" s="14"/>
-      <c r="AD22" s="14"/>
-      <c r="AE22" s="14"/>
-      <c r="AF22" s="14"/>
-    </row>
-    <row r="23" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A23" s="10">
-        <v>46661</v>
-      </c>
-      <c r="B23" s="11">
-        <v>2027</v>
-      </c>
-      <c r="C23" s="11">
-        <v>10</v>
-      </c>
-      <c r="D23" s="11"/>
-      <c r="E23" s="11">
-        <v>18023000</v>
-      </c>
-      <c r="F23" s="11">
-        <v>1145495000</v>
-      </c>
-      <c r="G23" s="11">
-        <v>33356000</v>
-      </c>
-      <c r="H23" s="11">
-        <v>14268000</v>
-      </c>
-      <c r="I23" s="11">
-        <v>127300502</v>
-      </c>
-      <c r="J23" s="11">
-        <v>67424436</v>
-      </c>
-      <c r="K23" s="11">
-        <v>63544000</v>
-      </c>
-      <c r="L23" s="11">
-        <v>26101000</v>
-      </c>
-      <c r="M23" s="11">
-        <v>54479000</v>
-      </c>
-      <c r="N23" s="11">
-        <v>700819000</v>
-      </c>
-      <c r="O23" s="11">
-        <v>231269000</v>
-      </c>
-      <c r="P23" s="11">
-        <v>11743000</v>
-      </c>
-      <c r="Q23" s="11">
-        <v>20867000</v>
-      </c>
-      <c r="R23" s="11">
-        <v>198491000</v>
-      </c>
-      <c r="S23" s="11">
-        <v>30489000</v>
-      </c>
-      <c r="T23" s="11">
-        <v>2226000</v>
-      </c>
-      <c r="U23" s="11"/>
-      <c r="V23" s="11"/>
-      <c r="W23" s="11"/>
-      <c r="X23" s="11"/>
-      <c r="Y23" s="13"/>
-      <c r="Z23" s="14"/>
-      <c r="AA23" s="14"/>
-      <c r="AB23" s="14"/>
-      <c r="AC23" s="14"/>
-      <c r="AD23" s="14"/>
-      <c r="AE23" s="14"/>
-      <c r="AF23" s="14"/>
-    </row>
-    <row r="24" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A24" s="2">
-        <v>46692</v>
-      </c>
-      <c r="B24" s="11">
-        <v>2027</v>
-      </c>
-      <c r="C24" s="11">
-        <v>11</v>
-      </c>
-      <c r="D24" s="11"/>
-      <c r="E24" s="11">
-        <v>19511000</v>
-      </c>
-      <c r="F24" s="11">
-        <v>2683014000</v>
-      </c>
-      <c r="G24" s="11">
-        <v>62990000</v>
-      </c>
-      <c r="H24" s="11">
-        <v>35667000</v>
-      </c>
-      <c r="I24" s="11">
-        <v>137892931</v>
-      </c>
-      <c r="J24" s="11">
-        <v>80279411</v>
-      </c>
-      <c r="K24" s="11">
-        <v>89898000</v>
-      </c>
-      <c r="L24" s="11">
-        <v>59473000</v>
-      </c>
-      <c r="M24" s="11">
-        <v>64427000</v>
-      </c>
-      <c r="N24" s="11">
-        <v>789034000</v>
-      </c>
-      <c r="O24" s="11">
-        <v>231910000</v>
-      </c>
-      <c r="P24" s="11">
-        <v>11775000</v>
-      </c>
-      <c r="Q24" s="11">
-        <v>23439000</v>
-      </c>
-      <c r="R24" s="11">
-        <v>191590000</v>
-      </c>
-      <c r="S24" s="11">
-        <v>396000</v>
-      </c>
-      <c r="T24" s="11">
-        <v>5051000</v>
-      </c>
-      <c r="U24" s="11"/>
-      <c r="V24" s="11"/>
-      <c r="W24" s="11"/>
-      <c r="X24" s="11"/>
-      <c r="Y24" s="13"/>
-      <c r="Z24" s="14"/>
-      <c r="AA24" s="14"/>
-      <c r="AB24" s="14"/>
-      <c r="AC24" s="14"/>
-      <c r="AD24" s="14"/>
-      <c r="AE24" s="14"/>
-      <c r="AF24" s="14"/>
-    </row>
-    <row r="25" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A25" s="10">
-        <v>46722</v>
-      </c>
-      <c r="B25" s="11">
-        <v>2027</v>
-      </c>
-      <c r="C25" s="11">
-        <v>12</v>
-      </c>
-      <c r="D25" s="11"/>
-      <c r="E25" s="11">
-        <v>23240000</v>
-      </c>
-      <c r="F25" s="11">
-        <v>4769651000</v>
-      </c>
-      <c r="G25" s="11">
-        <v>89448000</v>
-      </c>
-      <c r="H25" s="11">
-        <v>65316000</v>
-      </c>
-      <c r="I25" s="11">
-        <v>164848874</v>
-      </c>
-      <c r="J25" s="11">
-        <v>92461003</v>
-      </c>
-      <c r="K25" s="11">
-        <v>147139000</v>
-      </c>
-      <c r="L25" s="11">
-        <v>125821000</v>
-      </c>
-      <c r="M25" s="11">
-        <v>142413000</v>
-      </c>
-      <c r="N25" s="11">
-        <v>744457000</v>
-      </c>
-      <c r="O25" s="11">
-        <v>236135000</v>
-      </c>
-      <c r="P25" s="11">
-        <v>11949000</v>
-      </c>
-      <c r="Q25" s="11">
-        <v>25012000</v>
-      </c>
-      <c r="R25" s="11">
-        <v>200254000</v>
-      </c>
-      <c r="S25" s="11">
-        <v>623000</v>
-      </c>
-      <c r="T25" s="11">
-        <v>9908000</v>
-      </c>
-      <c r="U25" s="11"/>
-      <c r="V25" s="11"/>
-      <c r="W25" s="11"/>
-      <c r="X25" s="11"/>
-      <c r="Y25" s="13"/>
-      <c r="Z25" s="14"/>
-      <c r="AA25" s="14"/>
-      <c r="AB25" s="14"/>
-      <c r="AC25" s="14"/>
-      <c r="AD25" s="14"/>
-      <c r="AE25" s="14"/>
-      <c r="AF25" s="14"/>
-    </row>
-    <row r="26" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A26" s="10">
-        <v>46753</v>
-      </c>
-      <c r="B26" s="11">
-        <v>2028</v>
-      </c>
-      <c r="C26" s="11">
-        <v>1</v>
-      </c>
-      <c r="D26" s="11"/>
-      <c r="E26" s="11">
-        <v>23062000</v>
-      </c>
-      <c r="F26" s="11">
-        <v>5122418000</v>
-      </c>
-      <c r="G26" s="11">
-        <v>94598000</v>
-      </c>
-      <c r="H26" s="11">
-        <v>73353000</v>
-      </c>
-      <c r="I26" s="11">
-        <v>159050914</v>
-      </c>
-      <c r="J26" s="11">
-        <v>76634553</v>
-      </c>
-      <c r="K26" s="11">
-        <v>162183000</v>
-      </c>
-      <c r="L26" s="11">
-        <v>142917000</v>
-      </c>
-      <c r="M26" s="11">
-        <v>172609000</v>
-      </c>
-      <c r="N26" s="11">
-        <v>806900000</v>
-      </c>
-      <c r="O26" s="11">
-        <v>216518000</v>
-      </c>
-      <c r="P26" s="11">
-        <v>9985000</v>
-      </c>
-      <c r="Q26" s="11">
-        <v>24238000</v>
-      </c>
-      <c r="R26" s="11">
-        <v>198941000</v>
-      </c>
-      <c r="S26" s="11">
-        <v>718000</v>
-      </c>
-      <c r="T26" s="11">
-        <v>12113000</v>
-      </c>
-      <c r="U26" s="11"/>
-      <c r="V26" s="11"/>
-      <c r="W26" s="11"/>
-      <c r="X26" s="11"/>
-      <c r="Y26" s="13"/>
-      <c r="Z26" s="14"/>
-      <c r="AA26" s="14"/>
-      <c r="AB26" s="14"/>
-      <c r="AC26" s="14"/>
-      <c r="AD26" s="14"/>
-      <c r="AE26" s="14"/>
-      <c r="AF26" s="14"/>
-    </row>
-    <row r="27" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A27" s="10">
-        <v>46784</v>
-      </c>
-      <c r="B27" s="11">
-        <v>2028</v>
-      </c>
-      <c r="C27" s="11">
-        <v>2</v>
-      </c>
-      <c r="D27" s="11"/>
-      <c r="E27" s="11">
-        <v>20213000</v>
-      </c>
-      <c r="F27" s="11">
-        <v>4255346000</v>
-      </c>
-      <c r="G27" s="11">
-        <v>84923000</v>
-      </c>
-      <c r="H27" s="11">
-        <v>63009000</v>
-      </c>
-      <c r="I27" s="11">
-        <v>148816127</v>
-      </c>
-      <c r="J27" s="11">
-        <v>71820003</v>
-      </c>
-      <c r="K27" s="11">
-        <v>146431000</v>
-      </c>
-      <c r="L27" s="11">
-        <v>123138000</v>
-      </c>
-      <c r="M27" s="11">
-        <v>147128000</v>
-      </c>
-      <c r="N27" s="11">
-        <v>896379000</v>
-      </c>
-      <c r="O27" s="11">
-        <v>209618000</v>
-      </c>
-      <c r="P27" s="11">
-        <v>8778000</v>
-      </c>
-      <c r="Q27" s="11">
-        <v>21646000</v>
-      </c>
-      <c r="R27" s="11">
-        <v>177942000</v>
-      </c>
-      <c r="S27" s="11">
-        <v>692000</v>
-      </c>
-      <c r="T27" s="11">
-        <v>9788000</v>
-      </c>
-      <c r="U27" s="11"/>
-      <c r="V27" s="11"/>
-      <c r="W27" s="11"/>
-      <c r="X27" s="11"/>
-      <c r="Y27" s="13"/>
-      <c r="Z27" s="14"/>
-      <c r="AA27" s="14"/>
-      <c r="AB27" s="14"/>
-      <c r="AC27" s="14"/>
-      <c r="AD27" s="14"/>
-      <c r="AE27" s="14"/>
-      <c r="AF27" s="14"/>
-    </row>
-    <row r="28" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A28" s="10">
-        <v>46813</v>
-      </c>
-      <c r="B28" s="11">
-        <v>2028</v>
-      </c>
-      <c r="C28" s="11">
-        <v>3</v>
-      </c>
-      <c r="D28" s="11"/>
-      <c r="E28" s="11">
-        <v>22451000</v>
-      </c>
-      <c r="F28" s="11">
-        <v>2899376000</v>
-      </c>
-      <c r="G28" s="11">
-        <v>59251000</v>
-      </c>
-      <c r="H28" s="11">
-        <v>35714000</v>
-      </c>
-      <c r="I28" s="11">
-        <v>150984396</v>
-      </c>
-      <c r="J28" s="11">
-        <v>90372839</v>
-      </c>
-      <c r="K28" s="11">
-        <v>121979000</v>
-      </c>
-      <c r="L28" s="11">
-        <v>90164000</v>
-      </c>
-      <c r="M28" s="11">
-        <v>89485000</v>
-      </c>
-      <c r="N28" s="11">
-        <v>875653000</v>
-      </c>
-      <c r="O28" s="11">
-        <v>222820000</v>
-      </c>
-      <c r="P28" s="11">
-        <v>10482000</v>
-      </c>
-      <c r="Q28" s="11">
-        <v>22930000</v>
-      </c>
-      <c r="R28" s="11">
-        <v>196754000</v>
-      </c>
-      <c r="S28" s="11">
-        <v>572000</v>
-      </c>
-      <c r="T28" s="11">
-        <v>6783000</v>
-      </c>
-      <c r="U28" s="11"/>
-      <c r="V28" s="11"/>
-      <c r="W28" s="11"/>
-      <c r="X28" s="11"/>
-      <c r="Y28" s="13"/>
-      <c r="Z28" s="14"/>
-      <c r="AA28" s="14"/>
-      <c r="AB28" s="14"/>
-      <c r="AC28" s="14"/>
-      <c r="AD28" s="14"/>
-      <c r="AE28" s="14"/>
-      <c r="AF28" s="14"/>
-    </row>
-    <row r="29" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A29" s="10">
-        <v>46844</v>
-      </c>
-      <c r="B29" s="11">
-        <v>2028</v>
-      </c>
-      <c r="C29" s="11">
-        <v>4</v>
-      </c>
-      <c r="D29" s="11"/>
-      <c r="E29" s="11">
-        <v>16704000</v>
-      </c>
-      <c r="F29" s="11">
-        <v>1567364000</v>
-      </c>
-      <c r="G29" s="11">
-        <v>38888000</v>
-      </c>
-      <c r="H29" s="11">
-        <v>17526000</v>
-      </c>
-      <c r="I29" s="11">
-        <v>138810976</v>
-      </c>
-      <c r="J29" s="11">
-        <v>76900347</v>
-      </c>
-      <c r="K29" s="11">
-        <v>83389000</v>
-      </c>
-      <c r="L29" s="11">
-        <v>43127000</v>
-      </c>
-      <c r="M29" s="11">
-        <v>36612000</v>
-      </c>
-      <c r="N29" s="11">
-        <v>741576000</v>
-      </c>
-      <c r="O29" s="11">
-        <v>222103000</v>
-      </c>
-      <c r="P29" s="11">
-        <v>10449000</v>
-      </c>
-      <c r="Q29" s="11">
-        <v>18324000</v>
-      </c>
-      <c r="R29" s="11">
-        <v>190773000</v>
-      </c>
-      <c r="S29" s="11">
-        <v>532000</v>
-      </c>
-      <c r="T29" s="11">
-        <v>2495000</v>
-      </c>
-      <c r="U29" s="11"/>
-      <c r="V29" s="11"/>
-      <c r="W29" s="11"/>
-      <c r="X29" s="11"/>
-      <c r="Y29" s="13"/>
-      <c r="Z29" s="14"/>
-      <c r="AA29" s="14"/>
-      <c r="AB29" s="14"/>
-      <c r="AC29" s="14"/>
-      <c r="AD29" s="14"/>
-      <c r="AE29" s="14"/>
-      <c r="AF29" s="14"/>
-    </row>
-    <row r="30" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A30" s="10">
-        <v>46874</v>
-      </c>
-      <c r="B30" s="11">
-        <v>2028</v>
-      </c>
-      <c r="C30" s="11">
-        <v>5</v>
-      </c>
-      <c r="D30" s="11"/>
-      <c r="E30" s="11">
-        <v>18045000</v>
-      </c>
-      <c r="F30" s="11">
-        <v>985179000</v>
-      </c>
-      <c r="G30" s="11">
-        <v>23841000</v>
-      </c>
-      <c r="H30" s="11">
-        <v>8143000</v>
-      </c>
-      <c r="I30" s="11">
-        <v>137975948</v>
-      </c>
-      <c r="J30" s="11">
-        <v>75058261</v>
-      </c>
-      <c r="K30" s="11">
-        <v>68279000</v>
-      </c>
-      <c r="L30" s="11">
-        <v>27716000</v>
-      </c>
-      <c r="M30" s="11">
-        <v>62832000</v>
-      </c>
-      <c r="N30" s="11">
-        <v>705555000</v>
-      </c>
-      <c r="O30" s="11">
-        <v>231326000</v>
-      </c>
-      <c r="P30" s="11">
-        <v>10553000</v>
-      </c>
-      <c r="Q30" s="11">
-        <v>15753000</v>
-      </c>
-      <c r="R30" s="11">
-        <v>196754000</v>
-      </c>
-      <c r="S30" s="11">
-        <v>330000</v>
-      </c>
-      <c r="T30" s="11">
-        <v>2160000</v>
-      </c>
-      <c r="U30" s="11"/>
-      <c r="V30" s="11"/>
-      <c r="W30" s="11"/>
-      <c r="X30" s="11"/>
-      <c r="Y30" s="13"/>
-      <c r="Z30" s="14"/>
-      <c r="AA30" s="14"/>
-      <c r="AB30" s="14"/>
-      <c r="AC30" s="14"/>
-      <c r="AD30" s="14"/>
-      <c r="AE30" s="14"/>
-      <c r="AF30" s="14"/>
-    </row>
-    <row r="31" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A31" s="10">
-        <v>46905</v>
-      </c>
-      <c r="B31" s="11">
-        <v>2028</v>
-      </c>
-      <c r="C31" s="11">
-        <v>6</v>
-      </c>
-      <c r="D31" s="11"/>
-      <c r="E31" s="11">
-        <v>17184000</v>
-      </c>
-      <c r="F31" s="11">
-        <v>456022000</v>
-      </c>
-      <c r="G31" s="11">
-        <v>10022000</v>
-      </c>
-      <c r="H31" s="11">
-        <v>3345000</v>
-      </c>
-      <c r="I31" s="11">
-        <v>127128343</v>
-      </c>
-      <c r="J31" s="11">
-        <v>68479865</v>
-      </c>
-      <c r="K31" s="11">
-        <v>55123000</v>
-      </c>
-      <c r="L31" s="11">
-        <v>20481000</v>
-      </c>
-      <c r="M31" s="11">
-        <v>136370000</v>
-      </c>
-      <c r="N31" s="11">
-        <v>779181000</v>
-      </c>
-      <c r="O31" s="11">
-        <v>227494000</v>
-      </c>
-      <c r="P31" s="11">
-        <v>10777000</v>
-      </c>
-      <c r="Q31" s="11">
-        <v>11758000</v>
-      </c>
-      <c r="R31" s="11">
-        <v>192521000</v>
-      </c>
-      <c r="S31" s="11">
-        <v>325000</v>
-      </c>
-      <c r="T31" s="11">
-        <v>1811000</v>
-      </c>
-      <c r="U31" s="11"/>
-      <c r="V31" s="11"/>
-      <c r="W31" s="11"/>
-      <c r="X31" s="11"/>
-      <c r="Y31" s="13"/>
-      <c r="Z31" s="14"/>
-      <c r="AA31" s="14"/>
-      <c r="AB31" s="14"/>
-      <c r="AC31" s="14"/>
-      <c r="AD31" s="14"/>
-      <c r="AE31" s="14"/>
-      <c r="AF31" s="14"/>
-    </row>
-    <row r="32" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A32" s="10">
-        <v>46935</v>
-      </c>
-      <c r="B32" s="11">
-        <v>2028</v>
-      </c>
-      <c r="C32" s="11">
-        <v>7</v>
-      </c>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11">
-        <v>18522000</v>
-      </c>
-      <c r="F32" s="11">
-        <v>454579000</v>
-      </c>
-      <c r="G32" s="11">
-        <v>11004000</v>
-      </c>
-      <c r="H32" s="11">
-        <v>3162000</v>
-      </c>
-      <c r="I32" s="11">
-        <v>129387476</v>
-      </c>
-      <c r="J32" s="11">
-        <v>58501254</v>
-      </c>
-      <c r="K32" s="11">
-        <v>48913000</v>
-      </c>
-      <c r="L32" s="11">
-        <v>18586000</v>
-      </c>
-      <c r="M32" s="11">
-        <v>200621000</v>
-      </c>
-      <c r="N32" s="11">
-        <v>658854000</v>
-      </c>
-      <c r="O32" s="11">
-        <v>246513000</v>
-      </c>
-      <c r="P32" s="11">
-        <v>10269000</v>
-      </c>
-      <c r="Q32" s="11">
-        <v>18775000</v>
-      </c>
-      <c r="R32" s="11">
-        <v>198701000</v>
-      </c>
-      <c r="S32" s="11">
-        <v>617000</v>
-      </c>
-      <c r="T32" s="11">
-        <v>1603000</v>
-      </c>
-      <c r="U32" s="11"/>
-      <c r="V32" s="11"/>
-      <c r="W32" s="11"/>
-      <c r="X32" s="11"/>
-      <c r="Y32" s="13"/>
-      <c r="Z32" s="14"/>
-      <c r="AA32" s="14"/>
-      <c r="AB32" s="14"/>
-      <c r="AC32" s="14"/>
-      <c r="AD32" s="14"/>
-      <c r="AE32" s="14"/>
-      <c r="AF32" s="14"/>
-    </row>
-    <row r="33" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A33" s="2">
-        <v>46966</v>
-      </c>
-      <c r="B33" s="11">
-        <v>2028</v>
-      </c>
-      <c r="C33" s="11">
-        <v>8</v>
-      </c>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11">
-        <v>18367000</v>
-      </c>
-      <c r="F33" s="11">
-        <v>496011000</v>
-      </c>
-      <c r="G33" s="11">
-        <v>12430000</v>
-      </c>
-      <c r="H33" s="11">
-        <v>3414000</v>
-      </c>
-      <c r="I33" s="11">
-        <v>126028791</v>
-      </c>
-      <c r="J33" s="11">
-        <v>53304803</v>
-      </c>
-      <c r="K33" s="11">
-        <v>45716000</v>
-      </c>
-      <c r="L33" s="11">
-        <v>17091000</v>
-      </c>
-      <c r="M33" s="11">
-        <v>201775000</v>
-      </c>
-      <c r="N33" s="11">
-        <v>680707000</v>
-      </c>
-      <c r="O33" s="11">
-        <v>248133000</v>
-      </c>
-      <c r="P33" s="11">
-        <v>10767000</v>
-      </c>
-      <c r="Q33" s="11">
-        <v>17200000</v>
-      </c>
-      <c r="R33" s="11">
-        <v>198701000</v>
-      </c>
-      <c r="S33" s="11">
-        <v>599000</v>
-      </c>
-      <c r="T33" s="11">
-        <v>1457000</v>
-      </c>
-      <c r="U33" s="11"/>
-      <c r="V33" s="11"/>
-      <c r="W33" s="11"/>
-      <c r="X33" s="11"/>
-      <c r="Y33" s="13"/>
-      <c r="Z33" s="14"/>
-      <c r="AA33" s="14"/>
-      <c r="AB33" s="14"/>
-      <c r="AC33" s="14"/>
-      <c r="AD33" s="14"/>
-      <c r="AE33" s="14"/>
-      <c r="AF33" s="14"/>
-    </row>
-    <row r="34" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A34" s="10">
-        <v>46997</v>
-      </c>
-      <c r="B34" s="11">
-        <v>2028</v>
-      </c>
-      <c r="C34" s="11">
-        <v>9</v>
-      </c>
-      <c r="D34" s="11"/>
-      <c r="E34" s="11">
-        <v>17452000</v>
-      </c>
-      <c r="F34" s="11">
-        <v>444326000</v>
-      </c>
-      <c r="G34" s="11">
-        <v>10274000</v>
-      </c>
-      <c r="H34" s="11">
-        <v>2074000</v>
-      </c>
-      <c r="I34" s="11">
-        <v>122712497</v>
-      </c>
-      <c r="J34" s="11">
-        <v>58889416</v>
-      </c>
-      <c r="K34" s="11">
-        <v>47956000</v>
-      </c>
-      <c r="L34" s="11">
-        <v>17322000</v>
-      </c>
-      <c r="M34" s="11">
-        <v>136046000</v>
-      </c>
-      <c r="N34" s="11">
-        <v>708814000</v>
-      </c>
-      <c r="O34" s="11">
-        <v>229812000</v>
-      </c>
-      <c r="P34" s="11">
-        <v>11669000</v>
-      </c>
-      <c r="Q34" s="11">
-        <v>18695000</v>
-      </c>
-      <c r="R34" s="11">
-        <v>192292000</v>
-      </c>
-      <c r="S34" s="11">
-        <v>602000</v>
-      </c>
-      <c r="T34" s="11">
-        <v>1390000</v>
-      </c>
-      <c r="U34" s="11"/>
-      <c r="V34" s="11"/>
-      <c r="W34" s="11"/>
-      <c r="X34" s="11"/>
-      <c r="Y34" s="13"/>
-      <c r="Z34" s="14"/>
-      <c r="AA34" s="14"/>
-      <c r="AB34" s="14"/>
-      <c r="AC34" s="14"/>
-      <c r="AD34" s="14"/>
-      <c r="AE34" s="14"/>
-      <c r="AF34" s="14"/>
-    </row>
-    <row r="35" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A35" s="10">
-        <v>47027</v>
-      </c>
-      <c r="B35" s="11">
-        <v>2028</v>
-      </c>
-      <c r="C35" s="11">
-        <v>10</v>
-      </c>
-      <c r="D35" s="11"/>
-      <c r="E35" s="11">
-        <v>17843000</v>
-      </c>
-      <c r="F35" s="11">
-        <v>990424000</v>
-      </c>
-      <c r="G35" s="11">
-        <v>33329000</v>
-      </c>
-      <c r="H35" s="11">
-        <v>13968000</v>
-      </c>
-      <c r="I35" s="11">
-        <v>128712717</v>
-      </c>
-      <c r="J35" s="11">
-        <v>68027534</v>
-      </c>
-      <c r="K35" s="11">
-        <v>64180000</v>
-      </c>
-      <c r="L35" s="11">
-        <v>26154000</v>
-      </c>
-      <c r="M35" s="11">
-        <v>54752000</v>
-      </c>
-      <c r="N35" s="11">
-        <v>586196000</v>
-      </c>
-      <c r="O35" s="11">
-        <v>220681000</v>
-      </c>
-      <c r="P35" s="11">
-        <v>11206000</v>
-      </c>
-      <c r="Q35" s="11">
-        <v>20346000</v>
-      </c>
-      <c r="R35" s="11">
-        <v>196954000</v>
-      </c>
-      <c r="S35" s="11">
-        <v>479000</v>
-      </c>
-      <c r="T35" s="11">
-        <v>2201000</v>
-      </c>
-      <c r="U35" s="11"/>
-      <c r="V35" s="11"/>
-      <c r="W35" s="11"/>
-      <c r="X35" s="11"/>
-      <c r="Y35" s="13"/>
-      <c r="Z35" s="14"/>
-      <c r="AA35" s="14"/>
-      <c r="AB35" s="14"/>
-      <c r="AC35" s="14"/>
-      <c r="AD35" s="14"/>
-      <c r="AE35" s="14"/>
-      <c r="AF35" s="14"/>
-    </row>
-    <row r="36" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A36" s="2">
-        <v>47058</v>
-      </c>
-      <c r="B36" s="11">
-        <v>2028</v>
-      </c>
-      <c r="C36" s="11">
-        <v>11</v>
-      </c>
-      <c r="D36" s="11"/>
-      <c r="E36" s="11">
-        <v>19316000</v>
-      </c>
-      <c r="F36" s="11">
-        <v>2694414000</v>
-      </c>
-      <c r="G36" s="11">
-        <v>62939000</v>
-      </c>
-      <c r="H36" s="11">
-        <v>34918000</v>
-      </c>
-      <c r="I36" s="11">
-        <v>139422654</v>
-      </c>
-      <c r="J36" s="11">
-        <v>80997495</v>
-      </c>
-      <c r="K36" s="11">
-        <v>90797000</v>
-      </c>
-      <c r="L36" s="11">
-        <v>59592000</v>
-      </c>
-      <c r="M36" s="11">
-        <v>64750000</v>
-      </c>
-      <c r="N36" s="11">
-        <v>794966000</v>
-      </c>
-      <c r="O36" s="11">
-        <v>221222000</v>
-      </c>
-      <c r="P36" s="11">
-        <v>11233000</v>
-      </c>
-      <c r="Q36" s="11">
-        <v>22853000</v>
-      </c>
-      <c r="R36" s="11">
-        <v>190107000</v>
-      </c>
-      <c r="S36" s="11">
-        <v>375000</v>
-      </c>
-      <c r="T36" s="11">
-        <v>4995000</v>
-      </c>
-      <c r="U36" s="11"/>
-      <c r="V36" s="11"/>
-      <c r="W36" s="11"/>
-      <c r="X36" s="11"/>
-      <c r="Y36" s="13"/>
-      <c r="Z36" s="14"/>
-      <c r="AA36" s="14"/>
-      <c r="AB36" s="14"/>
-      <c r="AC36" s="14"/>
-      <c r="AD36" s="14"/>
-      <c r="AE36" s="14"/>
-      <c r="AF36" s="14"/>
-    </row>
-    <row r="37" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A37" s="10">
-        <v>47088</v>
-      </c>
-      <c r="B37" s="11">
-        <v>2028</v>
-      </c>
-      <c r="C37" s="11">
-        <v>12</v>
-      </c>
-      <c r="D37" s="11"/>
-      <c r="E37" s="11">
-        <v>23008000</v>
-      </c>
-      <c r="F37" s="11">
-        <v>4767418000</v>
-      </c>
-      <c r="G37" s="11">
-        <v>89376000</v>
-      </c>
-      <c r="H37" s="11">
-        <v>63944000</v>
-      </c>
-      <c r="I37" s="11">
-        <v>166677635</v>
-      </c>
-      <c r="J37" s="11">
-        <v>93288048</v>
-      </c>
-      <c r="K37" s="11">
-        <v>148610000</v>
-      </c>
-      <c r="L37" s="11">
-        <v>126073000</v>
-      </c>
-      <c r="M37" s="11">
-        <v>143125000</v>
-      </c>
-      <c r="N37" s="11">
-        <v>761459000</v>
-      </c>
-      <c r="O37" s="11">
-        <v>225255000</v>
-      </c>
-      <c r="P37" s="11">
-        <v>11396000</v>
-      </c>
-      <c r="Q37" s="11">
-        <v>24387000</v>
-      </c>
-      <c r="R37" s="11">
-        <v>198699000</v>
-      </c>
-      <c r="S37" s="11">
-        <v>590000</v>
-      </c>
-      <c r="T37" s="11">
-        <v>9799000</v>
-      </c>
-      <c r="U37" s="11"/>
-      <c r="V37" s="11"/>
-      <c r="W37" s="11"/>
-      <c r="X37" s="11"/>
-      <c r="Y37" s="13"/>
-      <c r="Z37" s="14"/>
-      <c r="AA37" s="14"/>
-      <c r="AB37" s="14"/>
-      <c r="AC37" s="14"/>
-      <c r="AD37" s="14"/>
-      <c r="AE37" s="14"/>
-      <c r="AF37" s="14"/>
-    </row>
-    <row r="39" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="E39">
-        <v>1000</v>
-      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/공급량실적_계획_실적_MJ.xlsx
+++ b/공급량실적_계획_실적_MJ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\실천사업계획\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57AC8545-600E-4640-9A0E-934C3A2A20C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CB0E25D-12F1-4D0D-8D9D-7140B8CE1EA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="공급량_실적" sheetId="1" r:id="rId1"/>
@@ -1965,80 +1965,80 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2C1F99CF-9391-4872-B93D-50B931598DD3}" name="표1_3" displayName="표1_3" ref="A1:AF13" totalsRowShown="0" headerRowDxfId="94" dataDxfId="93">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2C1F99CF-9391-4872-B93D-50B931598DD3}" name="표1_3" displayName="표1_3" ref="A1:AF13" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
   <tableColumns count="32">
-    <tableColumn id="1" xr3:uid="{19685FD4-89CE-478F-94BA-7A4B1E721FD4}" name="날짜" dataDxfId="92"/>
-    <tableColumn id="2" xr3:uid="{E31CA521-8EDF-4B60-95F2-6D99A2A44422}" name="연" dataDxfId="91"/>
-    <tableColumn id="3" xr3:uid="{0E1A3862-691A-4EE3-BC9F-15442CFF7BF6}" name="월" dataDxfId="90"/>
-    <tableColumn id="4" xr3:uid="{70EF9B81-BEFB-4CBB-822B-4CF1F1061D51}" name="평균기온" dataDxfId="89"/>
-    <tableColumn id="7" xr3:uid="{FC97C89C-B827-4EAB-8DAD-DBE4EB83293B}" name="취사용" dataDxfId="88"/>
-    <tableColumn id="5" xr3:uid="{6EB58682-1AB0-402D-B1B5-64D7A3FEE7DC}" name="개별난방용" dataDxfId="87"/>
-    <tableColumn id="6" xr3:uid="{9B5B2C66-64AC-4900-AA35-A909EB1F3ADB}" name="중앙난방용" dataDxfId="86"/>
-    <tableColumn id="19" xr3:uid="{BB6DF2E3-2587-479E-A2F3-005ADFBAD580}" name="자가열전용" dataDxfId="85"/>
-    <tableColumn id="32" xr3:uid="{19247A41-B716-45A1-89D6-71493825C64A}" name="영업용" dataDxfId="84"/>
-    <tableColumn id="9" xr3:uid="{AE3DB5EB-C7E4-47AD-9093-9ED129869DB2}" name="일반용(1)" dataDxfId="83"/>
-    <tableColumn id="12" xr3:uid="{8B4AF52F-6164-471B-AE99-CC06D0BB14EF}" name="일반용(2)" dataDxfId="82"/>
-    <tableColumn id="13" xr3:uid="{371738D5-71AD-4443-9E50-C5CBFA38DD53}" name="업무난방용" dataDxfId="81"/>
-    <tableColumn id="16" xr3:uid="{900065B7-DB40-43BE-8FF7-E75CA356AC45}" name="냉난방용" dataDxfId="80"/>
-    <tableColumn id="15" xr3:uid="{DEBF6157-B4E3-448F-B30C-6BA984C794F5}" name="산업용" dataDxfId="79"/>
-    <tableColumn id="22" xr3:uid="{110C96B1-CEF5-460E-976A-E31DDA355398}" name="수송용(CNG)" dataDxfId="78"/>
-    <tableColumn id="21" xr3:uid="{06CF64A6-4CFF-491D-A557-FA4850CF0868}" name="수송용(BIO)" dataDxfId="77"/>
-    <tableColumn id="17" xr3:uid="{325D94CD-83AF-4821-8554-98F27BA03A89}" name="열병합용" dataDxfId="76"/>
-    <tableColumn id="18" xr3:uid="{6CE1C920-1D02-4ED1-B172-01F6E3A7A08C}" name="연료전지용" dataDxfId="75"/>
-    <tableColumn id="20" xr3:uid="{0B7A0B86-42DA-48FF-AD28-7D4F4C7EE8B6}" name="열전용설비용(주택외)" dataDxfId="74"/>
-    <tableColumn id="14" xr3:uid="{66ED3A2C-2F9A-4DC1-B2E1-96B11BA082CD}" name="주한미군" dataDxfId="73"/>
-    <tableColumn id="11" xr3:uid="{8576E086-9957-4A83-B3D2-E6372750D253}" name="일반용1(영업)" dataDxfId="72"/>
-    <tableColumn id="10" xr3:uid="{AC7AEF69-FC00-4021-A757-1F6CB56D86E9}" name="일반용1(업무)" dataDxfId="71"/>
-    <tableColumn id="23" xr3:uid="{0A863EFD-5ACB-4216-A172-3D5E489B9B61}" name="총공급량" dataDxfId="70"/>
-    <tableColumn id="24" xr3:uid="{3F3F5052-4199-490C-8994-5E9CF83BDE9D}" name="총합계" dataDxfId="69"/>
-    <tableColumn id="25" xr3:uid="{F3502AAC-AAE0-469B-8FF7-545D8F24C683}" name="비교(V-W)" dataDxfId="68"/>
-    <tableColumn id="8" xr3:uid="{FA0345C9-D72C-4A34-84B0-7B3673E66B4B}" name="열1" dataDxfId="67"/>
-    <tableColumn id="26" xr3:uid="{924F492C-4495-498A-A3CC-8AB7A213EB49}" name="열2" dataDxfId="66"/>
-    <tableColumn id="27" xr3:uid="{7D1ACE6F-EB3E-490F-A815-30511D277AEB}" name="열3" dataDxfId="65"/>
-    <tableColumn id="28" xr3:uid="{D28E208B-F040-4AE4-ACFF-E094E4F8E7A7}" name="열4" dataDxfId="64"/>
-    <tableColumn id="29" xr3:uid="{186D4369-AF71-4A71-9851-5932B907782C}" name="열5" dataDxfId="63"/>
-    <tableColumn id="30" xr3:uid="{896603AA-8674-4905-8A79-3984C733419F}" name="열6" dataDxfId="62"/>
-    <tableColumn id="31" xr3:uid="{27B69BAA-C555-4945-8804-7D4A8F0D00B9}" name="열7" dataDxfId="61"/>
+    <tableColumn id="1" xr3:uid="{19685FD4-89CE-478F-94BA-7A4B1E721FD4}" name="날짜" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{E31CA521-8EDF-4B60-95F2-6D99A2A44422}" name="연" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{0E1A3862-691A-4EE3-BC9F-15442CFF7BF6}" name="월" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{70EF9B81-BEFB-4CBB-822B-4CF1F1061D51}" name="평균기온" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{FC97C89C-B827-4EAB-8DAD-DBE4EB83293B}" name="취사용" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{6EB58682-1AB0-402D-B1B5-64D7A3FEE7DC}" name="개별난방용" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{9B5B2C66-64AC-4900-AA35-A909EB1F3ADB}" name="중앙난방용" dataDxfId="25"/>
+    <tableColumn id="19" xr3:uid="{BB6DF2E3-2587-479E-A2F3-005ADFBAD580}" name="자가열전용" dataDxfId="24"/>
+    <tableColumn id="32" xr3:uid="{19247A41-B716-45A1-89D6-71493825C64A}" name="영업용" dataDxfId="23"/>
+    <tableColumn id="9" xr3:uid="{AE3DB5EB-C7E4-47AD-9093-9ED129869DB2}" name="일반용(1)" dataDxfId="22"/>
+    <tableColumn id="12" xr3:uid="{8B4AF52F-6164-471B-AE99-CC06D0BB14EF}" name="일반용(2)" dataDxfId="21"/>
+    <tableColumn id="13" xr3:uid="{371738D5-71AD-4443-9E50-C5CBFA38DD53}" name="업무난방용" dataDxfId="20"/>
+    <tableColumn id="16" xr3:uid="{900065B7-DB40-43BE-8FF7-E75CA356AC45}" name="냉난방용" dataDxfId="19"/>
+    <tableColumn id="15" xr3:uid="{DEBF6157-B4E3-448F-B30C-6BA984C794F5}" name="산업용" dataDxfId="18"/>
+    <tableColumn id="22" xr3:uid="{110C96B1-CEF5-460E-976A-E31DDA355398}" name="수송용(CNG)" dataDxfId="17"/>
+    <tableColumn id="21" xr3:uid="{06CF64A6-4CFF-491D-A557-FA4850CF0868}" name="수송용(BIO)" dataDxfId="16"/>
+    <tableColumn id="17" xr3:uid="{325D94CD-83AF-4821-8554-98F27BA03A89}" name="열병합용" dataDxfId="15"/>
+    <tableColumn id="18" xr3:uid="{6CE1C920-1D02-4ED1-B172-01F6E3A7A08C}" name="연료전지용" dataDxfId="14"/>
+    <tableColumn id="20" xr3:uid="{0B7A0B86-42DA-48FF-AD28-7D4F4C7EE8B6}" name="열전용설비용(주택외)" dataDxfId="13"/>
+    <tableColumn id="14" xr3:uid="{66ED3A2C-2F9A-4DC1-B2E1-96B11BA082CD}" name="주한미군" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{8576E086-9957-4A83-B3D2-E6372750D253}" name="일반용1(영업)" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{AC7AEF69-FC00-4021-A757-1F6CB56D86E9}" name="일반용1(업무)" dataDxfId="10"/>
+    <tableColumn id="23" xr3:uid="{0A863EFD-5ACB-4216-A172-3D5E489B9B61}" name="총공급량" dataDxfId="9"/>
+    <tableColumn id="24" xr3:uid="{3F3F5052-4199-490C-8994-5E9CF83BDE9D}" name="총합계" dataDxfId="8"/>
+    <tableColumn id="25" xr3:uid="{F3502AAC-AAE0-469B-8FF7-545D8F24C683}" name="비교(V-W)" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{FA0345C9-D72C-4A34-84B0-7B3673E66B4B}" name="열1" dataDxfId="6"/>
+    <tableColumn id="26" xr3:uid="{924F492C-4495-498A-A3CC-8AB7A213EB49}" name="열2" dataDxfId="5"/>
+    <tableColumn id="27" xr3:uid="{7D1ACE6F-EB3E-490F-A815-30511D277AEB}" name="열3" dataDxfId="4"/>
+    <tableColumn id="28" xr3:uid="{D28E208B-F040-4AE4-ACFF-E094E4F8E7A7}" name="열4" dataDxfId="3"/>
+    <tableColumn id="29" xr3:uid="{186D4369-AF71-4A71-9851-5932B907782C}" name="열5" dataDxfId="2"/>
+    <tableColumn id="30" xr3:uid="{896603AA-8674-4905-8A79-3984C733419F}" name="열6" dataDxfId="1"/>
+    <tableColumn id="31" xr3:uid="{27B69BAA-C555-4945-8804-7D4A8F0D00B9}" name="열7" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{EC6B23D4-390C-404E-AE69-455A5E70B9EF}" name="표1_34" displayName="표1_34" ref="A1:AF13" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{EC6B23D4-390C-404E-AE69-455A5E70B9EF}" name="표1_34" displayName="표1_34" ref="A1:AF13" totalsRowShown="0" headerRowDxfId="94" dataDxfId="93">
   <tableColumns count="32">
-    <tableColumn id="1" xr3:uid="{32BFE98C-3743-4F2A-B0AA-77B0B6019DD7}" name="날짜" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{51E25201-28D0-4E8C-BEC7-0E3F4D5F3645}" name="연" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{80FFE0A8-C94B-40E9-B01D-932A55EF6766}" name="월" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{B563055E-F2FB-42BE-BA0E-E08593191708}" name="평균기온" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{EC02A3A1-631C-42EF-85AF-A8B79A8D9F9B}" name="취사용" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{86073F88-2F80-4462-BB87-5B8A54551B6A}" name="개별난방용" dataDxfId="26"/>
-    <tableColumn id="6" xr3:uid="{139EC257-82FA-481B-9F18-60ADA6EB50D3}" name="중앙난방용" dataDxfId="25"/>
-    <tableColumn id="19" xr3:uid="{408C0C4D-65A0-4DC3-A85C-EF1BC48BFA6F}" name="자가열전용" dataDxfId="24"/>
-    <tableColumn id="32" xr3:uid="{F08BABB7-87AA-4744-89E7-228FA9D35660}" name="영업용" dataDxfId="23"/>
-    <tableColumn id="9" xr3:uid="{D46D49CA-B262-4926-A5D1-6DDB23F119D4}" name="일반용(1)" dataDxfId="22"/>
-    <tableColumn id="12" xr3:uid="{861B7867-2B87-4609-A7B2-0963E4807DC3}" name="일반용(2)" dataDxfId="21"/>
-    <tableColumn id="13" xr3:uid="{14954B61-A6C3-4B22-BB69-82FCB6C6800D}" name="업무난방용" dataDxfId="20"/>
-    <tableColumn id="16" xr3:uid="{79636BBA-3A6E-42BA-959F-C2875D1EB9BF}" name="냉난방용" dataDxfId="19"/>
-    <tableColumn id="15" xr3:uid="{9E90082E-3CE5-4697-A0B1-A041913653D4}" name="산업용" dataDxfId="18"/>
-    <tableColumn id="22" xr3:uid="{15EC95E6-8587-482D-BF25-3DEDC8762C1E}" name="수송용(CNG)" dataDxfId="17"/>
-    <tableColumn id="21" xr3:uid="{0578ED32-2CDD-4E0D-B4BF-9D8549DC6AE8}" name="수송용(BIO)" dataDxfId="16"/>
-    <tableColumn id="17" xr3:uid="{A2C46C4C-5370-461A-AEAE-B18F07625F71}" name="열병합용" dataDxfId="15"/>
-    <tableColumn id="18" xr3:uid="{DF7D0596-2D46-4696-A139-30735FD75FF7}" name="연료전지용" dataDxfId="14"/>
-    <tableColumn id="20" xr3:uid="{BE9174ED-E86A-4C72-8087-5A38B6314769}" name="열전용설비용(주택외)" dataDxfId="13"/>
-    <tableColumn id="14" xr3:uid="{094C3E7A-F02F-42B7-A5BF-D2A7A7C7AD81}" name="주한미군" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{7BEB8593-2810-4E4B-9386-DAA32EE4C15D}" name="일반용1(영업)" dataDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{35165667-3CFF-4452-B99D-526A70B3D7E9}" name="일반용1(업무)" dataDxfId="10"/>
-    <tableColumn id="23" xr3:uid="{B2866D34-3868-4FBB-9E30-43CEB374404E}" name="총공급량" dataDxfId="9"/>
-    <tableColumn id="24" xr3:uid="{894A25E9-5A19-4242-9DB5-639CFBC374F1}" name="총합계" dataDxfId="8"/>
-    <tableColumn id="25" xr3:uid="{F5CCC6CB-E5AE-40FD-91C6-4E7CB9F4BA01}" name="비교(V-W)" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{B91B61DE-5B24-4EC8-93F0-0F6AA7D335E4}" name="열1" dataDxfId="6"/>
-    <tableColumn id="26" xr3:uid="{E44140AD-42FF-4A23-851A-478A137EFA9D}" name="열2" dataDxfId="5"/>
-    <tableColumn id="27" xr3:uid="{73E9254A-E008-4F5A-B403-48577589F0F0}" name="열3" dataDxfId="4"/>
-    <tableColumn id="28" xr3:uid="{A4720811-BD5E-45EB-A6A1-04B96A422368}" name="열4" dataDxfId="3"/>
-    <tableColumn id="29" xr3:uid="{9EC4A7AA-2590-44BE-A6D9-3BC81C55515C}" name="열5" dataDxfId="2"/>
-    <tableColumn id="30" xr3:uid="{D9BA0330-49D3-4037-8508-64BF9FC5BD2C}" name="열6" dataDxfId="1"/>
-    <tableColumn id="31" xr3:uid="{AF823A94-60F7-4A09-B1B9-304146CD3013}" name="열7" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{32BFE98C-3743-4F2A-B0AA-77B0B6019DD7}" name="날짜" dataDxfId="92"/>
+    <tableColumn id="2" xr3:uid="{51E25201-28D0-4E8C-BEC7-0E3F4D5F3645}" name="연" dataDxfId="91"/>
+    <tableColumn id="3" xr3:uid="{80FFE0A8-C94B-40E9-B01D-932A55EF6766}" name="월" dataDxfId="90"/>
+    <tableColumn id="4" xr3:uid="{B563055E-F2FB-42BE-BA0E-E08593191708}" name="평균기온" dataDxfId="89"/>
+    <tableColumn id="7" xr3:uid="{EC02A3A1-631C-42EF-85AF-A8B79A8D9F9B}" name="취사용" dataDxfId="88"/>
+    <tableColumn id="5" xr3:uid="{86073F88-2F80-4462-BB87-5B8A54551B6A}" name="개별난방용" dataDxfId="87"/>
+    <tableColumn id="6" xr3:uid="{139EC257-82FA-481B-9F18-60ADA6EB50D3}" name="중앙난방용" dataDxfId="86"/>
+    <tableColumn id="19" xr3:uid="{408C0C4D-65A0-4DC3-A85C-EF1BC48BFA6F}" name="자가열전용" dataDxfId="85"/>
+    <tableColumn id="32" xr3:uid="{F08BABB7-87AA-4744-89E7-228FA9D35660}" name="영업용" dataDxfId="84"/>
+    <tableColumn id="9" xr3:uid="{D46D49CA-B262-4926-A5D1-6DDB23F119D4}" name="일반용(1)" dataDxfId="83"/>
+    <tableColumn id="12" xr3:uid="{861B7867-2B87-4609-A7B2-0963E4807DC3}" name="일반용(2)" dataDxfId="82"/>
+    <tableColumn id="13" xr3:uid="{14954B61-A6C3-4B22-BB69-82FCB6C6800D}" name="업무난방용" dataDxfId="81"/>
+    <tableColumn id="16" xr3:uid="{79636BBA-3A6E-42BA-959F-C2875D1EB9BF}" name="냉난방용" dataDxfId="80"/>
+    <tableColumn id="15" xr3:uid="{9E90082E-3CE5-4697-A0B1-A041913653D4}" name="산업용" dataDxfId="79"/>
+    <tableColumn id="22" xr3:uid="{15EC95E6-8587-482D-BF25-3DEDC8762C1E}" name="수송용(CNG)" dataDxfId="78"/>
+    <tableColumn id="21" xr3:uid="{0578ED32-2CDD-4E0D-B4BF-9D8549DC6AE8}" name="수송용(BIO)" dataDxfId="77"/>
+    <tableColumn id="17" xr3:uid="{A2C46C4C-5370-461A-AEAE-B18F07625F71}" name="열병합용" dataDxfId="76"/>
+    <tableColumn id="18" xr3:uid="{DF7D0596-2D46-4696-A139-30735FD75FF7}" name="연료전지용" dataDxfId="75"/>
+    <tableColumn id="20" xr3:uid="{BE9174ED-E86A-4C72-8087-5A38B6314769}" name="열전용설비용(주택외)" dataDxfId="74"/>
+    <tableColumn id="14" xr3:uid="{094C3E7A-F02F-42B7-A5BF-D2A7A7C7AD81}" name="주한미군" dataDxfId="73"/>
+    <tableColumn id="11" xr3:uid="{7BEB8593-2810-4E4B-9386-DAA32EE4C15D}" name="일반용1(영업)" dataDxfId="72"/>
+    <tableColumn id="10" xr3:uid="{35165667-3CFF-4452-B99D-526A70B3D7E9}" name="일반용1(업무)" dataDxfId="71"/>
+    <tableColumn id="23" xr3:uid="{B2866D34-3868-4FBB-9E30-43CEB374404E}" name="총공급량" dataDxfId="70"/>
+    <tableColumn id="24" xr3:uid="{894A25E9-5A19-4242-9DB5-639CFBC374F1}" name="총합계" dataDxfId="69"/>
+    <tableColumn id="25" xr3:uid="{F5CCC6CB-E5AE-40FD-91C6-4E7CB9F4BA01}" name="비교(V-W)" dataDxfId="68"/>
+    <tableColumn id="8" xr3:uid="{B91B61DE-5B24-4EC8-93F0-0F6AA7D335E4}" name="열1" dataDxfId="67"/>
+    <tableColumn id="26" xr3:uid="{E44140AD-42FF-4A23-851A-478A137EFA9D}" name="열2" dataDxfId="66"/>
+    <tableColumn id="27" xr3:uid="{73E9254A-E008-4F5A-B403-48577589F0F0}" name="열3" dataDxfId="65"/>
+    <tableColumn id="28" xr3:uid="{A4720811-BD5E-45EB-A6A1-04B96A422368}" name="열4" dataDxfId="64"/>
+    <tableColumn id="29" xr3:uid="{9EC4A7AA-2590-44BE-A6D9-3BC81C55515C}" name="열5" dataDxfId="63"/>
+    <tableColumn id="30" xr3:uid="{D9BA0330-49D3-4037-8508-64BF9FC5BD2C}" name="열6" dataDxfId="62"/>
+    <tableColumn id="31" xr3:uid="{AF823A94-60F7-4A09-B1B9-304146CD3013}" name="열7" dataDxfId="61"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10830,9 +10830,7 @@
       <c r="C113" s="11">
         <v>4</v>
       </c>
-      <c r="D113" s="11">
-        <v>15.3</v>
-      </c>
+      <c r="D113" s="11"/>
       <c r="E113" s="11"/>
       <c r="F113" s="11"/>
       <c r="G113" s="11"/>
@@ -12551,16 +12549,16 @@
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="11">
-        <v>17217000</v>
+        <v>17216859</v>
       </c>
       <c r="F5" s="11">
-        <v>1523677000</v>
+        <v>1470968768</v>
       </c>
       <c r="G5" s="11">
-        <v>39209000</v>
+        <v>38505823</v>
       </c>
       <c r="H5" s="11">
-        <v>18286000</v>
+        <v>18285997</v>
       </c>
       <c r="I5" s="11">
         <v>135781662</v>
@@ -12569,34 +12567,34 @@
         <v>75542871</v>
       </c>
       <c r="K5" s="11">
-        <v>81746000</v>
+        <v>79293388.170000002</v>
       </c>
       <c r="L5" s="11">
-        <v>42955000</v>
+        <v>40806894.699999996</v>
       </c>
       <c r="M5" s="11">
-        <v>36248000</v>
+        <v>34436029.399999999</v>
       </c>
       <c r="N5" s="11">
-        <v>771432000</v>
+        <v>787908453</v>
       </c>
       <c r="O5" s="11">
-        <v>242461000</v>
+        <v>247985958</v>
       </c>
       <c r="P5" s="11">
-        <v>11809000</v>
+        <v>12554326</v>
       </c>
       <c r="Q5" s="11">
-        <v>19276000</v>
+        <v>18612436.409000002</v>
       </c>
       <c r="R5" s="11">
-        <v>16581000</v>
+        <v>16580975</v>
       </c>
       <c r="S5" s="11">
-        <v>595000</v>
+        <v>594618</v>
       </c>
       <c r="T5" s="11">
-        <v>2551000</v>
+        <v>3119149</v>
       </c>
       <c r="U5" s="11"/>
       <c r="V5" s="11"/>
@@ -12623,16 +12621,16 @@
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="11">
-        <v>18599000</v>
+        <v>18599423</v>
       </c>
       <c r="F6" s="11">
-        <v>927685000</v>
+        <v>895594382</v>
       </c>
       <c r="G6" s="11">
-        <v>24038000</v>
+        <v>21446203</v>
       </c>
       <c r="H6" s="11">
-        <v>8496000</v>
+        <v>8495852</v>
       </c>
       <c r="I6" s="11">
         <v>134964858</v>
@@ -12641,34 +12639,34 @@
         <v>74733302</v>
       </c>
       <c r="K6" s="11">
-        <v>66933000</v>
+        <v>64925392.18</v>
       </c>
       <c r="L6" s="11">
-        <v>27605000</v>
+        <v>26224796.549999997</v>
       </c>
       <c r="M6" s="11">
-        <v>62208000</v>
+        <v>59097625.649999999</v>
       </c>
       <c r="N6" s="11">
-        <v>657574000</v>
+        <v>651657438</v>
       </c>
       <c r="O6" s="11">
-        <v>252662000</v>
+        <v>252662357</v>
       </c>
       <c r="P6" s="11">
-        <v>11959000</v>
+        <v>11958779</v>
       </c>
       <c r="Q6" s="11">
-        <v>16572000</v>
+        <v>16571668</v>
       </c>
       <c r="R6" s="11">
-        <v>16746000</v>
+        <v>16746017</v>
       </c>
       <c r="S6" s="11">
-        <v>369000</v>
+        <v>368820</v>
       </c>
       <c r="T6" s="11">
-        <v>2208000</v>
+        <v>2208175</v>
       </c>
       <c r="U6" s="11"/>
       <c r="V6" s="11"/>
@@ -12695,16 +12693,16 @@
       </c>
       <c r="D7" s="11"/>
       <c r="E7" s="11">
-        <v>17711000</v>
+        <v>17711412</v>
       </c>
       <c r="F7" s="11">
-        <v>519116000</v>
+        <v>501158031</v>
       </c>
       <c r="G7" s="11">
-        <v>10105000</v>
+        <v>14823593</v>
       </c>
       <c r="H7" s="11">
-        <v>3490000</v>
+        <v>3489735</v>
       </c>
       <c r="I7" s="11">
         <v>123353983</v>
@@ -12713,34 +12711,34 @@
         <v>67271031</v>
       </c>
       <c r="K7" s="11">
-        <v>54037000</v>
+        <v>52416173.240000002</v>
       </c>
       <c r="L7" s="11">
-        <v>20400000</v>
+        <v>19379772</v>
       </c>
       <c r="M7" s="11">
-        <v>135017000</v>
+        <v>128265681.64999999</v>
       </c>
       <c r="N7" s="11">
-        <v>750349000</v>
+        <v>742292521</v>
       </c>
       <c r="O7" s="11">
-        <v>248527000</v>
+        <v>248526852</v>
       </c>
       <c r="P7" s="11">
-        <v>12298000</v>
+        <v>12298069</v>
       </c>
       <c r="Q7" s="11">
-        <v>15369000</v>
+        <v>15368545</v>
       </c>
       <c r="R7" s="11">
-        <v>18373000</v>
+        <v>18372506</v>
       </c>
       <c r="S7" s="11">
-        <v>363000</v>
+        <v>362887</v>
       </c>
       <c r="T7" s="11">
-        <v>1851000</v>
+        <v>1851184</v>
       </c>
       <c r="U7" s="11"/>
       <c r="V7" s="11"/>
@@ -12767,16 +12765,16 @@
       </c>
       <c r="D8" s="11"/>
       <c r="E8" s="11">
-        <v>19091000</v>
+        <v>19091123</v>
       </c>
       <c r="F8" s="11">
-        <v>418058000</v>
+        <v>403596734</v>
       </c>
       <c r="G8" s="11">
-        <v>11095000</v>
+        <v>10599761</v>
       </c>
       <c r="H8" s="11">
-        <v>3299000</v>
+        <v>3298632</v>
       </c>
       <c r="I8" s="11">
         <v>125563814</v>
@@ -12785,34 +12783,34 @@
         <v>57468566</v>
       </c>
       <c r="K8" s="11">
-        <v>47949000</v>
+        <v>46510574.619999997</v>
       </c>
       <c r="L8" s="11">
-        <v>18512000</v>
+        <v>17586718.25</v>
       </c>
       <c r="M8" s="11">
-        <v>198630000</v>
+        <v>188698280.54999998</v>
       </c>
       <c r="N8" s="11">
-        <v>657768000</v>
+        <v>660631062</v>
       </c>
       <c r="O8" s="11">
-        <v>269265000</v>
+        <v>269265592</v>
       </c>
       <c r="P8" s="11">
-        <v>11823000</v>
+        <v>11823297</v>
       </c>
       <c r="Q8" s="11">
-        <v>15700000</v>
+        <v>15699682</v>
       </c>
       <c r="R8" s="11">
-        <v>18986000</v>
+        <v>18986109</v>
       </c>
       <c r="S8" s="11">
-        <v>690000</v>
+        <v>689740</v>
       </c>
       <c r="T8" s="11">
-        <v>1639000</v>
+        <v>1638722</v>
       </c>
       <c r="U8" s="11"/>
       <c r="V8" s="11"/>
@@ -12839,16 +12837,16 @@
       </c>
       <c r="D9" s="11"/>
       <c r="E9" s="11">
-        <v>18931000</v>
+        <v>18930791</v>
       </c>
       <c r="F9" s="11">
-        <v>384838000</v>
+        <v>371525310</v>
       </c>
       <c r="G9" s="11">
-        <v>12532000</v>
+        <v>8599230</v>
       </c>
       <c r="H9" s="11">
-        <v>3562000</v>
+        <v>3561524</v>
       </c>
       <c r="I9" s="11">
         <v>120278427</v>
@@ -12857,34 +12855,34 @@
         <v>51363845</v>
       </c>
       <c r="K9" s="11">
-        <v>44815000</v>
+        <v>43470713.93</v>
       </c>
       <c r="L9" s="11">
-        <v>17022000</v>
+        <v>16171360.75</v>
       </c>
       <c r="M9" s="11">
-        <v>199772000</v>
+        <v>189783439.90000001</v>
       </c>
       <c r="N9" s="11">
-        <v>631899000</v>
+        <v>642022304</v>
       </c>
       <c r="O9" s="11">
-        <v>271293000</v>
+        <v>271292299</v>
       </c>
       <c r="P9" s="11">
-        <v>12115000</v>
+        <v>12114875</v>
       </c>
       <c r="Q9" s="11">
-        <v>15593000</v>
+        <v>15592995</v>
       </c>
       <c r="R9" s="11">
-        <v>18986000</v>
+        <v>18986109</v>
       </c>
       <c r="S9" s="11">
-        <v>669000</v>
+        <v>669286</v>
       </c>
       <c r="T9" s="11">
-        <v>1510000</v>
+        <v>1509793</v>
       </c>
       <c r="U9" s="11"/>
       <c r="V9" s="11"/>
@@ -12911,16 +12909,16 @@
       </c>
       <c r="D10" s="11"/>
       <c r="E10" s="11">
-        <v>17988000</v>
+        <v>17988496</v>
       </c>
       <c r="F10" s="11">
-        <v>439533000</v>
+        <v>424328415</v>
       </c>
       <c r="G10" s="11">
-        <v>10359000</v>
+        <v>11378107</v>
       </c>
       <c r="H10" s="11">
-        <v>2164000</v>
+        <v>2163629</v>
       </c>
       <c r="I10" s="11">
         <v>117034505</v>
@@ -12929,34 +12927,34 @@
         <v>56649876</v>
       </c>
       <c r="K10" s="11">
-        <v>47011000</v>
+        <v>45600617.619999997</v>
       </c>
       <c r="L10" s="11">
-        <v>17253000</v>
+        <v>16389969.049999999</v>
       </c>
       <c r="M10" s="11">
-        <v>134696000</v>
+        <v>127960946.34999999</v>
       </c>
       <c r="N10" s="11">
-        <v>631497000</v>
+        <v>637387464</v>
       </c>
       <c r="O10" s="11">
-        <v>251119000</v>
+        <v>251119226</v>
       </c>
       <c r="P10" s="11">
-        <v>13376000</v>
+        <v>13375616</v>
       </c>
       <c r="Q10" s="11">
-        <v>17966000</v>
+        <v>17966136</v>
       </c>
       <c r="R10" s="11">
-        <v>18374000</v>
+        <v>18374429</v>
       </c>
       <c r="S10" s="11">
-        <v>673000</v>
+        <v>672824</v>
       </c>
       <c r="T10" s="11">
-        <v>1421000</v>
+        <v>1421151</v>
       </c>
       <c r="U10" s="11"/>
       <c r="V10" s="11"/>
@@ -12983,16 +12981,16 @@
       </c>
       <c r="D11" s="11"/>
       <c r="E11" s="11">
-        <v>18391000</v>
+        <v>18390885</v>
       </c>
       <c r="F11" s="11">
-        <v>1114860000</v>
+        <v>1076294093</v>
       </c>
       <c r="G11" s="11">
-        <v>33605000</v>
+        <v>22019989</v>
       </c>
       <c r="H11" s="11">
-        <v>14574000</v>
+        <v>14574059</v>
       </c>
       <c r="I11" s="11">
         <v>125903781</v>
@@ -13001,34 +12999,34 @@
         <v>66826684</v>
       </c>
       <c r="K11" s="11">
-        <v>62915000</v>
+        <v>61027608.199999996</v>
       </c>
       <c r="L11" s="11">
-        <v>26049000</v>
+        <v>24746866.349999998</v>
       </c>
       <c r="M11" s="11">
-        <v>54208000</v>
+        <v>51497963.849999994</v>
       </c>
       <c r="N11" s="11">
-        <v>721544000</v>
+        <v>731451995</v>
       </c>
       <c r="O11" s="11">
-        <v>241436000</v>
+        <v>241435330</v>
       </c>
       <c r="P11" s="11">
-        <v>12701000</v>
+        <v>12701349</v>
       </c>
       <c r="Q11" s="11">
-        <v>21402000</v>
+        <v>21402417</v>
       </c>
       <c r="R11" s="11">
-        <v>17195000</v>
+        <v>17195229</v>
       </c>
       <c r="S11" s="11">
-        <v>507000</v>
+        <v>506689</v>
       </c>
       <c r="T11" s="11">
-        <v>2280000</v>
+        <v>2280309</v>
       </c>
       <c r="U11" s="11"/>
       <c r="V11" s="11"/>
@@ -13055,16 +13053,16 @@
       </c>
       <c r="D12" s="11"/>
       <c r="E12" s="11">
-        <v>19909000</v>
+        <v>19908932</v>
       </c>
       <c r="F12" s="11">
-        <v>2456020000</v>
+        <v>2347287338</v>
       </c>
       <c r="G12" s="11">
-        <v>63460000</v>
+        <v>51623751</v>
       </c>
       <c r="H12" s="11">
-        <v>36432000</v>
+        <v>36431964</v>
       </c>
       <c r="I12" s="11">
         <v>135379992</v>
@@ -13073,34 +13071,34 @@
         <v>77567694</v>
       </c>
       <c r="K12" s="11">
-        <v>89008000</v>
+        <v>86338151.879999995</v>
       </c>
       <c r="L12" s="11">
-        <v>59355000</v>
+        <v>56386819.649999999</v>
       </c>
       <c r="M12" s="11">
-        <v>64107000</v>
+        <v>60901523.649999999</v>
       </c>
       <c r="N12" s="11">
-        <v>743804000</v>
+        <v>753658553</v>
       </c>
       <c r="O12" s="11">
-        <v>243126000</v>
+        <v>243126842</v>
       </c>
       <c r="P12" s="11">
-        <v>11789000</v>
+        <v>11788927</v>
       </c>
       <c r="Q12" s="11">
-        <v>24040000</v>
+        <v>24040091</v>
       </c>
       <c r="R12" s="11">
-        <v>16134000</v>
+        <v>16134336</v>
       </c>
       <c r="S12" s="11">
-        <v>419000</v>
+        <v>418977</v>
       </c>
       <c r="T12" s="11">
-        <v>5107000</v>
+        <v>5107092</v>
       </c>
       <c r="U12" s="11"/>
       <c r="V12" s="11"/>
@@ -13127,16 +13125,16 @@
       </c>
       <c r="D13" s="11"/>
       <c r="E13" s="11">
-        <v>23714000</v>
+        <v>23714408</v>
       </c>
       <c r="F13" s="11">
-        <v>4773207000</v>
+        <v>4574299834</v>
       </c>
       <c r="G13" s="11">
-        <v>90115000</v>
+        <v>81106231</v>
       </c>
       <c r="H13" s="11">
-        <v>66717000</v>
+        <v>66717098</v>
       </c>
       <c r="I13" s="11">
         <v>160740178</v>
@@ -13145,34 +13143,34 @@
         <v>91641290</v>
       </c>
       <c r="K13" s="11">
-        <v>145682000</v>
+        <v>141311709.75</v>
       </c>
       <c r="L13" s="11">
-        <v>125570000</v>
+        <v>119291298.59999999</v>
       </c>
       <c r="M13" s="11">
-        <v>141704000</v>
+        <v>134619184.75</v>
       </c>
       <c r="N13" s="11">
-        <v>826500000</v>
+        <v>836155039</v>
       </c>
       <c r="O13" s="11">
-        <v>246504000</v>
+        <v>246503941</v>
       </c>
       <c r="P13" s="11">
-        <v>13012000</v>
+        <v>13011733</v>
       </c>
       <c r="Q13" s="11">
-        <v>25654000</v>
+        <v>25653600</v>
       </c>
       <c r="R13" s="11">
-        <v>26022000</v>
+        <v>26022017</v>
       </c>
       <c r="S13" s="11">
-        <v>659000</v>
+        <v>659027</v>
       </c>
       <c r="T13" s="11">
-        <v>10018000</v>
+        <v>10018415</v>
       </c>
       <c r="U13" s="11"/>
       <c r="V13" s="11"/>

--- a/공급량실적_계획_실적_MJ.xlsx
+++ b/공급량실적_계획_실적_MJ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\실천사업계획\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9CB0E25D-12F1-4D0D-8D9D-7140B8CE1EA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38519795-80D0-49E3-BBEB-496A08495938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="공급량_실적" sheetId="1" r:id="rId1"/>
@@ -214,7 +214,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -224,6 +224,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -245,7 +251,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -294,12 +300,593 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="95">
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="맑은 고딕"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="맑은 고딕"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="맑은 고딕"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="맑은 고딕"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="맑은 고딕"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="맑은 고딕"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="맑은 고딕"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="맑은 고딕"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1336,584 +1923,6 @@
         <scheme val="minor"/>
       </font>
     </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1928,35 +1937,35 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="A1:Y121" totalsRowShown="0" headerRowDxfId="60" dataDxfId="59">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="A1:Y121" totalsRowShown="0" headerRowDxfId="94" dataDxfId="93">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="날짜" dataDxfId="58"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="연" dataDxfId="57"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="월" dataDxfId="56"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="평균기온" dataDxfId="55"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="취사용" dataDxfId="54"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="개별난방용" dataDxfId="53"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="중앙난방용" dataDxfId="52"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="자가열전용" dataDxfId="51"/>
-    <tableColumn id="8" xr3:uid="{F6CD84DD-4BD1-4B4F-8F66-408F637C64C3}" name="영업용" dataDxfId="50"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="일반용(1)" dataDxfId="49"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="일반용(2)" dataDxfId="48"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="업무난방용" dataDxfId="47"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="냉난방용" dataDxfId="46"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="산업용" dataDxfId="45"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="수송용(CNG)" dataDxfId="44"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="수송용(BIO)" dataDxfId="43"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="열병합용" dataDxfId="42"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="연료전지용" dataDxfId="41"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="열전용설비용(주택외)" dataDxfId="40"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="주한미군" dataDxfId="39"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="일반용1(영업)" dataDxfId="38"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="일반용1(업무)" dataDxfId="37"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="총공급량" dataDxfId="36"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="총합계" dataDxfId="35">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="날짜" dataDxfId="92"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="연" dataDxfId="91"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="월" dataDxfId="90"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="평균기온" dataDxfId="89"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="취사용" dataDxfId="88"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="개별난방용" dataDxfId="87"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="중앙난방용" dataDxfId="86"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="자가열전용" dataDxfId="85"/>
+    <tableColumn id="8" xr3:uid="{F6CD84DD-4BD1-4B4F-8F66-408F637C64C3}" name="영업용" dataDxfId="84"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="일반용(1)" dataDxfId="83"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="일반용(2)" dataDxfId="82"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="업무난방용" dataDxfId="81"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="냉난방용" dataDxfId="80"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="산업용" dataDxfId="79"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="수송용(CNG)" dataDxfId="78"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="수송용(BIO)" dataDxfId="77"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="열병합용" dataDxfId="76"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="연료전지용" dataDxfId="75"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="열전용설비용(주택외)" dataDxfId="74"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="주한미군" dataDxfId="73"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="일반용1(영업)" dataDxfId="72"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="일반용1(업무)" dataDxfId="71"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="총공급량" dataDxfId="70"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="총합계" dataDxfId="69">
       <calculatedColumnFormula>SUM(표1[[#This Row],[취사용]:[주한미군]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="비교(V-W)" dataDxfId="34">
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="비교(V-W)" dataDxfId="68">
       <calculatedColumnFormula>W2-X2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1965,80 +1974,80 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2C1F99CF-9391-4872-B93D-50B931598DD3}" name="표1_3" displayName="표1_3" ref="A1:AF13" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2C1F99CF-9391-4872-B93D-50B931598DD3}" name="표1_3" displayName="표1_3" ref="A1:AF13" totalsRowShown="0" headerRowDxfId="67" dataDxfId="66">
   <tableColumns count="32">
-    <tableColumn id="1" xr3:uid="{19685FD4-89CE-478F-94BA-7A4B1E721FD4}" name="날짜" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{E31CA521-8EDF-4B60-95F2-6D99A2A44422}" name="연" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{0E1A3862-691A-4EE3-BC9F-15442CFF7BF6}" name="월" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{70EF9B81-BEFB-4CBB-822B-4CF1F1061D51}" name="평균기온" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{FC97C89C-B827-4EAB-8DAD-DBE4EB83293B}" name="취사용" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{6EB58682-1AB0-402D-B1B5-64D7A3FEE7DC}" name="개별난방용" dataDxfId="26"/>
-    <tableColumn id="6" xr3:uid="{9B5B2C66-64AC-4900-AA35-A909EB1F3ADB}" name="중앙난방용" dataDxfId="25"/>
-    <tableColumn id="19" xr3:uid="{BB6DF2E3-2587-479E-A2F3-005ADFBAD580}" name="자가열전용" dataDxfId="24"/>
-    <tableColumn id="32" xr3:uid="{19247A41-B716-45A1-89D6-71493825C64A}" name="영업용" dataDxfId="23"/>
-    <tableColumn id="9" xr3:uid="{AE3DB5EB-C7E4-47AD-9093-9ED129869DB2}" name="일반용(1)" dataDxfId="22"/>
-    <tableColumn id="12" xr3:uid="{8B4AF52F-6164-471B-AE99-CC06D0BB14EF}" name="일반용(2)" dataDxfId="21"/>
-    <tableColumn id="13" xr3:uid="{371738D5-71AD-4443-9E50-C5CBFA38DD53}" name="업무난방용" dataDxfId="20"/>
-    <tableColumn id="16" xr3:uid="{900065B7-DB40-43BE-8FF7-E75CA356AC45}" name="냉난방용" dataDxfId="19"/>
-    <tableColumn id="15" xr3:uid="{DEBF6157-B4E3-448F-B30C-6BA984C794F5}" name="산업용" dataDxfId="18"/>
-    <tableColumn id="22" xr3:uid="{110C96B1-CEF5-460E-976A-E31DDA355398}" name="수송용(CNG)" dataDxfId="17"/>
-    <tableColumn id="21" xr3:uid="{06CF64A6-4CFF-491D-A557-FA4850CF0868}" name="수송용(BIO)" dataDxfId="16"/>
-    <tableColumn id="17" xr3:uid="{325D94CD-83AF-4821-8554-98F27BA03A89}" name="열병합용" dataDxfId="15"/>
-    <tableColumn id="18" xr3:uid="{6CE1C920-1D02-4ED1-B172-01F6E3A7A08C}" name="연료전지용" dataDxfId="14"/>
-    <tableColumn id="20" xr3:uid="{0B7A0B86-42DA-48FF-AD28-7D4F4C7EE8B6}" name="열전용설비용(주택외)" dataDxfId="13"/>
-    <tableColumn id="14" xr3:uid="{66ED3A2C-2F9A-4DC1-B2E1-96B11BA082CD}" name="주한미군" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{8576E086-9957-4A83-B3D2-E6372750D253}" name="일반용1(영업)" dataDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{AC7AEF69-FC00-4021-A757-1F6CB56D86E9}" name="일반용1(업무)" dataDxfId="10"/>
-    <tableColumn id="23" xr3:uid="{0A863EFD-5ACB-4216-A172-3D5E489B9B61}" name="총공급량" dataDxfId="9"/>
-    <tableColumn id="24" xr3:uid="{3F3F5052-4199-490C-8994-5E9CF83BDE9D}" name="총합계" dataDxfId="8"/>
-    <tableColumn id="25" xr3:uid="{F3502AAC-AAE0-469B-8FF7-545D8F24C683}" name="비교(V-W)" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{FA0345C9-D72C-4A34-84B0-7B3673E66B4B}" name="열1" dataDxfId="6"/>
-    <tableColumn id="26" xr3:uid="{924F492C-4495-498A-A3CC-8AB7A213EB49}" name="열2" dataDxfId="5"/>
-    <tableColumn id="27" xr3:uid="{7D1ACE6F-EB3E-490F-A815-30511D277AEB}" name="열3" dataDxfId="4"/>
-    <tableColumn id="28" xr3:uid="{D28E208B-F040-4AE4-ACFF-E094E4F8E7A7}" name="열4" dataDxfId="3"/>
-    <tableColumn id="29" xr3:uid="{186D4369-AF71-4A71-9851-5932B907782C}" name="열5" dataDxfId="2"/>
-    <tableColumn id="30" xr3:uid="{896603AA-8674-4905-8A79-3984C733419F}" name="열6" dataDxfId="1"/>
-    <tableColumn id="31" xr3:uid="{27B69BAA-C555-4945-8804-7D4A8F0D00B9}" name="열7" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{19685FD4-89CE-478F-94BA-7A4B1E721FD4}" name="날짜" dataDxfId="65"/>
+    <tableColumn id="2" xr3:uid="{E31CA521-8EDF-4B60-95F2-6D99A2A44422}" name="연" dataDxfId="64"/>
+    <tableColumn id="3" xr3:uid="{0E1A3862-691A-4EE3-BC9F-15442CFF7BF6}" name="월" dataDxfId="63"/>
+    <tableColumn id="4" xr3:uid="{70EF9B81-BEFB-4CBB-822B-4CF1F1061D51}" name="평균기온" dataDxfId="62"/>
+    <tableColumn id="7" xr3:uid="{FC97C89C-B827-4EAB-8DAD-DBE4EB83293B}" name="취사용" dataDxfId="61"/>
+    <tableColumn id="5" xr3:uid="{6EB58682-1AB0-402D-B1B5-64D7A3FEE7DC}" name="개별난방용" dataDxfId="60"/>
+    <tableColumn id="6" xr3:uid="{9B5B2C66-64AC-4900-AA35-A909EB1F3ADB}" name="중앙난방용" dataDxfId="59"/>
+    <tableColumn id="19" xr3:uid="{BB6DF2E3-2587-479E-A2F3-005ADFBAD580}" name="자가열전용" dataDxfId="58"/>
+    <tableColumn id="32" xr3:uid="{19247A41-B716-45A1-89D6-71493825C64A}" name="영업용" dataDxfId="57"/>
+    <tableColumn id="9" xr3:uid="{AE3DB5EB-C7E4-47AD-9093-9ED129869DB2}" name="일반용(1)" dataDxfId="56"/>
+    <tableColumn id="12" xr3:uid="{8B4AF52F-6164-471B-AE99-CC06D0BB14EF}" name="일반용(2)" dataDxfId="55"/>
+    <tableColumn id="13" xr3:uid="{371738D5-71AD-4443-9E50-C5CBFA38DD53}" name="업무난방용" dataDxfId="54"/>
+    <tableColumn id="16" xr3:uid="{900065B7-DB40-43BE-8FF7-E75CA356AC45}" name="냉난방용" dataDxfId="53"/>
+    <tableColumn id="15" xr3:uid="{DEBF6157-B4E3-448F-B30C-6BA984C794F5}" name="산업용" dataDxfId="52"/>
+    <tableColumn id="22" xr3:uid="{110C96B1-CEF5-460E-976A-E31DDA355398}" name="수송용(CNG)" dataDxfId="51"/>
+    <tableColumn id="21" xr3:uid="{06CF64A6-4CFF-491D-A557-FA4850CF0868}" name="수송용(BIO)" dataDxfId="50"/>
+    <tableColumn id="17" xr3:uid="{325D94CD-83AF-4821-8554-98F27BA03A89}" name="열병합용" dataDxfId="49"/>
+    <tableColumn id="18" xr3:uid="{6CE1C920-1D02-4ED1-B172-01F6E3A7A08C}" name="연료전지용" dataDxfId="48"/>
+    <tableColumn id="20" xr3:uid="{0B7A0B86-42DA-48FF-AD28-7D4F4C7EE8B6}" name="열전용설비용(주택외)" dataDxfId="47"/>
+    <tableColumn id="14" xr3:uid="{66ED3A2C-2F9A-4DC1-B2E1-96B11BA082CD}" name="주한미군" dataDxfId="46"/>
+    <tableColumn id="11" xr3:uid="{8576E086-9957-4A83-B3D2-E6372750D253}" name="일반용1(영업)" dataDxfId="45"/>
+    <tableColumn id="10" xr3:uid="{AC7AEF69-FC00-4021-A757-1F6CB56D86E9}" name="일반용1(업무)" dataDxfId="44"/>
+    <tableColumn id="23" xr3:uid="{0A863EFD-5ACB-4216-A172-3D5E489B9B61}" name="총공급량" dataDxfId="43"/>
+    <tableColumn id="24" xr3:uid="{3F3F5052-4199-490C-8994-5E9CF83BDE9D}" name="총합계" dataDxfId="42"/>
+    <tableColumn id="25" xr3:uid="{F3502AAC-AAE0-469B-8FF7-545D8F24C683}" name="비교(V-W)" dataDxfId="41"/>
+    <tableColumn id="8" xr3:uid="{FA0345C9-D72C-4A34-84B0-7B3673E66B4B}" name="열1" dataDxfId="40"/>
+    <tableColumn id="26" xr3:uid="{924F492C-4495-498A-A3CC-8AB7A213EB49}" name="열2" dataDxfId="39"/>
+    <tableColumn id="27" xr3:uid="{7D1ACE6F-EB3E-490F-A815-30511D277AEB}" name="열3" dataDxfId="38"/>
+    <tableColumn id="28" xr3:uid="{D28E208B-F040-4AE4-ACFF-E094E4F8E7A7}" name="열4" dataDxfId="37"/>
+    <tableColumn id="29" xr3:uid="{186D4369-AF71-4A71-9851-5932B907782C}" name="열5" dataDxfId="36"/>
+    <tableColumn id="30" xr3:uid="{896603AA-8674-4905-8A79-3984C733419F}" name="열6" dataDxfId="35"/>
+    <tableColumn id="31" xr3:uid="{27B69BAA-C555-4945-8804-7D4A8F0D00B9}" name="열7" dataDxfId="34"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{EC6B23D4-390C-404E-AE69-455A5E70B9EF}" name="표1_34" displayName="표1_34" ref="A1:AF13" totalsRowShown="0" headerRowDxfId="94" dataDxfId="93">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{EC6B23D4-390C-404E-AE69-455A5E70B9EF}" name="표1_34" displayName="표1_34" ref="A1:AF13" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
   <tableColumns count="32">
-    <tableColumn id="1" xr3:uid="{32BFE98C-3743-4F2A-B0AA-77B0B6019DD7}" name="날짜" dataDxfId="92"/>
-    <tableColumn id="2" xr3:uid="{51E25201-28D0-4E8C-BEC7-0E3F4D5F3645}" name="연" dataDxfId="91"/>
-    <tableColumn id="3" xr3:uid="{80FFE0A8-C94B-40E9-B01D-932A55EF6766}" name="월" dataDxfId="90"/>
-    <tableColumn id="4" xr3:uid="{B563055E-F2FB-42BE-BA0E-E08593191708}" name="평균기온" dataDxfId="89"/>
-    <tableColumn id="7" xr3:uid="{EC02A3A1-631C-42EF-85AF-A8B79A8D9F9B}" name="취사용" dataDxfId="88"/>
-    <tableColumn id="5" xr3:uid="{86073F88-2F80-4462-BB87-5B8A54551B6A}" name="개별난방용" dataDxfId="87"/>
-    <tableColumn id="6" xr3:uid="{139EC257-82FA-481B-9F18-60ADA6EB50D3}" name="중앙난방용" dataDxfId="86"/>
-    <tableColumn id="19" xr3:uid="{408C0C4D-65A0-4DC3-A85C-EF1BC48BFA6F}" name="자가열전용" dataDxfId="85"/>
-    <tableColumn id="32" xr3:uid="{F08BABB7-87AA-4744-89E7-228FA9D35660}" name="영업용" dataDxfId="84"/>
-    <tableColumn id="9" xr3:uid="{D46D49CA-B262-4926-A5D1-6DDB23F119D4}" name="일반용(1)" dataDxfId="83"/>
-    <tableColumn id="12" xr3:uid="{861B7867-2B87-4609-A7B2-0963E4807DC3}" name="일반용(2)" dataDxfId="82"/>
-    <tableColumn id="13" xr3:uid="{14954B61-A6C3-4B22-BB69-82FCB6C6800D}" name="업무난방용" dataDxfId="81"/>
-    <tableColumn id="16" xr3:uid="{79636BBA-3A6E-42BA-959F-C2875D1EB9BF}" name="냉난방용" dataDxfId="80"/>
-    <tableColumn id="15" xr3:uid="{9E90082E-3CE5-4697-A0B1-A041913653D4}" name="산업용" dataDxfId="79"/>
-    <tableColumn id="22" xr3:uid="{15EC95E6-8587-482D-BF25-3DEDC8762C1E}" name="수송용(CNG)" dataDxfId="78"/>
-    <tableColumn id="21" xr3:uid="{0578ED32-2CDD-4E0D-B4BF-9D8549DC6AE8}" name="수송용(BIO)" dataDxfId="77"/>
-    <tableColumn id="17" xr3:uid="{A2C46C4C-5370-461A-AEAE-B18F07625F71}" name="열병합용" dataDxfId="76"/>
-    <tableColumn id="18" xr3:uid="{DF7D0596-2D46-4696-A139-30735FD75FF7}" name="연료전지용" dataDxfId="75"/>
-    <tableColumn id="20" xr3:uid="{BE9174ED-E86A-4C72-8087-5A38B6314769}" name="열전용설비용(주택외)" dataDxfId="74"/>
-    <tableColumn id="14" xr3:uid="{094C3E7A-F02F-42B7-A5BF-D2A7A7C7AD81}" name="주한미군" dataDxfId="73"/>
-    <tableColumn id="11" xr3:uid="{7BEB8593-2810-4E4B-9386-DAA32EE4C15D}" name="일반용1(영업)" dataDxfId="72"/>
-    <tableColumn id="10" xr3:uid="{35165667-3CFF-4452-B99D-526A70B3D7E9}" name="일반용1(업무)" dataDxfId="71"/>
-    <tableColumn id="23" xr3:uid="{B2866D34-3868-4FBB-9E30-43CEB374404E}" name="총공급량" dataDxfId="70"/>
-    <tableColumn id="24" xr3:uid="{894A25E9-5A19-4242-9DB5-639CFBC374F1}" name="총합계" dataDxfId="69"/>
-    <tableColumn id="25" xr3:uid="{F5CCC6CB-E5AE-40FD-91C6-4E7CB9F4BA01}" name="비교(V-W)" dataDxfId="68"/>
-    <tableColumn id="8" xr3:uid="{B91B61DE-5B24-4EC8-93F0-0F6AA7D335E4}" name="열1" dataDxfId="67"/>
-    <tableColumn id="26" xr3:uid="{E44140AD-42FF-4A23-851A-478A137EFA9D}" name="열2" dataDxfId="66"/>
-    <tableColumn id="27" xr3:uid="{73E9254A-E008-4F5A-B403-48577589F0F0}" name="열3" dataDxfId="65"/>
-    <tableColumn id="28" xr3:uid="{A4720811-BD5E-45EB-A6A1-04B96A422368}" name="열4" dataDxfId="64"/>
-    <tableColumn id="29" xr3:uid="{9EC4A7AA-2590-44BE-A6D9-3BC81C55515C}" name="열5" dataDxfId="63"/>
-    <tableColumn id="30" xr3:uid="{D9BA0330-49D3-4037-8508-64BF9FC5BD2C}" name="열6" dataDxfId="62"/>
-    <tableColumn id="31" xr3:uid="{AF823A94-60F7-4A09-B1B9-304146CD3013}" name="열7" dataDxfId="61"/>
+    <tableColumn id="1" xr3:uid="{32BFE98C-3743-4F2A-B0AA-77B0B6019DD7}" name="날짜" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{51E25201-28D0-4E8C-BEC7-0E3F4D5F3645}" name="연" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{80FFE0A8-C94B-40E9-B01D-932A55EF6766}" name="월" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{B563055E-F2FB-42BE-BA0E-E08593191708}" name="평균기온" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{EC02A3A1-631C-42EF-85AF-A8B79A8D9F9B}" name="취사용" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{86073F88-2F80-4462-BB87-5B8A54551B6A}" name="개별난방용" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{139EC257-82FA-481B-9F18-60ADA6EB50D3}" name="중앙난방용" dataDxfId="25"/>
+    <tableColumn id="19" xr3:uid="{408C0C4D-65A0-4DC3-A85C-EF1BC48BFA6F}" name="자가열전용" dataDxfId="24"/>
+    <tableColumn id="32" xr3:uid="{F08BABB7-87AA-4744-89E7-228FA9D35660}" name="영업용" dataDxfId="23"/>
+    <tableColumn id="9" xr3:uid="{D46D49CA-B262-4926-A5D1-6DDB23F119D4}" name="일반용(1)" dataDxfId="22"/>
+    <tableColumn id="12" xr3:uid="{861B7867-2B87-4609-A7B2-0963E4807DC3}" name="일반용(2)" dataDxfId="21"/>
+    <tableColumn id="13" xr3:uid="{14954B61-A6C3-4B22-BB69-82FCB6C6800D}" name="업무난방용" dataDxfId="20"/>
+    <tableColumn id="16" xr3:uid="{79636BBA-3A6E-42BA-959F-C2875D1EB9BF}" name="냉난방용" dataDxfId="19"/>
+    <tableColumn id="15" xr3:uid="{9E90082E-3CE5-4697-A0B1-A041913653D4}" name="산업용" dataDxfId="18"/>
+    <tableColumn id="22" xr3:uid="{15EC95E6-8587-482D-BF25-3DEDC8762C1E}" name="수송용(CNG)" dataDxfId="17"/>
+    <tableColumn id="21" xr3:uid="{0578ED32-2CDD-4E0D-B4BF-9D8549DC6AE8}" name="수송용(BIO)" dataDxfId="16"/>
+    <tableColumn id="17" xr3:uid="{A2C46C4C-5370-461A-AEAE-B18F07625F71}" name="열병합용" dataDxfId="15"/>
+    <tableColumn id="18" xr3:uid="{DF7D0596-2D46-4696-A139-30735FD75FF7}" name="연료전지용" dataDxfId="14"/>
+    <tableColumn id="20" xr3:uid="{BE9174ED-E86A-4C72-8087-5A38B6314769}" name="열전용설비용(주택외)" dataDxfId="13"/>
+    <tableColumn id="14" xr3:uid="{094C3E7A-F02F-42B7-A5BF-D2A7A7C7AD81}" name="주한미군" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{7BEB8593-2810-4E4B-9386-DAA32EE4C15D}" name="일반용1(영업)" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{35165667-3CFF-4452-B99D-526A70B3D7E9}" name="일반용1(업무)" dataDxfId="10"/>
+    <tableColumn id="23" xr3:uid="{B2866D34-3868-4FBB-9E30-43CEB374404E}" name="총공급량" dataDxfId="9"/>
+    <tableColumn id="24" xr3:uid="{894A25E9-5A19-4242-9DB5-639CFBC374F1}" name="총합계" dataDxfId="8"/>
+    <tableColumn id="25" xr3:uid="{F5CCC6CB-E5AE-40FD-91C6-4E7CB9F4BA01}" name="비교(V-W)" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{B91B61DE-5B24-4EC8-93F0-0F6AA7D335E4}" name="열1" dataDxfId="6"/>
+    <tableColumn id="26" xr3:uid="{E44140AD-42FF-4A23-851A-478A137EFA9D}" name="열2" dataDxfId="5"/>
+    <tableColumn id="27" xr3:uid="{73E9254A-E008-4F5A-B403-48577589F0F0}" name="열3" dataDxfId="4"/>
+    <tableColumn id="28" xr3:uid="{A4720811-BD5E-45EB-A6A1-04B96A422368}" name="열4" dataDxfId="3"/>
+    <tableColumn id="29" xr3:uid="{9EC4A7AA-2590-44BE-A6D9-3BC81C55515C}" name="열5" dataDxfId="2"/>
+    <tableColumn id="30" xr3:uid="{D9BA0330-49D3-4037-8508-64BF9FC5BD2C}" name="열6" dataDxfId="1"/>
+    <tableColumn id="31" xr3:uid="{AF823A94-60F7-4A09-B1B9-304146CD3013}" name="열7" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12332,53 +12341,53 @@
         <v>1</v>
       </c>
       <c r="D2" s="11"/>
-      <c r="E2" s="11">
-        <v>23770000</v>
-      </c>
-      <c r="F2" s="11">
-        <v>5340234000</v>
-      </c>
-      <c r="G2" s="11">
-        <v>95380000</v>
-      </c>
-      <c r="H2" s="11">
-        <v>76533000</v>
-      </c>
-      <c r="I2" s="11">
-        <v>153579898</v>
-      </c>
-      <c r="J2" s="11">
-        <v>74281768</v>
-      </c>
-      <c r="K2" s="11">
-        <v>158987000</v>
-      </c>
-      <c r="L2" s="11">
-        <v>142347000</v>
-      </c>
-      <c r="M2" s="11">
-        <v>170895000</v>
-      </c>
-      <c r="N2" s="11">
-        <v>943307000</v>
-      </c>
-      <c r="O2" s="11">
-        <v>235978000</v>
-      </c>
-      <c r="P2" s="11">
-        <v>11401000</v>
-      </c>
-      <c r="Q2" s="11">
-        <v>25497000</v>
-      </c>
-      <c r="R2" s="11">
-        <v>18988000</v>
-      </c>
-      <c r="S2" s="11">
-        <v>802000</v>
-      </c>
-      <c r="T2" s="11">
-        <v>12384000</v>
+      <c r="E2" s="16">
+        <v>24299870</v>
+      </c>
+      <c r="F2" s="16">
+        <v>5488720626</v>
+      </c>
+      <c r="G2" s="16">
+        <v>99525221</v>
+      </c>
+      <c r="H2" s="16">
+        <v>77757917</v>
+      </c>
+      <c r="I2" s="16">
+        <v>159747657</v>
+      </c>
+      <c r="J2" s="16">
+        <v>80776567</v>
+      </c>
+      <c r="K2" s="16">
+        <v>164563755</v>
+      </c>
+      <c r="L2" s="16">
+        <v>154915949</v>
+      </c>
+      <c r="M2" s="16">
+        <v>181364249</v>
+      </c>
+      <c r="N2" s="16">
+        <v>922530985</v>
+      </c>
+      <c r="O2" s="16">
+        <v>255559765</v>
+      </c>
+      <c r="P2" s="16">
+        <v>12328825</v>
+      </c>
+      <c r="Q2" s="16">
+        <v>26951288.645</v>
+      </c>
+      <c r="R2" s="16">
+        <v>17582210</v>
+      </c>
+      <c r="S2" s="16">
+        <v>1180658</v>
+      </c>
+      <c r="T2" s="16">
+        <v>11421045</v>
       </c>
       <c r="U2" s="11"/>
       <c r="V2" s="11"/>
@@ -12404,53 +12413,53 @@
         <v>2</v>
       </c>
       <c r="D3" s="11"/>
-      <c r="E3" s="11">
-        <v>20834000</v>
-      </c>
-      <c r="F3" s="11">
-        <v>3896619000</v>
-      </c>
-      <c r="G3" s="11">
-        <v>85625000</v>
-      </c>
-      <c r="H3" s="11">
-        <v>65741000</v>
-      </c>
-      <c r="I3" s="11">
-        <v>145568468</v>
-      </c>
-      <c r="J3" s="11">
-        <v>70552207</v>
-      </c>
-      <c r="K3" s="11">
-        <v>143546000</v>
-      </c>
-      <c r="L3" s="11">
-        <v>122647000</v>
-      </c>
-      <c r="M3" s="11">
-        <v>145668000</v>
-      </c>
-      <c r="N3" s="11">
-        <v>727930000</v>
-      </c>
-      <c r="O3" s="11">
-        <v>228596000</v>
-      </c>
-      <c r="P3" s="11">
-        <v>9929000</v>
-      </c>
-      <c r="Q3" s="11">
-        <v>22770000</v>
-      </c>
-      <c r="R3" s="11">
-        <v>15360000</v>
-      </c>
-      <c r="S3" s="11">
-        <v>774000</v>
-      </c>
-      <c r="T3" s="11">
-        <v>10167000</v>
+      <c r="E3" s="16">
+        <v>20244839</v>
+      </c>
+      <c r="F3" s="16">
+        <v>3954941256</v>
+      </c>
+      <c r="G3" s="16">
+        <v>81166486</v>
+      </c>
+      <c r="H3" s="16">
+        <v>56988098</v>
+      </c>
+      <c r="I3" s="16">
+        <v>139080755</v>
+      </c>
+      <c r="J3" s="16">
+        <v>66368831</v>
+      </c>
+      <c r="K3" s="16">
+        <v>133527806</v>
+      </c>
+      <c r="L3" s="16">
+        <v>115810392</v>
+      </c>
+      <c r="M3" s="16">
+        <v>131009593</v>
+      </c>
+      <c r="N3" s="16">
+        <v>732838698</v>
+      </c>
+      <c r="O3" s="16">
+        <v>225660762</v>
+      </c>
+      <c r="P3" s="16">
+        <v>11843864</v>
+      </c>
+      <c r="Q3" s="16">
+        <v>24125862.190000001</v>
+      </c>
+      <c r="R3" s="16">
+        <v>17502574</v>
+      </c>
+      <c r="S3" s="16">
+        <v>1025235</v>
+      </c>
+      <c r="T3" s="16">
+        <v>9307650</v>
       </c>
       <c r="U3" s="11"/>
       <c r="V3" s="11"/>
@@ -12476,53 +12485,53 @@
         <v>3</v>
       </c>
       <c r="D4" s="11"/>
-      <c r="E4" s="11">
-        <v>23140000</v>
-      </c>
-      <c r="F4" s="11">
-        <v>2940781000</v>
-      </c>
-      <c r="G4" s="11">
-        <v>59741000</v>
-      </c>
-      <c r="H4" s="11">
-        <v>37262000</v>
-      </c>
-      <c r="I4" s="11">
-        <v>146489418</v>
-      </c>
-      <c r="J4" s="11">
-        <v>88277540</v>
-      </c>
-      <c r="K4" s="11">
-        <v>119576000</v>
-      </c>
-      <c r="L4" s="11">
-        <v>89804000</v>
-      </c>
-      <c r="M4" s="11">
-        <v>88597000</v>
-      </c>
-      <c r="N4" s="11">
-        <v>812951000</v>
-      </c>
-      <c r="O4" s="11">
-        <v>243127000</v>
-      </c>
-      <c r="P4" s="11">
-        <v>11820000</v>
-      </c>
-      <c r="Q4" s="11">
-        <v>24121000</v>
-      </c>
-      <c r="R4" s="11">
-        <v>16746000</v>
-      </c>
-      <c r="S4" s="11">
-        <v>639000</v>
-      </c>
-      <c r="T4" s="11">
-        <v>6935000</v>
+      <c r="E4" s="16">
+        <v>21179905</v>
+      </c>
+      <c r="F4" s="16">
+        <v>2884258887</v>
+      </c>
+      <c r="G4" s="16">
+        <v>70951238</v>
+      </c>
+      <c r="H4" s="16">
+        <v>39997670</v>
+      </c>
+      <c r="I4" s="16">
+        <v>149061939</v>
+      </c>
+      <c r="J4" s="16">
+        <v>87907988</v>
+      </c>
+      <c r="K4" s="16">
+        <v>118157095</v>
+      </c>
+      <c r="L4" s="16">
+        <v>86736495</v>
+      </c>
+      <c r="M4" s="16">
+        <v>78432678</v>
+      </c>
+      <c r="N4" s="16">
+        <v>824414065</v>
+      </c>
+      <c r="O4" s="16">
+        <v>248778924</v>
+      </c>
+      <c r="P4" s="16">
+        <v>12806117</v>
+      </c>
+      <c r="Q4" s="16">
+        <v>22681313.199999999</v>
+      </c>
+      <c r="R4" s="16">
+        <v>19638888</v>
+      </c>
+      <c r="S4" s="16">
+        <v>776191</v>
+      </c>
+      <c r="T4" s="16">
+        <v>7565713</v>
       </c>
       <c r="U4" s="11"/>
       <c r="V4" s="11"/>
@@ -12771,7 +12780,7 @@
         <v>403596734</v>
       </c>
       <c r="G8" s="11">
-        <v>10599761</v>
+        <v>9480098.6270000003</v>
       </c>
       <c r="H8" s="11">
         <v>3298632</v>
@@ -12843,7 +12852,7 @@
         <v>371525310</v>
       </c>
       <c r="G9" s="11">
-        <v>8599230</v>
+        <v>7705230.7879999997</v>
       </c>
       <c r="H9" s="11">
         <v>3561524</v>
@@ -12915,7 +12924,7 @@
         <v>424328415</v>
       </c>
       <c r="G10" s="11">
-        <v>11378107</v>
+        <v>10337147.964</v>
       </c>
       <c r="H10" s="11">
         <v>2163629</v>
@@ -12987,7 +12996,7 @@
         <v>1076294093</v>
       </c>
       <c r="G11" s="11">
-        <v>22019989</v>
+        <v>19794040.274999999</v>
       </c>
       <c r="H11" s="11">
         <v>14574059</v>
@@ -13059,7 +13068,7 @@
         <v>2347287338</v>
       </c>
       <c r="G12" s="11">
-        <v>51623751</v>
+        <v>46552131.399999999</v>
       </c>
       <c r="H12" s="11">
         <v>36431964</v>
@@ -13131,7 +13140,7 @@
         <v>4574299834</v>
       </c>
       <c r="G13" s="11">
-        <v>81106231</v>
+        <v>73125901.263999999</v>
       </c>
       <c r="H13" s="11">
         <v>66717098</v>

--- a/공급량실적_계획_실적_MJ.xlsx
+++ b/공급량실적_계획_실적_MJ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\실천사업계획\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{38519795-80D0-49E3-BBEB-496A08495938}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EC3D4F1-C01D-4385-BB27-1F8F63ED97DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="3900" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="공급량_실적" sheetId="1" r:id="rId1"/>
@@ -309,584 +309,6 @@
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="95">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <family val="3"/>
-        <charset val="129"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-      <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
     <dxf>
       <font>
         <b val="0"/>
@@ -1923,6 +1345,584 @@
         <scheme val="minor"/>
       </font>
     </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="맑은 고딕"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="맑은 고딕"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="맑은 고딕"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="맑은 고딕"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="맑은 고딕"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="맑은 고딕"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="맑은 고딕"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="맑은 고딕"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -1937,35 +1937,35 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="A1:Y121" totalsRowShown="0" headerRowDxfId="94" dataDxfId="93">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="A1:Y121" totalsRowShown="0" headerRowDxfId="60" dataDxfId="59">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="날짜" dataDxfId="92"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="연" dataDxfId="91"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="월" dataDxfId="90"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="평균기온" dataDxfId="89"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="취사용" dataDxfId="88"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="개별난방용" dataDxfId="87"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="중앙난방용" dataDxfId="86"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="자가열전용" dataDxfId="85"/>
-    <tableColumn id="8" xr3:uid="{F6CD84DD-4BD1-4B4F-8F66-408F637C64C3}" name="영업용" dataDxfId="84"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="일반용(1)" dataDxfId="83"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="일반용(2)" dataDxfId="82"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="업무난방용" dataDxfId="81"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="냉난방용" dataDxfId="80"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="산업용" dataDxfId="79"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="수송용(CNG)" dataDxfId="78"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="수송용(BIO)" dataDxfId="77"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="열병합용" dataDxfId="76"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="연료전지용" dataDxfId="75"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="열전용설비용(주택외)" dataDxfId="74"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="주한미군" dataDxfId="73"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="일반용1(영업)" dataDxfId="72"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="일반용1(업무)" dataDxfId="71"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="총공급량" dataDxfId="70"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="총합계" dataDxfId="69">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="날짜" dataDxfId="58"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="연" dataDxfId="57"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="월" dataDxfId="56"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="평균기온" dataDxfId="55"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="취사용" dataDxfId="54"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="개별난방용" dataDxfId="53"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="중앙난방용" dataDxfId="52"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="자가열전용" dataDxfId="51"/>
+    <tableColumn id="8" xr3:uid="{F6CD84DD-4BD1-4B4F-8F66-408F637C64C3}" name="영업용" dataDxfId="50"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="일반용(1)" dataDxfId="49"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="일반용(2)" dataDxfId="48"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="업무난방용" dataDxfId="47"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="냉난방용" dataDxfId="46"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="산업용" dataDxfId="45"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="수송용(CNG)" dataDxfId="44"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="수송용(BIO)" dataDxfId="43"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="열병합용" dataDxfId="42"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="연료전지용" dataDxfId="41"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="열전용설비용(주택외)" dataDxfId="40"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="주한미군" dataDxfId="39"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="일반용1(영업)" dataDxfId="38"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="일반용1(업무)" dataDxfId="37"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="총공급량" dataDxfId="36"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="총합계" dataDxfId="35">
       <calculatedColumnFormula>SUM(표1[[#This Row],[취사용]:[주한미군]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="비교(V-W)" dataDxfId="68">
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="비교(V-W)" dataDxfId="34">
       <calculatedColumnFormula>W2-X2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1974,80 +1974,80 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2C1F99CF-9391-4872-B93D-50B931598DD3}" name="표1_3" displayName="표1_3" ref="A1:AF13" totalsRowShown="0" headerRowDxfId="67" dataDxfId="66">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2C1F99CF-9391-4872-B93D-50B931598DD3}" name="표1_3" displayName="표1_3" ref="A1:AF13" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
   <tableColumns count="32">
-    <tableColumn id="1" xr3:uid="{19685FD4-89CE-478F-94BA-7A4B1E721FD4}" name="날짜" dataDxfId="65"/>
-    <tableColumn id="2" xr3:uid="{E31CA521-8EDF-4B60-95F2-6D99A2A44422}" name="연" dataDxfId="64"/>
-    <tableColumn id="3" xr3:uid="{0E1A3862-691A-4EE3-BC9F-15442CFF7BF6}" name="월" dataDxfId="63"/>
-    <tableColumn id="4" xr3:uid="{70EF9B81-BEFB-4CBB-822B-4CF1F1061D51}" name="평균기온" dataDxfId="62"/>
-    <tableColumn id="7" xr3:uid="{FC97C89C-B827-4EAB-8DAD-DBE4EB83293B}" name="취사용" dataDxfId="61"/>
-    <tableColumn id="5" xr3:uid="{6EB58682-1AB0-402D-B1B5-64D7A3FEE7DC}" name="개별난방용" dataDxfId="60"/>
-    <tableColumn id="6" xr3:uid="{9B5B2C66-64AC-4900-AA35-A909EB1F3ADB}" name="중앙난방용" dataDxfId="59"/>
-    <tableColumn id="19" xr3:uid="{BB6DF2E3-2587-479E-A2F3-005ADFBAD580}" name="자가열전용" dataDxfId="58"/>
-    <tableColumn id="32" xr3:uid="{19247A41-B716-45A1-89D6-71493825C64A}" name="영업용" dataDxfId="57"/>
-    <tableColumn id="9" xr3:uid="{AE3DB5EB-C7E4-47AD-9093-9ED129869DB2}" name="일반용(1)" dataDxfId="56"/>
-    <tableColumn id="12" xr3:uid="{8B4AF52F-6164-471B-AE99-CC06D0BB14EF}" name="일반용(2)" dataDxfId="55"/>
-    <tableColumn id="13" xr3:uid="{371738D5-71AD-4443-9E50-C5CBFA38DD53}" name="업무난방용" dataDxfId="54"/>
-    <tableColumn id="16" xr3:uid="{900065B7-DB40-43BE-8FF7-E75CA356AC45}" name="냉난방용" dataDxfId="53"/>
-    <tableColumn id="15" xr3:uid="{DEBF6157-B4E3-448F-B30C-6BA984C794F5}" name="산업용" dataDxfId="52"/>
-    <tableColumn id="22" xr3:uid="{110C96B1-CEF5-460E-976A-E31DDA355398}" name="수송용(CNG)" dataDxfId="51"/>
-    <tableColumn id="21" xr3:uid="{06CF64A6-4CFF-491D-A557-FA4850CF0868}" name="수송용(BIO)" dataDxfId="50"/>
-    <tableColumn id="17" xr3:uid="{325D94CD-83AF-4821-8554-98F27BA03A89}" name="열병합용" dataDxfId="49"/>
-    <tableColumn id="18" xr3:uid="{6CE1C920-1D02-4ED1-B172-01F6E3A7A08C}" name="연료전지용" dataDxfId="48"/>
-    <tableColumn id="20" xr3:uid="{0B7A0B86-42DA-48FF-AD28-7D4F4C7EE8B6}" name="열전용설비용(주택외)" dataDxfId="47"/>
-    <tableColumn id="14" xr3:uid="{66ED3A2C-2F9A-4DC1-B2E1-96B11BA082CD}" name="주한미군" dataDxfId="46"/>
-    <tableColumn id="11" xr3:uid="{8576E086-9957-4A83-B3D2-E6372750D253}" name="일반용1(영업)" dataDxfId="45"/>
-    <tableColumn id="10" xr3:uid="{AC7AEF69-FC00-4021-A757-1F6CB56D86E9}" name="일반용1(업무)" dataDxfId="44"/>
-    <tableColumn id="23" xr3:uid="{0A863EFD-5ACB-4216-A172-3D5E489B9B61}" name="총공급량" dataDxfId="43"/>
-    <tableColumn id="24" xr3:uid="{3F3F5052-4199-490C-8994-5E9CF83BDE9D}" name="총합계" dataDxfId="42"/>
-    <tableColumn id="25" xr3:uid="{F3502AAC-AAE0-469B-8FF7-545D8F24C683}" name="비교(V-W)" dataDxfId="41"/>
-    <tableColumn id="8" xr3:uid="{FA0345C9-D72C-4A34-84B0-7B3673E66B4B}" name="열1" dataDxfId="40"/>
-    <tableColumn id="26" xr3:uid="{924F492C-4495-498A-A3CC-8AB7A213EB49}" name="열2" dataDxfId="39"/>
-    <tableColumn id="27" xr3:uid="{7D1ACE6F-EB3E-490F-A815-30511D277AEB}" name="열3" dataDxfId="38"/>
-    <tableColumn id="28" xr3:uid="{D28E208B-F040-4AE4-ACFF-E094E4F8E7A7}" name="열4" dataDxfId="37"/>
-    <tableColumn id="29" xr3:uid="{186D4369-AF71-4A71-9851-5932B907782C}" name="열5" dataDxfId="36"/>
-    <tableColumn id="30" xr3:uid="{896603AA-8674-4905-8A79-3984C733419F}" name="열6" dataDxfId="35"/>
-    <tableColumn id="31" xr3:uid="{27B69BAA-C555-4945-8804-7D4A8F0D00B9}" name="열7" dataDxfId="34"/>
+    <tableColumn id="1" xr3:uid="{19685FD4-89CE-478F-94BA-7A4B1E721FD4}" name="날짜" dataDxfId="31"/>
+    <tableColumn id="2" xr3:uid="{E31CA521-8EDF-4B60-95F2-6D99A2A44422}" name="연" dataDxfId="30"/>
+    <tableColumn id="3" xr3:uid="{0E1A3862-691A-4EE3-BC9F-15442CFF7BF6}" name="월" dataDxfId="29"/>
+    <tableColumn id="4" xr3:uid="{70EF9B81-BEFB-4CBB-822B-4CF1F1061D51}" name="평균기온" dataDxfId="28"/>
+    <tableColumn id="7" xr3:uid="{FC97C89C-B827-4EAB-8DAD-DBE4EB83293B}" name="취사용" dataDxfId="27"/>
+    <tableColumn id="5" xr3:uid="{6EB58682-1AB0-402D-B1B5-64D7A3FEE7DC}" name="개별난방용" dataDxfId="26"/>
+    <tableColumn id="6" xr3:uid="{9B5B2C66-64AC-4900-AA35-A909EB1F3ADB}" name="중앙난방용" dataDxfId="25"/>
+    <tableColumn id="19" xr3:uid="{BB6DF2E3-2587-479E-A2F3-005ADFBAD580}" name="자가열전용" dataDxfId="24"/>
+    <tableColumn id="32" xr3:uid="{19247A41-B716-45A1-89D6-71493825C64A}" name="영업용" dataDxfId="23"/>
+    <tableColumn id="9" xr3:uid="{AE3DB5EB-C7E4-47AD-9093-9ED129869DB2}" name="일반용(1)" dataDxfId="22"/>
+    <tableColumn id="12" xr3:uid="{8B4AF52F-6164-471B-AE99-CC06D0BB14EF}" name="일반용(2)" dataDxfId="21"/>
+    <tableColumn id="13" xr3:uid="{371738D5-71AD-4443-9E50-C5CBFA38DD53}" name="업무난방용" dataDxfId="20"/>
+    <tableColumn id="16" xr3:uid="{900065B7-DB40-43BE-8FF7-E75CA356AC45}" name="냉난방용" dataDxfId="19"/>
+    <tableColumn id="15" xr3:uid="{DEBF6157-B4E3-448F-B30C-6BA984C794F5}" name="산업용" dataDxfId="18"/>
+    <tableColumn id="22" xr3:uid="{110C96B1-CEF5-460E-976A-E31DDA355398}" name="수송용(CNG)" dataDxfId="17"/>
+    <tableColumn id="21" xr3:uid="{06CF64A6-4CFF-491D-A557-FA4850CF0868}" name="수송용(BIO)" dataDxfId="16"/>
+    <tableColumn id="17" xr3:uid="{325D94CD-83AF-4821-8554-98F27BA03A89}" name="열병합용" dataDxfId="15"/>
+    <tableColumn id="18" xr3:uid="{6CE1C920-1D02-4ED1-B172-01F6E3A7A08C}" name="연료전지용" dataDxfId="14"/>
+    <tableColumn id="20" xr3:uid="{0B7A0B86-42DA-48FF-AD28-7D4F4C7EE8B6}" name="열전용설비용(주택외)" dataDxfId="13"/>
+    <tableColumn id="14" xr3:uid="{66ED3A2C-2F9A-4DC1-B2E1-96B11BA082CD}" name="주한미군" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{8576E086-9957-4A83-B3D2-E6372750D253}" name="일반용1(영업)" dataDxfId="11"/>
+    <tableColumn id="10" xr3:uid="{AC7AEF69-FC00-4021-A757-1F6CB56D86E9}" name="일반용1(업무)" dataDxfId="10"/>
+    <tableColumn id="23" xr3:uid="{0A863EFD-5ACB-4216-A172-3D5E489B9B61}" name="총공급량" dataDxfId="9"/>
+    <tableColumn id="24" xr3:uid="{3F3F5052-4199-490C-8994-5E9CF83BDE9D}" name="총합계" dataDxfId="8"/>
+    <tableColumn id="25" xr3:uid="{F3502AAC-AAE0-469B-8FF7-545D8F24C683}" name="비교(V-W)" dataDxfId="7"/>
+    <tableColumn id="8" xr3:uid="{FA0345C9-D72C-4A34-84B0-7B3673E66B4B}" name="열1" dataDxfId="6"/>
+    <tableColumn id="26" xr3:uid="{924F492C-4495-498A-A3CC-8AB7A213EB49}" name="열2" dataDxfId="5"/>
+    <tableColumn id="27" xr3:uid="{7D1ACE6F-EB3E-490F-A815-30511D277AEB}" name="열3" dataDxfId="4"/>
+    <tableColumn id="28" xr3:uid="{D28E208B-F040-4AE4-ACFF-E094E4F8E7A7}" name="열4" dataDxfId="3"/>
+    <tableColumn id="29" xr3:uid="{186D4369-AF71-4A71-9851-5932B907782C}" name="열5" dataDxfId="2"/>
+    <tableColumn id="30" xr3:uid="{896603AA-8674-4905-8A79-3984C733419F}" name="열6" dataDxfId="1"/>
+    <tableColumn id="31" xr3:uid="{27B69BAA-C555-4945-8804-7D4A8F0D00B9}" name="열7" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{EC6B23D4-390C-404E-AE69-455A5E70B9EF}" name="표1_34" displayName="표1_34" ref="A1:AF13" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{EC6B23D4-390C-404E-AE69-455A5E70B9EF}" name="표1_34" displayName="표1_34" ref="A1:AF13" totalsRowShown="0" headerRowDxfId="94" dataDxfId="93">
   <tableColumns count="32">
-    <tableColumn id="1" xr3:uid="{32BFE98C-3743-4F2A-B0AA-77B0B6019DD7}" name="날짜" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{51E25201-28D0-4E8C-BEC7-0E3F4D5F3645}" name="연" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{80FFE0A8-C94B-40E9-B01D-932A55EF6766}" name="월" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{B563055E-F2FB-42BE-BA0E-E08593191708}" name="평균기온" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{EC02A3A1-631C-42EF-85AF-A8B79A8D9F9B}" name="취사용" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{86073F88-2F80-4462-BB87-5B8A54551B6A}" name="개별난방용" dataDxfId="26"/>
-    <tableColumn id="6" xr3:uid="{139EC257-82FA-481B-9F18-60ADA6EB50D3}" name="중앙난방용" dataDxfId="25"/>
-    <tableColumn id="19" xr3:uid="{408C0C4D-65A0-4DC3-A85C-EF1BC48BFA6F}" name="자가열전용" dataDxfId="24"/>
-    <tableColumn id="32" xr3:uid="{F08BABB7-87AA-4744-89E7-228FA9D35660}" name="영업용" dataDxfId="23"/>
-    <tableColumn id="9" xr3:uid="{D46D49CA-B262-4926-A5D1-6DDB23F119D4}" name="일반용(1)" dataDxfId="22"/>
-    <tableColumn id="12" xr3:uid="{861B7867-2B87-4609-A7B2-0963E4807DC3}" name="일반용(2)" dataDxfId="21"/>
-    <tableColumn id="13" xr3:uid="{14954B61-A6C3-4B22-BB69-82FCB6C6800D}" name="업무난방용" dataDxfId="20"/>
-    <tableColumn id="16" xr3:uid="{79636BBA-3A6E-42BA-959F-C2875D1EB9BF}" name="냉난방용" dataDxfId="19"/>
-    <tableColumn id="15" xr3:uid="{9E90082E-3CE5-4697-A0B1-A041913653D4}" name="산업용" dataDxfId="18"/>
-    <tableColumn id="22" xr3:uid="{15EC95E6-8587-482D-BF25-3DEDC8762C1E}" name="수송용(CNG)" dataDxfId="17"/>
-    <tableColumn id="21" xr3:uid="{0578ED32-2CDD-4E0D-B4BF-9D8549DC6AE8}" name="수송용(BIO)" dataDxfId="16"/>
-    <tableColumn id="17" xr3:uid="{A2C46C4C-5370-461A-AEAE-B18F07625F71}" name="열병합용" dataDxfId="15"/>
-    <tableColumn id="18" xr3:uid="{DF7D0596-2D46-4696-A139-30735FD75FF7}" name="연료전지용" dataDxfId="14"/>
-    <tableColumn id="20" xr3:uid="{BE9174ED-E86A-4C72-8087-5A38B6314769}" name="열전용설비용(주택외)" dataDxfId="13"/>
-    <tableColumn id="14" xr3:uid="{094C3E7A-F02F-42B7-A5BF-D2A7A7C7AD81}" name="주한미군" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{7BEB8593-2810-4E4B-9386-DAA32EE4C15D}" name="일반용1(영업)" dataDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{35165667-3CFF-4452-B99D-526A70B3D7E9}" name="일반용1(업무)" dataDxfId="10"/>
-    <tableColumn id="23" xr3:uid="{B2866D34-3868-4FBB-9E30-43CEB374404E}" name="총공급량" dataDxfId="9"/>
-    <tableColumn id="24" xr3:uid="{894A25E9-5A19-4242-9DB5-639CFBC374F1}" name="총합계" dataDxfId="8"/>
-    <tableColumn id="25" xr3:uid="{F5CCC6CB-E5AE-40FD-91C6-4E7CB9F4BA01}" name="비교(V-W)" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{B91B61DE-5B24-4EC8-93F0-0F6AA7D335E4}" name="열1" dataDxfId="6"/>
-    <tableColumn id="26" xr3:uid="{E44140AD-42FF-4A23-851A-478A137EFA9D}" name="열2" dataDxfId="5"/>
-    <tableColumn id="27" xr3:uid="{73E9254A-E008-4F5A-B403-48577589F0F0}" name="열3" dataDxfId="4"/>
-    <tableColumn id="28" xr3:uid="{A4720811-BD5E-45EB-A6A1-04B96A422368}" name="열4" dataDxfId="3"/>
-    <tableColumn id="29" xr3:uid="{9EC4A7AA-2590-44BE-A6D9-3BC81C55515C}" name="열5" dataDxfId="2"/>
-    <tableColumn id="30" xr3:uid="{D9BA0330-49D3-4037-8508-64BF9FC5BD2C}" name="열6" dataDxfId="1"/>
-    <tableColumn id="31" xr3:uid="{AF823A94-60F7-4A09-B1B9-304146CD3013}" name="열7" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{32BFE98C-3743-4F2A-B0AA-77B0B6019DD7}" name="날짜" dataDxfId="92"/>
+    <tableColumn id="2" xr3:uid="{51E25201-28D0-4E8C-BEC7-0E3F4D5F3645}" name="연" dataDxfId="91"/>
+    <tableColumn id="3" xr3:uid="{80FFE0A8-C94B-40E9-B01D-932A55EF6766}" name="월" dataDxfId="90"/>
+    <tableColumn id="4" xr3:uid="{B563055E-F2FB-42BE-BA0E-E08593191708}" name="평균기온" dataDxfId="89"/>
+    <tableColumn id="7" xr3:uid="{EC02A3A1-631C-42EF-85AF-A8B79A8D9F9B}" name="취사용" dataDxfId="88"/>
+    <tableColumn id="5" xr3:uid="{86073F88-2F80-4462-BB87-5B8A54551B6A}" name="개별난방용" dataDxfId="87"/>
+    <tableColumn id="6" xr3:uid="{139EC257-82FA-481B-9F18-60ADA6EB50D3}" name="중앙난방용" dataDxfId="86"/>
+    <tableColumn id="19" xr3:uid="{408C0C4D-65A0-4DC3-A85C-EF1BC48BFA6F}" name="자가열전용" dataDxfId="85"/>
+    <tableColumn id="32" xr3:uid="{F08BABB7-87AA-4744-89E7-228FA9D35660}" name="영업용" dataDxfId="84"/>
+    <tableColumn id="9" xr3:uid="{D46D49CA-B262-4926-A5D1-6DDB23F119D4}" name="일반용(1)" dataDxfId="83"/>
+    <tableColumn id="12" xr3:uid="{861B7867-2B87-4609-A7B2-0963E4807DC3}" name="일반용(2)" dataDxfId="82"/>
+    <tableColumn id="13" xr3:uid="{14954B61-A6C3-4B22-BB69-82FCB6C6800D}" name="업무난방용" dataDxfId="81"/>
+    <tableColumn id="16" xr3:uid="{79636BBA-3A6E-42BA-959F-C2875D1EB9BF}" name="냉난방용" dataDxfId="80"/>
+    <tableColumn id="15" xr3:uid="{9E90082E-3CE5-4697-A0B1-A041913653D4}" name="산업용" dataDxfId="79"/>
+    <tableColumn id="22" xr3:uid="{15EC95E6-8587-482D-BF25-3DEDC8762C1E}" name="수송용(CNG)" dataDxfId="78"/>
+    <tableColumn id="21" xr3:uid="{0578ED32-2CDD-4E0D-B4BF-9D8549DC6AE8}" name="수송용(BIO)" dataDxfId="77"/>
+    <tableColumn id="17" xr3:uid="{A2C46C4C-5370-461A-AEAE-B18F07625F71}" name="열병합용" dataDxfId="76"/>
+    <tableColumn id="18" xr3:uid="{DF7D0596-2D46-4696-A139-30735FD75FF7}" name="연료전지용" dataDxfId="75"/>
+    <tableColumn id="20" xr3:uid="{BE9174ED-E86A-4C72-8087-5A38B6314769}" name="열전용설비용(주택외)" dataDxfId="74"/>
+    <tableColumn id="14" xr3:uid="{094C3E7A-F02F-42B7-A5BF-D2A7A7C7AD81}" name="주한미군" dataDxfId="73"/>
+    <tableColumn id="11" xr3:uid="{7BEB8593-2810-4E4B-9386-DAA32EE4C15D}" name="일반용1(영업)" dataDxfId="72"/>
+    <tableColumn id="10" xr3:uid="{35165667-3CFF-4452-B99D-526A70B3D7E9}" name="일반용1(업무)" dataDxfId="71"/>
+    <tableColumn id="23" xr3:uid="{B2866D34-3868-4FBB-9E30-43CEB374404E}" name="총공급량" dataDxfId="70"/>
+    <tableColumn id="24" xr3:uid="{894A25E9-5A19-4242-9DB5-639CFBC374F1}" name="총합계" dataDxfId="69"/>
+    <tableColumn id="25" xr3:uid="{F5CCC6CB-E5AE-40FD-91C6-4E7CB9F4BA01}" name="비교(V-W)" dataDxfId="68"/>
+    <tableColumn id="8" xr3:uid="{B91B61DE-5B24-4EC8-93F0-0F6AA7D335E4}" name="열1" dataDxfId="67"/>
+    <tableColumn id="26" xr3:uid="{E44140AD-42FF-4A23-851A-478A137EFA9D}" name="열2" dataDxfId="66"/>
+    <tableColumn id="27" xr3:uid="{73E9254A-E008-4F5A-B403-48577589F0F0}" name="열3" dataDxfId="65"/>
+    <tableColumn id="28" xr3:uid="{A4720811-BD5E-45EB-A6A1-04B96A422368}" name="열4" dataDxfId="64"/>
+    <tableColumn id="29" xr3:uid="{9EC4A7AA-2590-44BE-A6D9-3BC81C55515C}" name="열5" dataDxfId="63"/>
+    <tableColumn id="30" xr3:uid="{D9BA0330-49D3-4037-8508-64BF9FC5BD2C}" name="열6" dataDxfId="62"/>
+    <tableColumn id="31" xr3:uid="{AF823A94-60F7-4A09-B1B9-304146CD3013}" name="열7" dataDxfId="61"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12561,7 +12561,7 @@
         <v>17216859</v>
       </c>
       <c r="F5" s="11">
-        <v>1470968768</v>
+        <v>1429905580.4920909</v>
       </c>
       <c r="G5" s="11">
         <v>38505823</v>
@@ -12633,7 +12633,7 @@
         <v>18599423</v>
       </c>
       <c r="F6" s="11">
-        <v>895594382</v>
+        <v>870593198.98114467</v>
       </c>
       <c r="G6" s="11">
         <v>21446203</v>
@@ -12705,7 +12705,7 @@
         <v>17711412</v>
       </c>
       <c r="F7" s="11">
-        <v>501158031</v>
+        <v>487167831.34020805</v>
       </c>
       <c r="G7" s="11">
         <v>14823593</v>
@@ -12777,7 +12777,7 @@
         <v>19091123</v>
       </c>
       <c r="F8" s="11">
-        <v>403596734</v>
+        <v>392330031.12423694</v>
       </c>
       <c r="G8" s="11">
         <v>9480098.6270000003</v>
@@ -12849,7 +12849,7 @@
         <v>18930791</v>
       </c>
       <c r="F9" s="11">
-        <v>371525310</v>
+        <v>361153904.40035677</v>
       </c>
       <c r="G9" s="11">
         <v>7705230.7879999997</v>
@@ -12921,7 +12921,7 @@
         <v>17988496</v>
       </c>
       <c r="F10" s="11">
-        <v>424328415</v>
+        <v>412482971.1851669</v>
       </c>
       <c r="G10" s="11">
         <v>10337147.964</v>
@@ -12993,7 +12993,7 @@
         <v>18390885</v>
       </c>
       <c r="F11" s="11">
-        <v>1076294093</v>
+        <v>1046248542.4740975</v>
       </c>
       <c r="G11" s="11">
         <v>19794040.274999999</v>
@@ -13065,7 +13065,7 @@
         <v>19908932</v>
       </c>
       <c r="F12" s="11">
-        <v>2347287338</v>
+        <v>2304870023.3452382</v>
       </c>
       <c r="G12" s="11">
         <v>46552131.399999999</v>
@@ -13137,7 +13137,7 @@
         <v>23714408</v>
       </c>
       <c r="F13" s="11">
-        <v>4574299834</v>
+        <v>4479450855.6574593</v>
       </c>
       <c r="G13" s="11">
         <v>73125901.263999999</v>

--- a/공급량실적_계획_실적_MJ.xlsx
+++ b/공급량실적_계획_실적_MJ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\실천사업계획\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1EC3D4F1-C01D-4385-BB27-1F8F63ED97DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16642AD2-B00D-4A8B-820F-84A9756D891B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="3900" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="공급량_실적" sheetId="1" r:id="rId1"/>
@@ -12657,7 +12657,7 @@
         <v>59097625.649999999</v>
       </c>
       <c r="N6" s="11">
-        <v>651657438</v>
+        <v>645328748</v>
       </c>
       <c r="O6" s="11">
         <v>252662357</v>
@@ -12729,7 +12729,7 @@
         <v>128265681.64999999</v>
       </c>
       <c r="N7" s="11">
-        <v>742292521</v>
+        <v>735070923</v>
       </c>
       <c r="O7" s="11">
         <v>248526852</v>
@@ -12801,7 +12801,7 @@
         <v>188698280.54999998</v>
       </c>
       <c r="N8" s="11">
-        <v>660631062</v>
+        <v>654300510</v>
       </c>
       <c r="O8" s="11">
         <v>269265592</v>
@@ -12873,7 +12873,7 @@
         <v>189783439.90000001</v>
       </c>
       <c r="N9" s="11">
-        <v>642022304</v>
+        <v>635940722</v>
       </c>
       <c r="O9" s="11">
         <v>271292299</v>
@@ -12945,7 +12945,7 @@
         <v>127960946.34999999</v>
       </c>
       <c r="N10" s="11">
-        <v>637387464</v>
+        <v>631309778</v>
       </c>
       <c r="O10" s="11">
         <v>251119226</v>
@@ -13017,7 +13017,7 @@
         <v>51497963.849999994</v>
       </c>
       <c r="N11" s="11">
-        <v>731451995</v>
+        <v>722390553</v>
       </c>
       <c r="O11" s="11">
         <v>241435330</v>
@@ -13089,7 +13089,7 @@
         <v>60901523.649999999</v>
       </c>
       <c r="N12" s="11">
-        <v>753658553</v>
+        <v>744382861</v>
       </c>
       <c r="O12" s="11">
         <v>243126842</v>
@@ -13161,7 +13161,7 @@
         <v>134619184.75</v>
       </c>
       <c r="N13" s="11">
-        <v>836155039</v>
+        <v>826083486</v>
       </c>
       <c r="O13" s="11">
         <v>246503941</v>

--- a/공급량실적_계획_실적_MJ.xlsx
+++ b/공급량실적_계획_실적_MJ.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\실천사업계획\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16642AD2-B00D-4A8B-820F-84A9756D891B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D1D476-8FB0-4416-8BFA-57AADEE77369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="공급량_실적" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="33">
   <si>
     <t>날짜</t>
   </si>
@@ -308,7 +308,7 @@
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="95">
+  <dxfs count="83">
     <dxf>
       <font>
         <b val="0"/>
@@ -1357,206 +1357,6 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="9"/>
-        <color rgb="FF000000"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
         <color theme="1"/>
         <name val="맑은 고딕"/>
         <scheme val="minor"/>
@@ -2014,40 +1814,28 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{EC6B23D4-390C-404E-AE69-455A5E70B9EF}" name="표1_34" displayName="표1_34" ref="A1:AF13" totalsRowShown="0" headerRowDxfId="94" dataDxfId="93">
-  <tableColumns count="32">
-    <tableColumn id="1" xr3:uid="{32BFE98C-3743-4F2A-B0AA-77B0B6019DD7}" name="날짜" dataDxfId="92"/>
-    <tableColumn id="2" xr3:uid="{51E25201-28D0-4E8C-BEC7-0E3F4D5F3645}" name="연" dataDxfId="91"/>
-    <tableColumn id="3" xr3:uid="{80FFE0A8-C94B-40E9-B01D-932A55EF6766}" name="월" dataDxfId="90"/>
-    <tableColumn id="4" xr3:uid="{B563055E-F2FB-42BE-BA0E-E08593191708}" name="평균기온" dataDxfId="89"/>
-    <tableColumn id="7" xr3:uid="{EC02A3A1-631C-42EF-85AF-A8B79A8D9F9B}" name="취사용" dataDxfId="88"/>
-    <tableColumn id="5" xr3:uid="{86073F88-2F80-4462-BB87-5B8A54551B6A}" name="개별난방용" dataDxfId="87"/>
-    <tableColumn id="6" xr3:uid="{139EC257-82FA-481B-9F18-60ADA6EB50D3}" name="중앙난방용" dataDxfId="86"/>
-    <tableColumn id="19" xr3:uid="{408C0C4D-65A0-4DC3-A85C-EF1BC48BFA6F}" name="자가열전용" dataDxfId="85"/>
-    <tableColumn id="32" xr3:uid="{F08BABB7-87AA-4744-89E7-228FA9D35660}" name="영업용" dataDxfId="84"/>
-    <tableColumn id="9" xr3:uid="{D46D49CA-B262-4926-A5D1-6DDB23F119D4}" name="일반용(1)" dataDxfId="83"/>
-    <tableColumn id="12" xr3:uid="{861B7867-2B87-4609-A7B2-0963E4807DC3}" name="일반용(2)" dataDxfId="82"/>
-    <tableColumn id="13" xr3:uid="{14954B61-A6C3-4B22-BB69-82FCB6C6800D}" name="업무난방용" dataDxfId="81"/>
-    <tableColumn id="16" xr3:uid="{79636BBA-3A6E-42BA-959F-C2875D1EB9BF}" name="냉난방용" dataDxfId="80"/>
-    <tableColumn id="15" xr3:uid="{9E90082E-3CE5-4697-A0B1-A041913653D4}" name="산업용" dataDxfId="79"/>
-    <tableColumn id="22" xr3:uid="{15EC95E6-8587-482D-BF25-3DEDC8762C1E}" name="수송용(CNG)" dataDxfId="78"/>
-    <tableColumn id="21" xr3:uid="{0578ED32-2CDD-4E0D-B4BF-9D8549DC6AE8}" name="수송용(BIO)" dataDxfId="77"/>
-    <tableColumn id="17" xr3:uid="{A2C46C4C-5370-461A-AEAE-B18F07625F71}" name="열병합용" dataDxfId="76"/>
-    <tableColumn id="18" xr3:uid="{DF7D0596-2D46-4696-A139-30735FD75FF7}" name="연료전지용" dataDxfId="75"/>
-    <tableColumn id="20" xr3:uid="{BE9174ED-E86A-4C72-8087-5A38B6314769}" name="열전용설비용(주택외)" dataDxfId="74"/>
-    <tableColumn id="14" xr3:uid="{094C3E7A-F02F-42B7-A5BF-D2A7A7C7AD81}" name="주한미군" dataDxfId="73"/>
-    <tableColumn id="11" xr3:uid="{7BEB8593-2810-4E4B-9386-DAA32EE4C15D}" name="일반용1(영업)" dataDxfId="72"/>
-    <tableColumn id="10" xr3:uid="{35165667-3CFF-4452-B99D-526A70B3D7E9}" name="일반용1(업무)" dataDxfId="71"/>
-    <tableColumn id="23" xr3:uid="{B2866D34-3868-4FBB-9E30-43CEB374404E}" name="총공급량" dataDxfId="70"/>
-    <tableColumn id="24" xr3:uid="{894A25E9-5A19-4242-9DB5-639CFBC374F1}" name="총합계" dataDxfId="69"/>
-    <tableColumn id="25" xr3:uid="{F5CCC6CB-E5AE-40FD-91C6-4E7CB9F4BA01}" name="비교(V-W)" dataDxfId="68"/>
-    <tableColumn id="8" xr3:uid="{B91B61DE-5B24-4EC8-93F0-0F6AA7D335E4}" name="열1" dataDxfId="67"/>
-    <tableColumn id="26" xr3:uid="{E44140AD-42FF-4A23-851A-478A137EFA9D}" name="열2" dataDxfId="66"/>
-    <tableColumn id="27" xr3:uid="{73E9254A-E008-4F5A-B403-48577589F0F0}" name="열3" dataDxfId="65"/>
-    <tableColumn id="28" xr3:uid="{A4720811-BD5E-45EB-A6A1-04B96A422368}" name="열4" dataDxfId="64"/>
-    <tableColumn id="29" xr3:uid="{9EC4A7AA-2590-44BE-A6D9-3BC81C55515C}" name="열5" dataDxfId="63"/>
-    <tableColumn id="30" xr3:uid="{D9BA0330-49D3-4037-8508-64BF9FC5BD2C}" name="열6" dataDxfId="62"/>
-    <tableColumn id="31" xr3:uid="{AF823A94-60F7-4A09-B1B9-304146CD3013}" name="열7" dataDxfId="61"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{EC6B23D4-390C-404E-AE69-455A5E70B9EF}" name="표1_34" displayName="표1_34" ref="A1:T13" totalsRowShown="0" headerRowDxfId="82" dataDxfId="81">
+  <tableColumns count="20">
+    <tableColumn id="1" xr3:uid="{32BFE98C-3743-4F2A-B0AA-77B0B6019DD7}" name="날짜" dataDxfId="80"/>
+    <tableColumn id="2" xr3:uid="{51E25201-28D0-4E8C-BEC7-0E3F4D5F3645}" name="연" dataDxfId="79"/>
+    <tableColumn id="3" xr3:uid="{80FFE0A8-C94B-40E9-B01D-932A55EF6766}" name="월" dataDxfId="78"/>
+    <tableColumn id="4" xr3:uid="{B563055E-F2FB-42BE-BA0E-E08593191708}" name="평균기온" dataDxfId="77"/>
+    <tableColumn id="7" xr3:uid="{EC02A3A1-631C-42EF-85AF-A8B79A8D9F9B}" name="취사용" dataDxfId="76"/>
+    <tableColumn id="5" xr3:uid="{86073F88-2F80-4462-BB87-5B8A54551B6A}" name="개별난방용" dataDxfId="75"/>
+    <tableColumn id="6" xr3:uid="{139EC257-82FA-481B-9F18-60ADA6EB50D3}" name="중앙난방용" dataDxfId="74"/>
+    <tableColumn id="19" xr3:uid="{408C0C4D-65A0-4DC3-A85C-EF1BC48BFA6F}" name="자가열전용" dataDxfId="73"/>
+    <tableColumn id="32" xr3:uid="{F08BABB7-87AA-4744-89E7-228FA9D35660}" name="영업용" dataDxfId="72"/>
+    <tableColumn id="9" xr3:uid="{D46D49CA-B262-4926-A5D1-6DDB23F119D4}" name="일반용(1)" dataDxfId="71"/>
+    <tableColumn id="12" xr3:uid="{861B7867-2B87-4609-A7B2-0963E4807DC3}" name="일반용(2)" dataDxfId="70"/>
+    <tableColumn id="13" xr3:uid="{14954B61-A6C3-4B22-BB69-82FCB6C6800D}" name="업무난방용" dataDxfId="69"/>
+    <tableColumn id="16" xr3:uid="{79636BBA-3A6E-42BA-959F-C2875D1EB9BF}" name="냉난방용" dataDxfId="68"/>
+    <tableColumn id="15" xr3:uid="{9E90082E-3CE5-4697-A0B1-A041913653D4}" name="산업용" dataDxfId="67"/>
+    <tableColumn id="22" xr3:uid="{15EC95E6-8587-482D-BF25-3DEDC8762C1E}" name="수송용(CNG)" dataDxfId="66"/>
+    <tableColumn id="21" xr3:uid="{0578ED32-2CDD-4E0D-B4BF-9D8549DC6AE8}" name="수송용(BIO)" dataDxfId="65"/>
+    <tableColumn id="17" xr3:uid="{A2C46C4C-5370-461A-AEAE-B18F07625F71}" name="열병합용" dataDxfId="64"/>
+    <tableColumn id="18" xr3:uid="{DF7D0596-2D46-4696-A139-30735FD75FF7}" name="연료전지용" dataDxfId="63"/>
+    <tableColumn id="20" xr3:uid="{BE9174ED-E86A-4C72-8087-5A38B6314769}" name="열전용설비용(주택외)" dataDxfId="62"/>
+    <tableColumn id="14" xr3:uid="{094C3E7A-F02F-42B7-A5BF-D2A7A7C7AD81}" name="주한미군" dataDxfId="61"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -12199,7 +11987,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F931A64-B197-4832-BE2D-4772CDA5D9CA}">
-  <dimension ref="A1:AJ13"/>
+  <dimension ref="A1:X13"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.75" style="3" bestFit="1" customWidth="1"/>
@@ -12218,20 +12006,12 @@
     <col min="16" max="16" width="12.875" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="10.5" bestFit="1" customWidth="1"/>
     <col min="19" max="20" width="11.5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="13" bestFit="1" customWidth="1"/>
-    <col min="23" max="25" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="11" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="13.625" customWidth="1"/>
-    <col min="30" max="30" width="14.125" customWidth="1"/>
-    <col min="31" max="31" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.375" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="11.875" style="8" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="11.875" style="8" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -12292,45 +12072,9 @@
       <c r="T1" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="U1" s="7" t="s">
-        <v>8</v>
-      </c>
-      <c r="V1" s="7" t="s">
-        <v>7</v>
-      </c>
-      <c r="W1" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="X1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="Y1" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="Z1" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="AA1" s="11" t="s">
-        <v>25</v>
-      </c>
-      <c r="AB1" s="11" t="s">
-        <v>26</v>
-      </c>
-      <c r="AC1" s="11" t="s">
-        <v>27</v>
-      </c>
-      <c r="AD1" s="11" t="s">
-        <v>28</v>
-      </c>
-      <c r="AE1" s="11" t="s">
-        <v>29</v>
-      </c>
-      <c r="AF1" s="11" t="s">
-        <v>30</v>
-      </c>
-      <c r="AJ1"/>
-    </row>
-    <row r="2" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="X1"/>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2" s="10">
         <v>46023</v>
       </c>
@@ -12354,11 +12098,9 @@
         <v>77757917</v>
       </c>
       <c r="I2" s="16">
-        <v>159747657</v>
-      </c>
-      <c r="J2" s="16">
-        <v>80776567</v>
-      </c>
+        <v>240524224</v>
+      </c>
+      <c r="J2" s="16"/>
       <c r="K2" s="16">
         <v>164563755</v>
       </c>
@@ -12378,7 +12120,7 @@
         <v>12328825</v>
       </c>
       <c r="Q2" s="16">
-        <v>26951288.645</v>
+        <v>26951289</v>
       </c>
       <c r="R2" s="16">
         <v>17582210</v>
@@ -12389,20 +12131,8 @@
       <c r="T2" s="16">
         <v>11421045</v>
       </c>
-      <c r="U2" s="11"/>
-      <c r="V2" s="11"/>
-      <c r="W2" s="11"/>
-      <c r="X2" s="11"/>
-      <c r="Y2" s="13"/>
-      <c r="Z2" s="14"/>
-      <c r="AA2" s="14"/>
-      <c r="AB2" s="14"/>
-      <c r="AC2" s="14"/>
-      <c r="AD2" s="14"/>
-      <c r="AE2" s="14"/>
-      <c r="AF2" s="14"/>
-    </row>
-    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>46054</v>
       </c>
@@ -12426,11 +12156,9 @@
         <v>56988098</v>
       </c>
       <c r="I3" s="16">
-        <v>139080755</v>
-      </c>
-      <c r="J3" s="16">
-        <v>66368831</v>
-      </c>
+        <v>205449586</v>
+      </c>
+      <c r="J3" s="16"/>
       <c r="K3" s="16">
         <v>133527806</v>
       </c>
@@ -12450,7 +12178,7 @@
         <v>11843864</v>
       </c>
       <c r="Q3" s="16">
-        <v>24125862.190000001</v>
+        <v>24125862</v>
       </c>
       <c r="R3" s="16">
         <v>17502574</v>
@@ -12461,20 +12189,8 @@
       <c r="T3" s="16">
         <v>9307650</v>
       </c>
-      <c r="U3" s="11"/>
-      <c r="V3" s="11"/>
-      <c r="W3" s="11"/>
-      <c r="X3" s="11"/>
-      <c r="Y3" s="13"/>
-      <c r="Z3" s="14"/>
-      <c r="AA3" s="14"/>
-      <c r="AB3" s="14"/>
-      <c r="AC3" s="14"/>
-      <c r="AD3" s="14"/>
-      <c r="AE3" s="14"/>
-      <c r="AF3" s="14"/>
-    </row>
-    <row r="4" spans="1:36" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" s="10">
         <v>46082</v>
       </c>
@@ -12486,10 +12202,10 @@
       </c>
       <c r="D4" s="11"/>
       <c r="E4" s="16">
-        <v>21179905</v>
+        <v>21282176</v>
       </c>
       <c r="F4" s="16">
-        <v>2884258887</v>
+        <v>2884156616</v>
       </c>
       <c r="G4" s="16">
         <v>70951238</v>
@@ -12498,11 +12214,9 @@
         <v>39997670</v>
       </c>
       <c r="I4" s="16">
-        <v>149061939</v>
-      </c>
-      <c r="J4" s="16">
-        <v>87907988</v>
-      </c>
+        <v>236969927</v>
+      </c>
+      <c r="J4" s="16"/>
       <c r="K4" s="16">
         <v>118157095</v>
       </c>
@@ -12522,7 +12236,7 @@
         <v>12806117</v>
       </c>
       <c r="Q4" s="16">
-        <v>22681313.199999999</v>
+        <v>22681313</v>
       </c>
       <c r="R4" s="16">
         <v>19638888</v>
@@ -12533,20 +12247,8 @@
       <c r="T4" s="16">
         <v>7565713</v>
       </c>
-      <c r="U4" s="11"/>
-      <c r="V4" s="11"/>
-      <c r="W4" s="11"/>
-      <c r="X4" s="11"/>
-      <c r="Y4" s="13"/>
-      <c r="Z4" s="14"/>
-      <c r="AA4" s="14"/>
-      <c r="AB4" s="14"/>
-      <c r="AC4" s="14"/>
-      <c r="AD4" s="14"/>
-      <c r="AE4" s="14"/>
-      <c r="AF4" s="14"/>
-    </row>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
         <v>46113</v>
       </c>
@@ -12558,34 +12260,32 @@
       </c>
       <c r="D5" s="11"/>
       <c r="E5" s="11">
-        <v>17216859</v>
+        <v>17423951</v>
       </c>
       <c r="F5" s="11">
-        <v>1429905580.4920909</v>
+        <v>1317984108</v>
       </c>
       <c r="G5" s="11">
-        <v>38505823</v>
+        <v>33556765</v>
       </c>
       <c r="H5" s="11">
-        <v>18285997</v>
+        <v>16338705</v>
       </c>
       <c r="I5" s="11">
-        <v>135781662</v>
-      </c>
-      <c r="J5" s="11">
-        <v>75542871</v>
-      </c>
+        <v>210530636</v>
+      </c>
+      <c r="J5" s="11"/>
       <c r="K5" s="11">
-        <v>79293388.170000002</v>
+        <v>79667647</v>
       </c>
       <c r="L5" s="11">
-        <v>40806894.699999996</v>
+        <v>40917600</v>
       </c>
       <c r="M5" s="11">
-        <v>34436029.399999999</v>
+        <v>32668164</v>
       </c>
       <c r="N5" s="11">
-        <v>787908453</v>
+        <v>762126521</v>
       </c>
       <c r="O5" s="11">
         <v>247985958</v>
@@ -12594,31 +12294,19 @@
         <v>12554326</v>
       </c>
       <c r="Q5" s="11">
-        <v>18612436.409000002</v>
+        <v>18612436</v>
       </c>
       <c r="R5" s="11">
-        <v>16580975</v>
+        <v>17472595</v>
       </c>
       <c r="S5" s="11">
-        <v>594618</v>
+        <v>679333</v>
       </c>
       <c r="T5" s="11">
         <v>3119149</v>
       </c>
-      <c r="U5" s="11"/>
-      <c r="V5" s="11"/>
-      <c r="W5" s="11"/>
-      <c r="X5" s="11"/>
-      <c r="Y5" s="13"/>
-      <c r="Z5" s="14"/>
-      <c r="AA5" s="14"/>
-      <c r="AB5" s="14"/>
-      <c r="AC5" s="14"/>
-      <c r="AD5" s="14"/>
-      <c r="AE5" s="14"/>
-      <c r="AF5" s="14"/>
-    </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>46143</v>
       </c>
@@ -12630,67 +12318,53 @@
       </c>
       <c r="D6" s="11"/>
       <c r="E6" s="11">
-        <v>18599423</v>
+        <v>17978198</v>
       </c>
       <c r="F6" s="11">
-        <v>870593198.98114467</v>
+        <v>745886107</v>
       </c>
       <c r="G6" s="11">
-        <v>21446203</v>
+        <v>20148017</v>
       </c>
       <c r="H6" s="11">
-        <v>8495852</v>
+        <v>8274790</v>
       </c>
       <c r="I6" s="11">
-        <v>134964858</v>
-      </c>
-      <c r="J6" s="11">
-        <v>74733302</v>
-      </c>
+        <v>201802358</v>
+      </c>
+      <c r="J6" s="11"/>
       <c r="K6" s="11">
-        <v>64925392.18</v>
+        <v>65164715</v>
       </c>
       <c r="L6" s="11">
-        <v>26224796.549999997</v>
+        <v>25533895</v>
       </c>
       <c r="M6" s="11">
-        <v>59097625.649999999</v>
+        <v>67881591</v>
       </c>
       <c r="N6" s="11">
-        <v>645328748</v>
+        <v>727133107</v>
       </c>
       <c r="O6" s="11">
-        <v>252662357</v>
+        <v>256073335</v>
       </c>
       <c r="P6" s="11">
-        <v>11958779</v>
+        <v>12975222</v>
       </c>
       <c r="Q6" s="11">
-        <v>16571668</v>
+        <v>17485587</v>
       </c>
       <c r="R6" s="11">
-        <v>16746017</v>
+        <v>17360057</v>
       </c>
       <c r="S6" s="11">
-        <v>368820</v>
+        <v>574895</v>
       </c>
       <c r="T6" s="11">
-        <v>2208175</v>
-      </c>
-      <c r="U6" s="11"/>
-      <c r="V6" s="11"/>
-      <c r="W6" s="11"/>
-      <c r="X6" s="11"/>
-      <c r="Y6" s="13"/>
-      <c r="Z6" s="14"/>
-      <c r="AA6" s="14"/>
-      <c r="AB6" s="14"/>
-      <c r="AC6" s="14"/>
-      <c r="AD6" s="14"/>
-      <c r="AE6" s="14"/>
-      <c r="AF6" s="14"/>
-    </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2273092</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" s="10">
         <v>46174</v>
       </c>
@@ -12705,64 +12379,50 @@
         <v>17711412</v>
       </c>
       <c r="F7" s="11">
-        <v>487167831.34020805</v>
+        <v>570535663</v>
       </c>
       <c r="G7" s="11">
-        <v>14823593</v>
+        <v>14164767</v>
       </c>
       <c r="H7" s="11">
         <v>3489735</v>
       </c>
       <c r="I7" s="11">
-        <v>123353983</v>
-      </c>
-      <c r="J7" s="11">
-        <v>67271031</v>
-      </c>
+        <v>189828300</v>
+      </c>
+      <c r="J7" s="11"/>
       <c r="K7" s="11">
-        <v>52416173.240000002</v>
+        <v>53185938</v>
       </c>
       <c r="L7" s="11">
-        <v>19379772</v>
+        <v>20431913</v>
       </c>
       <c r="M7" s="11">
-        <v>128265681.64999999</v>
+        <v>135471653</v>
       </c>
       <c r="N7" s="11">
-        <v>735070923</v>
+        <v>641653473</v>
       </c>
       <c r="O7" s="11">
-        <v>248526852</v>
+        <v>256275986</v>
       </c>
       <c r="P7" s="11">
-        <v>12298069</v>
+        <v>12797217</v>
       </c>
       <c r="Q7" s="11">
-        <v>15368545</v>
+        <v>15296371</v>
       </c>
       <c r="R7" s="11">
-        <v>18372506</v>
+        <v>19048834</v>
       </c>
       <c r="S7" s="11">
-        <v>362887</v>
+        <v>363305</v>
       </c>
       <c r="T7" s="11">
-        <v>1851184</v>
-      </c>
-      <c r="U7" s="11"/>
-      <c r="V7" s="11"/>
-      <c r="W7" s="11"/>
-      <c r="X7" s="11"/>
-      <c r="Y7" s="13"/>
-      <c r="Z7" s="14"/>
-      <c r="AA7" s="14"/>
-      <c r="AB7" s="14"/>
-      <c r="AC7" s="14"/>
-      <c r="AD7" s="14"/>
-      <c r="AE7" s="14"/>
-      <c r="AF7" s="14"/>
-    </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.3">
+        <v>1964110</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
         <v>46204</v>
       </c>
@@ -12777,64 +12437,50 @@
         <v>19091123</v>
       </c>
       <c r="F8" s="11">
-        <v>392330031.12423694</v>
+        <v>399010844</v>
       </c>
       <c r="G8" s="11">
-        <v>9480098.6270000003</v>
+        <v>11095126</v>
       </c>
       <c r="H8" s="11">
         <v>3298632</v>
       </c>
       <c r="I8" s="11">
-        <v>125563814</v>
-      </c>
-      <c r="J8" s="11">
-        <v>57468566</v>
-      </c>
+        <v>183365593</v>
+      </c>
+      <c r="J8" s="11"/>
       <c r="K8" s="11">
-        <v>46510574.619999997</v>
+        <v>47193612</v>
       </c>
       <c r="L8" s="11">
-        <v>17586718.25</v>
+        <v>18448952</v>
       </c>
       <c r="M8" s="11">
-        <v>188698280.54999998</v>
+        <v>198504839</v>
       </c>
       <c r="N8" s="11">
-        <v>654300510</v>
+        <v>657628999</v>
       </c>
       <c r="O8" s="11">
-        <v>269265592</v>
+        <v>269265107</v>
       </c>
       <c r="P8" s="11">
-        <v>11823297</v>
+        <v>11823298</v>
       </c>
       <c r="Q8" s="11">
-        <v>15699682</v>
+        <v>15695080</v>
       </c>
       <c r="R8" s="11">
-        <v>18986109</v>
+        <v>19685025</v>
       </c>
       <c r="S8" s="11">
-        <v>689740</v>
+        <v>690534</v>
       </c>
       <c r="T8" s="11">
-        <v>1638722</v>
-      </c>
-      <c r="U8" s="11"/>
-      <c r="V8" s="11"/>
-      <c r="W8" s="11"/>
-      <c r="X8" s="11"/>
-      <c r="Y8" s="13"/>
-      <c r="Z8" s="14"/>
-      <c r="AA8" s="14"/>
-      <c r="AB8" s="14"/>
-      <c r="AC8" s="14"/>
-      <c r="AD8" s="14"/>
-      <c r="AE8" s="14"/>
-      <c r="AF8" s="14"/>
-    </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.3">
+        <v>1623257</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" s="10">
         <v>46235</v>
       </c>
@@ -12849,64 +12495,50 @@
         <v>18930791</v>
       </c>
       <c r="F9" s="11">
-        <v>361153904.40035677</v>
+        <v>367303833</v>
       </c>
       <c r="G9" s="11">
-        <v>7705230.7879999997</v>
+        <v>11638464.788000001</v>
       </c>
       <c r="H9" s="11">
         <v>3561524</v>
       </c>
       <c r="I9" s="11">
-        <v>120278427</v>
-      </c>
-      <c r="J9" s="11">
-        <v>51363845</v>
-      </c>
+        <v>171954749</v>
+      </c>
+      <c r="J9" s="11"/>
       <c r="K9" s="11">
-        <v>43470713.93</v>
+        <v>44109109</v>
       </c>
       <c r="L9" s="11">
-        <v>16171360.75</v>
+        <v>16964203</v>
       </c>
       <c r="M9" s="11">
-        <v>189783439.90000001</v>
+        <v>199646393</v>
       </c>
       <c r="N9" s="11">
-        <v>635940722</v>
+        <v>631765337</v>
       </c>
       <c r="O9" s="11">
-        <v>271292299</v>
+        <v>271292700</v>
       </c>
       <c r="P9" s="11">
         <v>12114875</v>
       </c>
       <c r="Q9" s="11">
-        <v>15592995</v>
+        <v>15588424</v>
       </c>
       <c r="R9" s="11">
-        <v>18986109</v>
+        <v>19685025</v>
       </c>
       <c r="S9" s="11">
-        <v>669286</v>
+        <v>670057</v>
       </c>
       <c r="T9" s="11">
-        <v>1509793</v>
-      </c>
-      <c r="U9" s="11"/>
-      <c r="V9" s="11"/>
-      <c r="W9" s="11"/>
-      <c r="X9" s="11"/>
-      <c r="Y9" s="13"/>
-      <c r="Z9" s="14"/>
-      <c r="AA9" s="14"/>
-      <c r="AB9" s="14"/>
-      <c r="AC9" s="14"/>
-      <c r="AD9" s="14"/>
-      <c r="AE9" s="14"/>
-      <c r="AF9" s="14"/>
-    </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
+        <v>1495545</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>46266</v>
       </c>
@@ -12921,64 +12553,50 @@
         <v>17988496</v>
       </c>
       <c r="F10" s="11">
-        <v>412482971.1851669</v>
+        <v>419506960</v>
       </c>
       <c r="G10" s="11">
-        <v>10337147.964</v>
+        <v>9318008.9639999997</v>
       </c>
       <c r="H10" s="11">
         <v>2163629</v>
       </c>
       <c r="I10" s="11">
-        <v>117034505</v>
-      </c>
-      <c r="J10" s="11">
-        <v>56649876</v>
-      </c>
+        <v>174000576</v>
+      </c>
+      <c r="J10" s="11"/>
       <c r="K10" s="11">
-        <v>45600617.619999997</v>
+        <v>46270291</v>
       </c>
       <c r="L10" s="11">
-        <v>16389969.049999999</v>
+        <v>17193529</v>
       </c>
       <c r="M10" s="11">
-        <v>127960946.34999999</v>
+        <v>134611015</v>
       </c>
       <c r="N10" s="11">
-        <v>631309778</v>
+        <v>631363795</v>
       </c>
       <c r="O10" s="11">
-        <v>251119226</v>
+        <v>251119328</v>
       </c>
       <c r="P10" s="11">
         <v>13375616</v>
       </c>
       <c r="Q10" s="11">
-        <v>17966136</v>
+        <v>17960870</v>
       </c>
       <c r="R10" s="11">
-        <v>18374429</v>
+        <v>19050828</v>
       </c>
       <c r="S10" s="11">
-        <v>672824</v>
+        <v>673599</v>
       </c>
       <c r="T10" s="11">
-        <v>1421151</v>
-      </c>
-      <c r="U10" s="11"/>
-      <c r="V10" s="11"/>
-      <c r="W10" s="11"/>
-      <c r="X10" s="11"/>
-      <c r="Y10" s="13"/>
-      <c r="Z10" s="14"/>
-      <c r="AA10" s="14"/>
-      <c r="AB10" s="14"/>
-      <c r="AC10" s="14"/>
-      <c r="AD10" s="14"/>
-      <c r="AE10" s="14"/>
-      <c r="AF10" s="14"/>
-    </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
+        <v>1407739</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" s="10">
         <v>46296</v>
       </c>
@@ -12993,64 +12611,50 @@
         <v>18390885</v>
       </c>
       <c r="F11" s="11">
-        <v>1046248542.4740975</v>
+        <v>1064064642</v>
       </c>
       <c r="G11" s="11">
-        <v>19794040.274999999</v>
+        <v>31378967.274999999</v>
       </c>
       <c r="H11" s="11">
         <v>14574059</v>
       </c>
       <c r="I11" s="11">
-        <v>125903781</v>
-      </c>
-      <c r="J11" s="11">
-        <v>66826684</v>
-      </c>
+        <v>193081334</v>
+      </c>
+      <c r="J11" s="11"/>
       <c r="K11" s="11">
-        <v>61027608.199999996</v>
+        <v>61923837</v>
       </c>
       <c r="L11" s="11">
-        <v>24746866.349999998</v>
+        <v>25960144</v>
       </c>
       <c r="M11" s="11">
-        <v>51497963.849999994</v>
+        <v>54174288</v>
       </c>
       <c r="N11" s="11">
-        <v>722390553</v>
+        <v>721391799</v>
       </c>
       <c r="O11" s="11">
-        <v>241435330</v>
+        <v>241435932</v>
       </c>
       <c r="P11" s="11">
         <v>12701349</v>
       </c>
       <c r="Q11" s="11">
-        <v>21402417</v>
+        <v>21396143</v>
       </c>
       <c r="R11" s="11">
-        <v>17195229</v>
+        <v>17828219</v>
       </c>
       <c r="S11" s="11">
-        <v>506689</v>
+        <v>507273</v>
       </c>
       <c r="T11" s="11">
-        <v>2280309</v>
-      </c>
-      <c r="U11" s="11"/>
-      <c r="V11" s="11"/>
-      <c r="W11" s="11"/>
-      <c r="X11" s="11"/>
-      <c r="Y11" s="13"/>
-      <c r="Z11" s="14"/>
-      <c r="AA11" s="14"/>
-      <c r="AB11" s="14"/>
-      <c r="AC11" s="14"/>
-      <c r="AD11" s="14"/>
-      <c r="AE11" s="14"/>
-      <c r="AF11" s="14"/>
-    </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.3">
+        <v>2258789</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
         <v>46327</v>
       </c>
@@ -13065,64 +12669,50 @@
         <v>19908932</v>
       </c>
       <c r="F12" s="11">
-        <v>2304870023.3452382</v>
+        <v>2344118627</v>
       </c>
       <c r="G12" s="11">
-        <v>46552131.399999999</v>
+        <v>58388019.399999999</v>
       </c>
       <c r="H12" s="11">
         <v>36431964</v>
       </c>
       <c r="I12" s="11">
-        <v>135379992</v>
-      </c>
-      <c r="J12" s="11">
-        <v>77567694</v>
-      </c>
+        <v>213335361</v>
+      </c>
+      <c r="J12" s="11"/>
       <c r="K12" s="11">
-        <v>86338151.879999995</v>
+        <v>87606082</v>
       </c>
       <c r="L12" s="11">
-        <v>56386819.649999999</v>
+        <v>59151326</v>
       </c>
       <c r="M12" s="11">
-        <v>60901523.649999999</v>
+        <v>64066546</v>
       </c>
       <c r="N12" s="11">
-        <v>744382861</v>
+        <v>743647221</v>
       </c>
       <c r="O12" s="11">
-        <v>243126842</v>
+        <v>243125516</v>
       </c>
       <c r="P12" s="11">
-        <v>11788927</v>
+        <v>11789274</v>
       </c>
       <c r="Q12" s="11">
-        <v>24040091</v>
+        <v>24033044</v>
       </c>
       <c r="R12" s="11">
-        <v>16134336</v>
+        <v>16728273</v>
       </c>
       <c r="S12" s="11">
-        <v>418977</v>
+        <v>419460</v>
       </c>
       <c r="T12" s="11">
-        <v>5107092</v>
-      </c>
-      <c r="U12" s="11"/>
-      <c r="V12" s="11"/>
-      <c r="W12" s="11"/>
-      <c r="X12" s="11"/>
-      <c r="Y12" s="13"/>
-      <c r="Z12" s="14"/>
-      <c r="AA12" s="14"/>
-      <c r="AB12" s="14"/>
-      <c r="AC12" s="14"/>
-      <c r="AD12" s="14"/>
-      <c r="AE12" s="14"/>
-      <c r="AF12" s="14"/>
-    </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.3">
+        <v>5058894</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>46357</v>
       </c>
@@ -13137,62 +12727,48 @@
         <v>23714408</v>
       </c>
       <c r="F13" s="11">
-        <v>4479450855.6574593</v>
+        <v>4555729427</v>
       </c>
       <c r="G13" s="11">
-        <v>73125901.263999999</v>
+        <v>82134723.263999999</v>
       </c>
       <c r="H13" s="11">
         <v>66717098</v>
       </c>
       <c r="I13" s="11">
-        <v>160740178</v>
-      </c>
-      <c r="J13" s="11">
-        <v>91641290</v>
-      </c>
+        <v>252840932</v>
+      </c>
+      <c r="J13" s="11"/>
       <c r="K13" s="11">
-        <v>141311709.75</v>
+        <v>143386961</v>
       </c>
       <c r="L13" s="11">
-        <v>119291298.59999999</v>
+        <v>125139856</v>
       </c>
       <c r="M13" s="11">
-        <v>134619184.75</v>
+        <v>141615279</v>
       </c>
       <c r="N13" s="11">
-        <v>826083486</v>
+        <v>826325218</v>
       </c>
       <c r="O13" s="11">
-        <v>246503941</v>
+        <v>246504114</v>
       </c>
       <c r="P13" s="11">
-        <v>13011733</v>
+        <v>13011734</v>
       </c>
       <c r="Q13" s="11">
-        <v>25653600</v>
+        <v>25646080</v>
       </c>
       <c r="R13" s="11">
-        <v>26022017</v>
+        <v>19686601</v>
       </c>
       <c r="S13" s="11">
-        <v>659027</v>
+        <v>659786</v>
       </c>
       <c r="T13" s="11">
-        <v>10018415</v>
-      </c>
-      <c r="U13" s="11"/>
-      <c r="V13" s="11"/>
-      <c r="W13" s="11"/>
-      <c r="X13" s="11"/>
-      <c r="Y13" s="13"/>
-      <c r="Z13" s="14"/>
-      <c r="AA13" s="14"/>
-      <c r="AB13" s="14"/>
-      <c r="AC13" s="14"/>
-      <c r="AD13" s="14"/>
-      <c r="AE13" s="14"/>
-      <c r="AF13" s="14"/>
+        <v>9923867</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/공급량실적_계획_실적_MJ.xlsx
+++ b/공급량실적_계획_실적_MJ.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\실천사업계획\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82D1D476-8FB0-4416-8BFA-57AADEE77369}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DA7A3C6-8BA9-4FCD-B5CF-89BE48E4B0EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -251,7 +251,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -303,212 +303,15 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="쉼표 [0]" xfId="1" builtinId="6"/>
     <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="83">
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <name val="맑은 고딕"/>
-        <scheme val="none"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="9"/>
-        <color theme="1"/>
-        <name val="맑은 고딕"/>
-        <scheme val="minor"/>
-      </font>
-    </dxf>
+  <dxfs count="115">
     <dxf>
       <font>
         <b val="0"/>
@@ -1357,8 +1160,294 @@
         <u val="none"/>
         <vertAlign val="baseline"/>
         <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="맑은 고딕"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="맑은 고딕"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="맑은 고딕"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="맑은 고딕"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="맑은 고딕"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="맑은 고딕"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <name val="맑은 고딕"/>
+        <scheme val="none"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
         <color theme="1"/>
         <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
         <scheme val="minor"/>
       </font>
     </dxf>
@@ -1393,6 +1482,8 @@
         <sz val="9"/>
         <color theme="1"/>
         <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
         <scheme val="minor"/>
       </font>
     </dxf>
@@ -1427,6 +1518,8 @@
         <sz val="9"/>
         <color theme="1"/>
         <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
         <scheme val="minor"/>
       </font>
     </dxf>
@@ -1461,6 +1554,8 @@
         <sz val="9"/>
         <color theme="1"/>
         <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
         <scheme val="minor"/>
       </font>
     </dxf>
@@ -1495,6 +1590,8 @@
         <sz val="9"/>
         <color theme="1"/>
         <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
         <scheme val="minor"/>
       </font>
     </dxf>
@@ -1514,6 +1611,350 @@
         <name val="맑은 고딕"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
       <font>
@@ -1566,6 +2007,27 @@
         <sz val="9"/>
         <color theme="1"/>
         <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
         <scheme val="minor"/>
       </font>
     </dxf>
@@ -1600,6 +2062,8 @@
         <sz val="9"/>
         <color theme="1"/>
         <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
         <scheme val="minor"/>
       </font>
     </dxf>
@@ -1634,6 +2098,8 @@
         <sz val="9"/>
         <color theme="1"/>
         <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
         <scheme val="minor"/>
       </font>
     </dxf>
@@ -1668,8 +2134,155 @@
         <sz val="9"/>
         <color theme="1"/>
         <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
         <scheme val="minor"/>
       </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <scheme val="minor"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="9"/>
+        <color theme="1"/>
+        <name val="맑은 고딕"/>
+        <family val="3"/>
+        <charset val="129"/>
+        <scheme val="minor"/>
+      </font>
+      <numFmt numFmtId="19" formatCode="yyyy/mm/dd"/>
     </dxf>
     <dxf>
       <font>
@@ -1737,35 +2350,35 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="A1:Y121" totalsRowShown="0" headerRowDxfId="60" dataDxfId="59">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="표1" displayName="표1" ref="A1:Y121" totalsRowShown="0" headerRowDxfId="48" dataDxfId="47">
   <tableColumns count="25">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="날짜" dataDxfId="58"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="연" dataDxfId="57"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="월" dataDxfId="56"/>
-    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="평균기온" dataDxfId="55"/>
-    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="취사용" dataDxfId="54"/>
-    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="개별난방용" dataDxfId="53"/>
-    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="중앙난방용" dataDxfId="52"/>
-    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="자가열전용" dataDxfId="51"/>
-    <tableColumn id="8" xr3:uid="{F6CD84DD-4BD1-4B4F-8F66-408F637C64C3}" name="영업용" dataDxfId="50"/>
-    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="일반용(1)" dataDxfId="49"/>
-    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="일반용(2)" dataDxfId="48"/>
-    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="업무난방용" dataDxfId="47"/>
-    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="냉난방용" dataDxfId="46"/>
-    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="산업용" dataDxfId="45"/>
-    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="수송용(CNG)" dataDxfId="44"/>
-    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="수송용(BIO)" dataDxfId="43"/>
-    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="열병합용" dataDxfId="42"/>
-    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="연료전지용" dataDxfId="41"/>
-    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="열전용설비용(주택외)" dataDxfId="40"/>
-    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="주한미군" dataDxfId="39"/>
-    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="일반용1(영업)" dataDxfId="38"/>
-    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="일반용1(업무)" dataDxfId="37"/>
-    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="총공급량" dataDxfId="36"/>
-    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="총합계" dataDxfId="35">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="날짜" dataDxfId="46"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="연" dataDxfId="45"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="월" dataDxfId="44"/>
+    <tableColumn id="4" xr3:uid="{00000000-0010-0000-0000-000004000000}" name="평균기온" dataDxfId="43"/>
+    <tableColumn id="7" xr3:uid="{00000000-0010-0000-0000-000007000000}" name="취사용" dataDxfId="42"/>
+    <tableColumn id="5" xr3:uid="{00000000-0010-0000-0000-000005000000}" name="개별난방용" dataDxfId="41"/>
+    <tableColumn id="6" xr3:uid="{00000000-0010-0000-0000-000006000000}" name="중앙난방용" dataDxfId="40"/>
+    <tableColumn id="19" xr3:uid="{00000000-0010-0000-0000-000013000000}" name="자가열전용" dataDxfId="39"/>
+    <tableColumn id="8" xr3:uid="{F6CD84DD-4BD1-4B4F-8F66-408F637C64C3}" name="영업용" dataDxfId="38"/>
+    <tableColumn id="9" xr3:uid="{00000000-0010-0000-0000-000009000000}" name="일반용(1)" dataDxfId="37"/>
+    <tableColumn id="12" xr3:uid="{00000000-0010-0000-0000-00000C000000}" name="일반용(2)" dataDxfId="36"/>
+    <tableColumn id="13" xr3:uid="{00000000-0010-0000-0000-00000D000000}" name="업무난방용" dataDxfId="35"/>
+    <tableColumn id="16" xr3:uid="{00000000-0010-0000-0000-000010000000}" name="냉난방용" dataDxfId="34"/>
+    <tableColumn id="15" xr3:uid="{00000000-0010-0000-0000-00000F000000}" name="산업용" dataDxfId="33"/>
+    <tableColumn id="22" xr3:uid="{00000000-0010-0000-0000-000016000000}" name="수송용(CNG)" dataDxfId="32"/>
+    <tableColumn id="21" xr3:uid="{00000000-0010-0000-0000-000015000000}" name="수송용(BIO)" dataDxfId="31"/>
+    <tableColumn id="17" xr3:uid="{00000000-0010-0000-0000-000011000000}" name="열병합용" dataDxfId="30"/>
+    <tableColumn id="18" xr3:uid="{00000000-0010-0000-0000-000012000000}" name="연료전지용" dataDxfId="29"/>
+    <tableColumn id="20" xr3:uid="{00000000-0010-0000-0000-000014000000}" name="열전용설비용(주택외)" dataDxfId="28"/>
+    <tableColumn id="14" xr3:uid="{00000000-0010-0000-0000-00000E000000}" name="주한미군" dataDxfId="27"/>
+    <tableColumn id="11" xr3:uid="{00000000-0010-0000-0000-00000B000000}" name="일반용1(영업)" dataDxfId="26"/>
+    <tableColumn id="10" xr3:uid="{00000000-0010-0000-0000-00000A000000}" name="일반용1(업무)" dataDxfId="25"/>
+    <tableColumn id="23" xr3:uid="{00000000-0010-0000-0000-000017000000}" name="총공급량" dataDxfId="24"/>
+    <tableColumn id="24" xr3:uid="{00000000-0010-0000-0000-000018000000}" name="총합계" dataDxfId="23">
       <calculatedColumnFormula>SUM(표1[[#This Row],[취사용]:[주한미군]])</calculatedColumnFormula>
     </tableColumn>
-    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="비교(V-W)" dataDxfId="34">
+    <tableColumn id="25" xr3:uid="{00000000-0010-0000-0000-000019000000}" name="비교(V-W)" dataDxfId="22">
       <calculatedColumnFormula>W2-X2</calculatedColumnFormula>
     </tableColumn>
   </tableColumns>
@@ -1774,68 +2387,68 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2C1F99CF-9391-4872-B93D-50B931598DD3}" name="표1_3" displayName="표1_3" ref="A1:AF13" totalsRowShown="0" headerRowDxfId="33" dataDxfId="32">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{2C1F99CF-9391-4872-B93D-50B931598DD3}" name="표1_3" displayName="표1_3" ref="A1:AF13" totalsRowShown="0" headerRowDxfId="114" dataDxfId="113">
   <tableColumns count="32">
-    <tableColumn id="1" xr3:uid="{19685FD4-89CE-478F-94BA-7A4B1E721FD4}" name="날짜" dataDxfId="31"/>
-    <tableColumn id="2" xr3:uid="{E31CA521-8EDF-4B60-95F2-6D99A2A44422}" name="연" dataDxfId="30"/>
-    <tableColumn id="3" xr3:uid="{0E1A3862-691A-4EE3-BC9F-15442CFF7BF6}" name="월" dataDxfId="29"/>
-    <tableColumn id="4" xr3:uid="{70EF9B81-BEFB-4CBB-822B-4CF1F1061D51}" name="평균기온" dataDxfId="28"/>
-    <tableColumn id="7" xr3:uid="{FC97C89C-B827-4EAB-8DAD-DBE4EB83293B}" name="취사용" dataDxfId="27"/>
-    <tableColumn id="5" xr3:uid="{6EB58682-1AB0-402D-B1B5-64D7A3FEE7DC}" name="개별난방용" dataDxfId="26"/>
-    <tableColumn id="6" xr3:uid="{9B5B2C66-64AC-4900-AA35-A909EB1F3ADB}" name="중앙난방용" dataDxfId="25"/>
-    <tableColumn id="19" xr3:uid="{BB6DF2E3-2587-479E-A2F3-005ADFBAD580}" name="자가열전용" dataDxfId="24"/>
-    <tableColumn id="32" xr3:uid="{19247A41-B716-45A1-89D6-71493825C64A}" name="영업용" dataDxfId="23"/>
-    <tableColumn id="9" xr3:uid="{AE3DB5EB-C7E4-47AD-9093-9ED129869DB2}" name="일반용(1)" dataDxfId="22"/>
-    <tableColumn id="12" xr3:uid="{8B4AF52F-6164-471B-AE99-CC06D0BB14EF}" name="일반용(2)" dataDxfId="21"/>
-    <tableColumn id="13" xr3:uid="{371738D5-71AD-4443-9E50-C5CBFA38DD53}" name="업무난방용" dataDxfId="20"/>
-    <tableColumn id="16" xr3:uid="{900065B7-DB40-43BE-8FF7-E75CA356AC45}" name="냉난방용" dataDxfId="19"/>
-    <tableColumn id="15" xr3:uid="{DEBF6157-B4E3-448F-B30C-6BA984C794F5}" name="산업용" dataDxfId="18"/>
-    <tableColumn id="22" xr3:uid="{110C96B1-CEF5-460E-976A-E31DDA355398}" name="수송용(CNG)" dataDxfId="17"/>
-    <tableColumn id="21" xr3:uid="{06CF64A6-4CFF-491D-A557-FA4850CF0868}" name="수송용(BIO)" dataDxfId="16"/>
-    <tableColumn id="17" xr3:uid="{325D94CD-83AF-4821-8554-98F27BA03A89}" name="열병합용" dataDxfId="15"/>
-    <tableColumn id="18" xr3:uid="{6CE1C920-1D02-4ED1-B172-01F6E3A7A08C}" name="연료전지용" dataDxfId="14"/>
-    <tableColumn id="20" xr3:uid="{0B7A0B86-42DA-48FF-AD28-7D4F4C7EE8B6}" name="열전용설비용(주택외)" dataDxfId="13"/>
-    <tableColumn id="14" xr3:uid="{66ED3A2C-2F9A-4DC1-B2E1-96B11BA082CD}" name="주한미군" dataDxfId="12"/>
-    <tableColumn id="11" xr3:uid="{8576E086-9957-4A83-B3D2-E6372750D253}" name="일반용1(영업)" dataDxfId="11"/>
-    <tableColumn id="10" xr3:uid="{AC7AEF69-FC00-4021-A757-1F6CB56D86E9}" name="일반용1(업무)" dataDxfId="10"/>
-    <tableColumn id="23" xr3:uid="{0A863EFD-5ACB-4216-A172-3D5E489B9B61}" name="총공급량" dataDxfId="9"/>
-    <tableColumn id="24" xr3:uid="{3F3F5052-4199-490C-8994-5E9CF83BDE9D}" name="총합계" dataDxfId="8"/>
-    <tableColumn id="25" xr3:uid="{F3502AAC-AAE0-469B-8FF7-545D8F24C683}" name="비교(V-W)" dataDxfId="7"/>
-    <tableColumn id="8" xr3:uid="{FA0345C9-D72C-4A34-84B0-7B3673E66B4B}" name="열1" dataDxfId="6"/>
-    <tableColumn id="26" xr3:uid="{924F492C-4495-498A-A3CC-8AB7A213EB49}" name="열2" dataDxfId="5"/>
-    <tableColumn id="27" xr3:uid="{7D1ACE6F-EB3E-490F-A815-30511D277AEB}" name="열3" dataDxfId="4"/>
-    <tableColumn id="28" xr3:uid="{D28E208B-F040-4AE4-ACFF-E094E4F8E7A7}" name="열4" dataDxfId="3"/>
-    <tableColumn id="29" xr3:uid="{186D4369-AF71-4A71-9851-5932B907782C}" name="열5" dataDxfId="2"/>
-    <tableColumn id="30" xr3:uid="{896603AA-8674-4905-8A79-3984C733419F}" name="열6" dataDxfId="1"/>
-    <tableColumn id="31" xr3:uid="{27B69BAA-C555-4945-8804-7D4A8F0D00B9}" name="열7" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{19685FD4-89CE-478F-94BA-7A4B1E721FD4}" name="날짜" dataDxfId="112" totalsRowDxfId="111"/>
+    <tableColumn id="2" xr3:uid="{E31CA521-8EDF-4B60-95F2-6D99A2A44422}" name="연" dataDxfId="110" totalsRowDxfId="109"/>
+    <tableColumn id="3" xr3:uid="{0E1A3862-691A-4EE3-BC9F-15442CFF7BF6}" name="월" dataDxfId="108" totalsRowDxfId="107"/>
+    <tableColumn id="4" xr3:uid="{70EF9B81-BEFB-4CBB-822B-4CF1F1061D51}" name="평균기온" dataDxfId="106" totalsRowDxfId="105"/>
+    <tableColumn id="7" xr3:uid="{FC97C89C-B827-4EAB-8DAD-DBE4EB83293B}" name="취사용" dataDxfId="104" totalsRowDxfId="103"/>
+    <tableColumn id="5" xr3:uid="{6EB58682-1AB0-402D-B1B5-64D7A3FEE7DC}" name="개별난방용" dataDxfId="102" totalsRowDxfId="101"/>
+    <tableColumn id="6" xr3:uid="{9B5B2C66-64AC-4900-AA35-A909EB1F3ADB}" name="중앙난방용" dataDxfId="100" totalsRowDxfId="99"/>
+    <tableColumn id="19" xr3:uid="{BB6DF2E3-2587-479E-A2F3-005ADFBAD580}" name="자가열전용" dataDxfId="98" totalsRowDxfId="97"/>
+    <tableColumn id="32" xr3:uid="{19247A41-B716-45A1-89D6-71493825C64A}" name="영업용" dataDxfId="96" totalsRowDxfId="95"/>
+    <tableColumn id="9" xr3:uid="{AE3DB5EB-C7E4-47AD-9093-9ED129869DB2}" name="일반용(1)" dataDxfId="94" totalsRowDxfId="93"/>
+    <tableColumn id="12" xr3:uid="{8B4AF52F-6164-471B-AE99-CC06D0BB14EF}" name="일반용(2)" dataDxfId="92" totalsRowDxfId="91"/>
+    <tableColumn id="13" xr3:uid="{371738D5-71AD-4443-9E50-C5CBFA38DD53}" name="업무난방용" dataDxfId="90" totalsRowDxfId="89"/>
+    <tableColumn id="16" xr3:uid="{900065B7-DB40-43BE-8FF7-E75CA356AC45}" name="냉난방용" dataDxfId="88" totalsRowDxfId="87"/>
+    <tableColumn id="15" xr3:uid="{DEBF6157-B4E3-448F-B30C-6BA984C794F5}" name="산업용" dataDxfId="86" totalsRowDxfId="85"/>
+    <tableColumn id="22" xr3:uid="{110C96B1-CEF5-460E-976A-E31DDA355398}" name="수송용(CNG)" dataDxfId="84" totalsRowDxfId="83"/>
+    <tableColumn id="21" xr3:uid="{06CF64A6-4CFF-491D-A557-FA4850CF0868}" name="수송용(BIO)" dataDxfId="82" totalsRowDxfId="81"/>
+    <tableColumn id="17" xr3:uid="{325D94CD-83AF-4821-8554-98F27BA03A89}" name="열병합용" dataDxfId="80" totalsRowDxfId="79"/>
+    <tableColumn id="18" xr3:uid="{6CE1C920-1D02-4ED1-B172-01F6E3A7A08C}" name="연료전지용" dataDxfId="78" totalsRowDxfId="77"/>
+    <tableColumn id="20" xr3:uid="{0B7A0B86-42DA-48FF-AD28-7D4F4C7EE8B6}" name="열전용설비용(주택외)" dataDxfId="76" totalsRowDxfId="75"/>
+    <tableColumn id="14" xr3:uid="{66ED3A2C-2F9A-4DC1-B2E1-96B11BA082CD}" name="주한미군" dataDxfId="74" totalsRowDxfId="73"/>
+    <tableColumn id="11" xr3:uid="{8576E086-9957-4A83-B3D2-E6372750D253}" name="일반용1(영업)" dataDxfId="72" totalsRowDxfId="71"/>
+    <tableColumn id="10" xr3:uid="{AC7AEF69-FC00-4021-A757-1F6CB56D86E9}" name="일반용1(업무)" dataDxfId="70" totalsRowDxfId="69"/>
+    <tableColumn id="23" xr3:uid="{0A863EFD-5ACB-4216-A172-3D5E489B9B61}" name="총공급량" dataDxfId="68" totalsRowDxfId="67"/>
+    <tableColumn id="24" xr3:uid="{3F3F5052-4199-490C-8994-5E9CF83BDE9D}" name="총합계" dataDxfId="66" totalsRowDxfId="65"/>
+    <tableColumn id="25" xr3:uid="{F3502AAC-AAE0-469B-8FF7-545D8F24C683}" name="비교(V-W)" dataDxfId="64" totalsRowDxfId="63"/>
+    <tableColumn id="8" xr3:uid="{FA0345C9-D72C-4A34-84B0-7B3673E66B4B}" name="열1" dataDxfId="62" totalsRowDxfId="61"/>
+    <tableColumn id="26" xr3:uid="{924F492C-4495-498A-A3CC-8AB7A213EB49}" name="열2" dataDxfId="60" totalsRowDxfId="59"/>
+    <tableColumn id="27" xr3:uid="{7D1ACE6F-EB3E-490F-A815-30511D277AEB}" name="열3" dataDxfId="58" totalsRowDxfId="57"/>
+    <tableColumn id="28" xr3:uid="{D28E208B-F040-4AE4-ACFF-E094E4F8E7A7}" name="열4" dataDxfId="56" totalsRowDxfId="55"/>
+    <tableColumn id="29" xr3:uid="{186D4369-AF71-4A71-9851-5932B907782C}" name="열5" dataDxfId="54" totalsRowDxfId="53"/>
+    <tableColumn id="30" xr3:uid="{896603AA-8674-4905-8A79-3984C733419F}" name="열6" dataDxfId="52" totalsRowDxfId="51"/>
+    <tableColumn id="31" xr3:uid="{27B69BAA-C555-4945-8804-7D4A8F0D00B9}" name="열7" dataDxfId="50" totalsRowDxfId="49"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{EC6B23D4-390C-404E-AE69-455A5E70B9EF}" name="표1_34" displayName="표1_34" ref="A1:T13" totalsRowShown="0" headerRowDxfId="82" dataDxfId="81">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{EC6B23D4-390C-404E-AE69-455A5E70B9EF}" name="표1_34" displayName="표1_34" ref="A1:T13" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
   <tableColumns count="20">
-    <tableColumn id="1" xr3:uid="{32BFE98C-3743-4F2A-B0AA-77B0B6019DD7}" name="날짜" dataDxfId="80"/>
-    <tableColumn id="2" xr3:uid="{51E25201-28D0-4E8C-BEC7-0E3F4D5F3645}" name="연" dataDxfId="79"/>
-    <tableColumn id="3" xr3:uid="{80FFE0A8-C94B-40E9-B01D-932A55EF6766}" name="월" dataDxfId="78"/>
-    <tableColumn id="4" xr3:uid="{B563055E-F2FB-42BE-BA0E-E08593191708}" name="평균기온" dataDxfId="77"/>
-    <tableColumn id="7" xr3:uid="{EC02A3A1-631C-42EF-85AF-A8B79A8D9F9B}" name="취사용" dataDxfId="76"/>
-    <tableColumn id="5" xr3:uid="{86073F88-2F80-4462-BB87-5B8A54551B6A}" name="개별난방용" dataDxfId="75"/>
-    <tableColumn id="6" xr3:uid="{139EC257-82FA-481B-9F18-60ADA6EB50D3}" name="중앙난방용" dataDxfId="74"/>
-    <tableColumn id="19" xr3:uid="{408C0C4D-65A0-4DC3-A85C-EF1BC48BFA6F}" name="자가열전용" dataDxfId="73"/>
-    <tableColumn id="32" xr3:uid="{F08BABB7-87AA-4744-89E7-228FA9D35660}" name="영업용" dataDxfId="72"/>
-    <tableColumn id="9" xr3:uid="{D46D49CA-B262-4926-A5D1-6DDB23F119D4}" name="일반용(1)" dataDxfId="71"/>
-    <tableColumn id="12" xr3:uid="{861B7867-2B87-4609-A7B2-0963E4807DC3}" name="일반용(2)" dataDxfId="70"/>
-    <tableColumn id="13" xr3:uid="{14954B61-A6C3-4B22-BB69-82FCB6C6800D}" name="업무난방용" dataDxfId="69"/>
-    <tableColumn id="16" xr3:uid="{79636BBA-3A6E-42BA-959F-C2875D1EB9BF}" name="냉난방용" dataDxfId="68"/>
-    <tableColumn id="15" xr3:uid="{9E90082E-3CE5-4697-A0B1-A041913653D4}" name="산업용" dataDxfId="67"/>
-    <tableColumn id="22" xr3:uid="{15EC95E6-8587-482D-BF25-3DEDC8762C1E}" name="수송용(CNG)" dataDxfId="66"/>
-    <tableColumn id="21" xr3:uid="{0578ED32-2CDD-4E0D-B4BF-9D8549DC6AE8}" name="수송용(BIO)" dataDxfId="65"/>
-    <tableColumn id="17" xr3:uid="{A2C46C4C-5370-461A-AEAE-B18F07625F71}" name="열병합용" dataDxfId="64"/>
-    <tableColumn id="18" xr3:uid="{DF7D0596-2D46-4696-A139-30735FD75FF7}" name="연료전지용" dataDxfId="63"/>
-    <tableColumn id="20" xr3:uid="{BE9174ED-E86A-4C72-8087-5A38B6314769}" name="열전용설비용(주택외)" dataDxfId="62"/>
-    <tableColumn id="14" xr3:uid="{094C3E7A-F02F-42B7-A5BF-D2A7A7C7AD81}" name="주한미군" dataDxfId="61"/>
+    <tableColumn id="1" xr3:uid="{32BFE98C-3743-4F2A-B0AA-77B0B6019DD7}" name="날짜" dataDxfId="19"/>
+    <tableColumn id="2" xr3:uid="{51E25201-28D0-4E8C-BEC7-0E3F4D5F3645}" name="연" dataDxfId="18"/>
+    <tableColumn id="3" xr3:uid="{80FFE0A8-C94B-40E9-B01D-932A55EF6766}" name="월" dataDxfId="17"/>
+    <tableColumn id="4" xr3:uid="{B563055E-F2FB-42BE-BA0E-E08593191708}" name="평균기온" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{EC02A3A1-631C-42EF-85AF-A8B79A8D9F9B}" name="취사용" dataDxfId="15"/>
+    <tableColumn id="5" xr3:uid="{86073F88-2F80-4462-BB87-5B8A54551B6A}" name="개별난방용" dataDxfId="14"/>
+    <tableColumn id="6" xr3:uid="{139EC257-82FA-481B-9F18-60ADA6EB50D3}" name="중앙난방용" dataDxfId="13"/>
+    <tableColumn id="19" xr3:uid="{408C0C4D-65A0-4DC3-A85C-EF1BC48BFA6F}" name="자가열전용" dataDxfId="12"/>
+    <tableColumn id="32" xr3:uid="{F08BABB7-87AA-4744-89E7-228FA9D35660}" name="영업용" dataDxfId="11"/>
+    <tableColumn id="9" xr3:uid="{D46D49CA-B262-4926-A5D1-6DDB23F119D4}" name="일반용(1)" dataDxfId="10"/>
+    <tableColumn id="12" xr3:uid="{861B7867-2B87-4609-A7B2-0963E4807DC3}" name="일반용(2)" dataDxfId="9"/>
+    <tableColumn id="13" xr3:uid="{14954B61-A6C3-4B22-BB69-82FCB6C6800D}" name="업무난방용" dataDxfId="8"/>
+    <tableColumn id="16" xr3:uid="{79636BBA-3A6E-42BA-959F-C2875D1EB9BF}" name="냉난방용" dataDxfId="7"/>
+    <tableColumn id="15" xr3:uid="{9E90082E-3CE5-4697-A0B1-A041913653D4}" name="산업용" dataDxfId="6"/>
+    <tableColumn id="22" xr3:uid="{15EC95E6-8587-482D-BF25-3DEDC8762C1E}" name="수송용(CNG)" dataDxfId="5"/>
+    <tableColumn id="21" xr3:uid="{0578ED32-2CDD-4E0D-B4BF-9D8549DC6AE8}" name="수송용(BIO)" dataDxfId="4"/>
+    <tableColumn id="17" xr3:uid="{A2C46C4C-5370-461A-AEAE-B18F07625F71}" name="열병합용" dataDxfId="3"/>
+    <tableColumn id="18" xr3:uid="{DF7D0596-2D46-4696-A139-30735FD75FF7}" name="연료전지용" dataDxfId="2"/>
+    <tableColumn id="20" xr3:uid="{BE9174ED-E86A-4C72-8087-5A38B6314769}" name="열전용설비용(주택외)" dataDxfId="1"/>
+    <tableColumn id="14" xr3:uid="{094C3E7A-F02F-42B7-A5BF-D2A7A7C7AD81}" name="주한미군" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight15" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10980,7 +11593,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{029D494F-C948-427C-AD81-22450CB874BD}">
-  <dimension ref="A1:AJ13"/>
+  <dimension ref="A1:AJ20"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.75" style="3" bestFit="1" customWidth="1"/>
@@ -10998,7 +11611,8 @@
     <col min="15" max="15" width="11.5" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12.875" bestFit="1" customWidth="1"/>
     <col min="17" max="18" width="10.5" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.5" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="15.625" bestFit="1" customWidth="1"/>
     <col min="21" max="21" width="12.875" bestFit="1" customWidth="1"/>
     <col min="22" max="22" width="13" bestFit="1" customWidth="1"/>
     <col min="23" max="25" width="12.875" bestFit="1" customWidth="1"/>
@@ -11135,11 +11749,9 @@
         <v>76533000</v>
       </c>
       <c r="I2" s="11">
-        <v>153579898</v>
-      </c>
-      <c r="J2" s="11">
-        <v>74281768</v>
-      </c>
+        <v>227861666</v>
+      </c>
+      <c r="J2" s="11"/>
       <c r="K2" s="11">
         <v>158987000</v>
       </c>
@@ -11207,11 +11819,9 @@
         <v>65741000</v>
       </c>
       <c r="I3" s="11">
-        <v>145568468</v>
-      </c>
-      <c r="J3" s="11">
-        <v>70552207</v>
-      </c>
+        <v>216120675</v>
+      </c>
+      <c r="J3" s="11"/>
       <c r="K3" s="11">
         <v>143546000</v>
       </c>
@@ -11279,11 +11889,9 @@
         <v>37262000</v>
       </c>
       <c r="I4" s="11">
-        <v>146489418</v>
-      </c>
-      <c r="J4" s="11">
-        <v>88277540</v>
-      </c>
+        <v>234766958</v>
+      </c>
+      <c r="J4" s="11"/>
       <c r="K4" s="11">
         <v>119576000</v>
       </c>
@@ -11351,11 +11959,9 @@
         <v>18286000</v>
       </c>
       <c r="I5" s="11">
-        <v>135781662</v>
-      </c>
-      <c r="J5" s="11">
-        <v>75542871</v>
-      </c>
+        <v>211324533</v>
+      </c>
+      <c r="J5" s="11"/>
       <c r="K5" s="11">
         <v>81746000</v>
       </c>
@@ -11423,11 +12029,9 @@
         <v>8496000</v>
       </c>
       <c r="I6" s="11">
-        <v>134964858</v>
-      </c>
-      <c r="J6" s="11">
-        <v>74733302</v>
-      </c>
+        <v>209698160</v>
+      </c>
+      <c r="J6" s="11"/>
       <c r="K6" s="11">
         <v>66933000</v>
       </c>
@@ -11495,11 +12099,9 @@
         <v>3490000</v>
       </c>
       <c r="I7" s="11">
-        <v>123353983</v>
-      </c>
-      <c r="J7" s="11">
-        <v>67271031</v>
-      </c>
+        <v>190625014</v>
+      </c>
+      <c r="J7" s="11"/>
       <c r="K7" s="11">
         <v>54037000</v>
       </c>
@@ -11567,11 +12169,9 @@
         <v>3299000</v>
       </c>
       <c r="I8" s="11">
-        <v>125563814</v>
-      </c>
-      <c r="J8" s="11">
-        <v>57468566</v>
-      </c>
+        <v>183032380</v>
+      </c>
+      <c r="J8" s="11"/>
       <c r="K8" s="11">
         <v>47949000</v>
       </c>
@@ -11639,11 +12239,9 @@
         <v>3562000</v>
       </c>
       <c r="I9" s="11">
-        <v>120278427</v>
-      </c>
-      <c r="J9" s="11">
-        <v>51363845</v>
-      </c>
+        <v>171642272</v>
+      </c>
+      <c r="J9" s="11"/>
       <c r="K9" s="11">
         <v>44815000</v>
       </c>
@@ -11711,11 +12309,9 @@
         <v>2164000</v>
       </c>
       <c r="I10" s="11">
-        <v>117034505</v>
-      </c>
-      <c r="J10" s="11">
-        <v>56649876</v>
-      </c>
+        <v>173684381</v>
+      </c>
+      <c r="J10" s="11"/>
       <c r="K10" s="11">
         <v>47011000</v>
       </c>
@@ -11783,11 +12379,9 @@
         <v>14574000</v>
       </c>
       <c r="I11" s="11">
-        <v>125903781</v>
-      </c>
-      <c r="J11" s="11">
-        <v>66826684</v>
-      </c>
+        <v>192730465</v>
+      </c>
+      <c r="J11" s="11"/>
       <c r="K11" s="11">
         <v>62915000</v>
       </c>
@@ -11855,11 +12449,9 @@
         <v>36432000</v>
       </c>
       <c r="I12" s="11">
-        <v>135379992</v>
-      </c>
-      <c r="J12" s="11">
-        <v>77567694</v>
-      </c>
+        <v>212947686</v>
+      </c>
+      <c r="J12" s="11"/>
       <c r="K12" s="11">
         <v>89008000</v>
       </c>
@@ -11927,11 +12519,9 @@
         <v>66717000</v>
       </c>
       <c r="I13" s="11">
-        <v>160740178</v>
-      </c>
-      <c r="J13" s="11">
-        <v>91641290</v>
-      </c>
+        <v>252381468</v>
+      </c>
+      <c r="J13" s="11"/>
       <c r="K13" s="11">
         <v>145682000</v>
       </c>
@@ -11974,6 +12564,9 @@
       <c r="AD13" s="14"/>
       <c r="AE13" s="14"/>
       <c r="AF13" s="14"/>
+    </row>
+    <row r="20" spans="20:20" x14ac:dyDescent="0.3">
+      <c r="T20" s="17"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/공급량실적_계획_실적_MJ.xlsx
+++ b/공급량실적_계획_실적_MJ.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Users\user\Desktop\0. 마케팅기획팀\2026\0. 스터디\2026\streamlit_study\실천사업계획\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DA7A3C6-8BA9-4FCD-B5CF-89BE48E4B0EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF5A1F6A-D475-4C24-8A39-3DE40C386A56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="공급량_실적" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="34">
   <si>
     <t>날짜</t>
   </si>
@@ -140,6 +140,10 @@
   </si>
   <si>
     <t>영업용</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>영업/업무용</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -2397,7 +2401,7 @@
     <tableColumn id="5" xr3:uid="{6EB58682-1AB0-402D-B1B5-64D7A3FEE7DC}" name="개별난방용" dataDxfId="102" totalsRowDxfId="101"/>
     <tableColumn id="6" xr3:uid="{9B5B2C66-64AC-4900-AA35-A909EB1F3ADB}" name="중앙난방용" dataDxfId="100" totalsRowDxfId="99"/>
     <tableColumn id="19" xr3:uid="{BB6DF2E3-2587-479E-A2F3-005ADFBAD580}" name="자가열전용" dataDxfId="98" totalsRowDxfId="97"/>
-    <tableColumn id="32" xr3:uid="{19247A41-B716-45A1-89D6-71493825C64A}" name="영업용" dataDxfId="96" totalsRowDxfId="95"/>
+    <tableColumn id="32" xr3:uid="{19247A41-B716-45A1-89D6-71493825C64A}" name="영업/업무용" dataDxfId="96" totalsRowDxfId="95"/>
     <tableColumn id="9" xr3:uid="{AE3DB5EB-C7E4-47AD-9093-9ED129869DB2}" name="일반용(1)" dataDxfId="94" totalsRowDxfId="93"/>
     <tableColumn id="12" xr3:uid="{8B4AF52F-6164-471B-AE99-CC06D0BB14EF}" name="일반용(2)" dataDxfId="92" totalsRowDxfId="91"/>
     <tableColumn id="13" xr3:uid="{371738D5-71AD-4443-9E50-C5CBFA38DD53}" name="업무난방용" dataDxfId="90" totalsRowDxfId="89"/>
@@ -2437,7 +2441,7 @@
     <tableColumn id="5" xr3:uid="{86073F88-2F80-4462-BB87-5B8A54551B6A}" name="개별난방용" dataDxfId="14"/>
     <tableColumn id="6" xr3:uid="{139EC257-82FA-481B-9F18-60ADA6EB50D3}" name="중앙난방용" dataDxfId="13"/>
     <tableColumn id="19" xr3:uid="{408C0C4D-65A0-4DC3-A85C-EF1BC48BFA6F}" name="자가열전용" dataDxfId="12"/>
-    <tableColumn id="32" xr3:uid="{F08BABB7-87AA-4744-89E7-228FA9D35660}" name="영업용" dataDxfId="11"/>
+    <tableColumn id="32" xr3:uid="{F08BABB7-87AA-4744-89E7-228FA9D35660}" name="영업/업무용" dataDxfId="11"/>
     <tableColumn id="9" xr3:uid="{D46D49CA-B262-4926-A5D1-6DDB23F119D4}" name="일반용(1)" dataDxfId="10"/>
     <tableColumn id="12" xr3:uid="{861B7867-2B87-4609-A7B2-0963E4807DC3}" name="일반용(2)" dataDxfId="9"/>
     <tableColumn id="13" xr3:uid="{14954B61-A6C3-4B22-BB69-82FCB6C6800D}" name="업무난방용" dataDxfId="8"/>
@@ -11593,7 +11597,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{029D494F-C948-427C-AD81-22450CB874BD}">
-  <dimension ref="A1:AJ20"/>
+  <dimension ref="A1:AJ27"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.75" style="3" bestFit="1" customWidth="1"/>
@@ -11652,7 +11656,7 @@
         <v>16</v>
       </c>
       <c r="I1" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J1" s="15" t="s">
         <v>22</v>
@@ -11749,18 +11753,12 @@
         <v>76533000</v>
       </c>
       <c r="I2" s="11">
-        <v>227861666</v>
+        <v>712474666</v>
       </c>
       <c r="J2" s="11"/>
-      <c r="K2" s="11">
-        <v>158987000</v>
-      </c>
-      <c r="L2" s="11">
-        <v>142347000</v>
-      </c>
-      <c r="M2" s="11">
-        <v>170895000</v>
-      </c>
+      <c r="K2" s="11"/>
+      <c r="L2" s="11"/>
+      <c r="M2" s="11"/>
       <c r="N2" s="11">
         <v>943307000</v>
       </c>
@@ -11779,9 +11777,7 @@
       <c r="S2" s="11">
         <v>802000</v>
       </c>
-      <c r="T2" s="11">
-        <v>12384000</v>
-      </c>
+      <c r="T2" s="11"/>
       <c r="U2" s="11"/>
       <c r="V2" s="11"/>
       <c r="W2" s="11"/>
@@ -11819,18 +11815,12 @@
         <v>65741000</v>
       </c>
       <c r="I3" s="11">
-        <v>216120675</v>
+        <v>638148675</v>
       </c>
       <c r="J3" s="11"/>
-      <c r="K3" s="11">
-        <v>143546000</v>
-      </c>
-      <c r="L3" s="11">
-        <v>122647000</v>
-      </c>
-      <c r="M3" s="11">
-        <v>145668000</v>
-      </c>
+      <c r="K3" s="11"/>
+      <c r="L3" s="11"/>
+      <c r="M3" s="11"/>
       <c r="N3" s="11">
         <v>727930000</v>
       </c>
@@ -11849,9 +11839,7 @@
       <c r="S3" s="11">
         <v>774000</v>
       </c>
-      <c r="T3" s="11">
-        <v>10167000</v>
-      </c>
+      <c r="T3" s="11"/>
       <c r="U3" s="11"/>
       <c r="V3" s="11"/>
       <c r="W3" s="11"/>
@@ -11889,18 +11877,12 @@
         <v>37262000</v>
       </c>
       <c r="I4" s="11">
-        <v>234766958</v>
+        <v>539678958</v>
       </c>
       <c r="J4" s="11"/>
-      <c r="K4" s="11">
-        <v>119576000</v>
-      </c>
-      <c r="L4" s="11">
-        <v>89804000</v>
-      </c>
-      <c r="M4" s="11">
-        <v>88597000</v>
-      </c>
+      <c r="K4" s="11"/>
+      <c r="L4" s="11"/>
+      <c r="M4" s="11"/>
       <c r="N4" s="11">
         <v>812951000</v>
       </c>
@@ -11919,9 +11901,7 @@
       <c r="S4" s="11">
         <v>639000</v>
       </c>
-      <c r="T4" s="11">
-        <v>6935000</v>
-      </c>
+      <c r="T4" s="11"/>
       <c r="U4" s="11"/>
       <c r="V4" s="11"/>
       <c r="W4" s="11"/>
@@ -11959,18 +11939,12 @@
         <v>18286000</v>
       </c>
       <c r="I5" s="11">
-        <v>211324533</v>
+        <v>374824533</v>
       </c>
       <c r="J5" s="11"/>
-      <c r="K5" s="11">
-        <v>81746000</v>
-      </c>
-      <c r="L5" s="11">
-        <v>42955000</v>
-      </c>
-      <c r="M5" s="11">
-        <v>36248000</v>
-      </c>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
       <c r="N5" s="11">
         <v>771432000</v>
       </c>
@@ -11989,9 +11963,7 @@
       <c r="S5" s="11">
         <v>595000</v>
       </c>
-      <c r="T5" s="11">
-        <v>2551000</v>
-      </c>
+      <c r="T5" s="11"/>
       <c r="U5" s="11"/>
       <c r="V5" s="11"/>
       <c r="W5" s="11"/>
@@ -12029,18 +12001,12 @@
         <v>8496000</v>
       </c>
       <c r="I6" s="11">
-        <v>209698160</v>
+        <v>368652160</v>
       </c>
       <c r="J6" s="11"/>
-      <c r="K6" s="11">
-        <v>66933000</v>
-      </c>
-      <c r="L6" s="11">
-        <v>27605000</v>
-      </c>
-      <c r="M6" s="11">
-        <v>62208000</v>
-      </c>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
       <c r="N6" s="11">
         <v>657574000</v>
       </c>
@@ -12059,9 +12025,7 @@
       <c r="S6" s="11">
         <v>369000</v>
       </c>
-      <c r="T6" s="11">
-        <v>2208000</v>
-      </c>
+      <c r="T6" s="11"/>
       <c r="U6" s="11"/>
       <c r="V6" s="11"/>
       <c r="W6" s="11"/>
@@ -12099,18 +12063,12 @@
         <v>3490000</v>
       </c>
       <c r="I7" s="11">
-        <v>190625014</v>
+        <v>401930014</v>
       </c>
       <c r="J7" s="11"/>
-      <c r="K7" s="11">
-        <v>54037000</v>
-      </c>
-      <c r="L7" s="11">
-        <v>20400000</v>
-      </c>
-      <c r="M7" s="11">
-        <v>135017000</v>
-      </c>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
       <c r="N7" s="11">
         <v>750349000</v>
       </c>
@@ -12129,9 +12087,7 @@
       <c r="S7" s="11">
         <v>363000</v>
       </c>
-      <c r="T7" s="11">
-        <v>1851000</v>
-      </c>
+      <c r="T7" s="11"/>
       <c r="U7" s="11"/>
       <c r="V7" s="11"/>
       <c r="W7" s="11"/>
@@ -12169,18 +12125,12 @@
         <v>3299000</v>
       </c>
       <c r="I8" s="11">
-        <v>183032380</v>
+        <v>449762380</v>
       </c>
       <c r="J8" s="11"/>
-      <c r="K8" s="11">
-        <v>47949000</v>
-      </c>
-      <c r="L8" s="11">
-        <v>18512000</v>
-      </c>
-      <c r="M8" s="11">
-        <v>198630000</v>
-      </c>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
       <c r="N8" s="11">
         <v>657768000</v>
       </c>
@@ -12199,9 +12149,7 @@
       <c r="S8" s="11">
         <v>690000</v>
       </c>
-      <c r="T8" s="11">
-        <v>1639000</v>
-      </c>
+      <c r="T8" s="11"/>
       <c r="U8" s="11"/>
       <c r="V8" s="11"/>
       <c r="W8" s="11"/>
@@ -12239,18 +12187,12 @@
         <v>3562000</v>
       </c>
       <c r="I9" s="11">
-        <v>171642272</v>
+        <v>434761272</v>
       </c>
       <c r="J9" s="11"/>
-      <c r="K9" s="11">
-        <v>44815000</v>
-      </c>
-      <c r="L9" s="11">
-        <v>17022000</v>
-      </c>
-      <c r="M9" s="11">
-        <v>199772000</v>
-      </c>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
       <c r="N9" s="11">
         <v>631899000</v>
       </c>
@@ -12269,9 +12211,7 @@
       <c r="S9" s="11">
         <v>669000</v>
       </c>
-      <c r="T9" s="11">
-        <v>1510000</v>
-      </c>
+      <c r="T9" s="11"/>
       <c r="U9" s="11"/>
       <c r="V9" s="11"/>
       <c r="W9" s="11"/>
@@ -12309,18 +12249,12 @@
         <v>2164000</v>
       </c>
       <c r="I10" s="11">
-        <v>173684381</v>
+        <v>374065381</v>
       </c>
       <c r="J10" s="11"/>
-      <c r="K10" s="11">
-        <v>47011000</v>
-      </c>
-      <c r="L10" s="11">
-        <v>17253000</v>
-      </c>
-      <c r="M10" s="11">
-        <v>134696000</v>
-      </c>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
       <c r="N10" s="11">
         <v>631497000</v>
       </c>
@@ -12339,9 +12273,7 @@
       <c r="S10" s="11">
         <v>673000</v>
       </c>
-      <c r="T10" s="11">
-        <v>1421000</v>
-      </c>
+      <c r="T10" s="11"/>
       <c r="U10" s="11"/>
       <c r="V10" s="11"/>
       <c r="W10" s="11"/>
@@ -12379,18 +12311,12 @@
         <v>14574000</v>
       </c>
       <c r="I11" s="11">
-        <v>192730465</v>
+        <v>338182465</v>
       </c>
       <c r="J11" s="11"/>
-      <c r="K11" s="11">
-        <v>62915000</v>
-      </c>
-      <c r="L11" s="11">
-        <v>26049000</v>
-      </c>
-      <c r="M11" s="11">
-        <v>54208000</v>
-      </c>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
       <c r="N11" s="11">
         <v>721544000</v>
       </c>
@@ -12409,9 +12335,7 @@
       <c r="S11" s="11">
         <v>507000</v>
       </c>
-      <c r="T11" s="11">
-        <v>2280000</v>
-      </c>
+      <c r="T11" s="11"/>
       <c r="U11" s="11"/>
       <c r="V11" s="11"/>
       <c r="W11" s="11"/>
@@ -12449,18 +12373,12 @@
         <v>36432000</v>
       </c>
       <c r="I12" s="11">
-        <v>212947686</v>
+        <v>430524686</v>
       </c>
       <c r="J12" s="11"/>
-      <c r="K12" s="11">
-        <v>89008000</v>
-      </c>
-      <c r="L12" s="11">
-        <v>59355000</v>
-      </c>
-      <c r="M12" s="11">
-        <v>64107000</v>
-      </c>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
       <c r="N12" s="11">
         <v>743804000</v>
       </c>
@@ -12479,9 +12397,7 @@
       <c r="S12" s="11">
         <v>419000</v>
       </c>
-      <c r="T12" s="11">
-        <v>5107000</v>
-      </c>
+      <c r="T12" s="11"/>
       <c r="U12" s="11"/>
       <c r="V12" s="11"/>
       <c r="W12" s="11"/>
@@ -12519,18 +12435,12 @@
         <v>66717000</v>
       </c>
       <c r="I13" s="11">
-        <v>252381468</v>
+        <v>675355468</v>
       </c>
       <c r="J13" s="11"/>
-      <c r="K13" s="11">
-        <v>145682000</v>
-      </c>
-      <c r="L13" s="11">
-        <v>125570000</v>
-      </c>
-      <c r="M13" s="11">
-        <v>141704000</v>
-      </c>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
       <c r="N13" s="11">
         <v>826500000</v>
       </c>
@@ -12549,9 +12459,7 @@
       <c r="S13" s="11">
         <v>659000</v>
       </c>
-      <c r="T13" s="11">
-        <v>10018000</v>
-      </c>
+      <c r="T13" s="11"/>
       <c r="U13" s="11"/>
       <c r="V13" s="11"/>
       <c r="W13" s="11"/>
@@ -12565,8 +12473,78 @@
       <c r="AE13" s="14"/>
       <c r="AF13" s="14"/>
     </row>
-    <row r="20" spans="20:20" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.3">
+      <c r="I16">
+        <f>SUM(I2:M2,T2)</f>
+        <v>712474666</v>
+      </c>
+    </row>
+    <row r="17" spans="9:20" x14ac:dyDescent="0.3">
+      <c r="I17">
+        <f t="shared" ref="I17:I27" si="0">SUM(I3:M3,T3)</f>
+        <v>638148675</v>
+      </c>
+    </row>
+    <row r="18" spans="9:20" x14ac:dyDescent="0.3">
+      <c r="I18">
+        <f t="shared" si="0"/>
+        <v>539678958</v>
+      </c>
+    </row>
+    <row r="19" spans="9:20" x14ac:dyDescent="0.3">
+      <c r="I19">
+        <f t="shared" si="0"/>
+        <v>374824533</v>
+      </c>
+    </row>
+    <row r="20" spans="9:20" x14ac:dyDescent="0.3">
+      <c r="I20">
+        <f t="shared" si="0"/>
+        <v>368652160</v>
+      </c>
       <c r="T20" s="17"/>
+    </row>
+    <row r="21" spans="9:20" x14ac:dyDescent="0.3">
+      <c r="I21">
+        <f t="shared" si="0"/>
+        <v>401930014</v>
+      </c>
+    </row>
+    <row r="22" spans="9:20" x14ac:dyDescent="0.3">
+      <c r="I22">
+        <f t="shared" si="0"/>
+        <v>449762380</v>
+      </c>
+    </row>
+    <row r="23" spans="9:20" x14ac:dyDescent="0.3">
+      <c r="I23">
+        <f t="shared" si="0"/>
+        <v>434761272</v>
+      </c>
+    </row>
+    <row r="24" spans="9:20" x14ac:dyDescent="0.3">
+      <c r="I24">
+        <f t="shared" si="0"/>
+        <v>374065381</v>
+      </c>
+    </row>
+    <row r="25" spans="9:20" x14ac:dyDescent="0.3">
+      <c r="I25">
+        <f t="shared" si="0"/>
+        <v>338182465</v>
+      </c>
+    </row>
+    <row r="26" spans="9:20" x14ac:dyDescent="0.3">
+      <c r="I26">
+        <f t="shared" si="0"/>
+        <v>430524686</v>
+      </c>
+    </row>
+    <row r="27" spans="9:20" x14ac:dyDescent="0.3">
+      <c r="I27">
+        <f t="shared" si="0"/>
+        <v>675355468</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -12630,7 +12608,7 @@
         <v>16</v>
       </c>
       <c r="I1" s="12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="J1" s="15" t="s">
         <v>22</v>
@@ -12691,18 +12669,12 @@
         <v>77757917</v>
       </c>
       <c r="I2" s="16">
-        <v>240524224</v>
+        <v>752789222</v>
       </c>
       <c r="J2" s="16"/>
-      <c r="K2" s="16">
-        <v>164563755</v>
-      </c>
-      <c r="L2" s="16">
-        <v>154915949</v>
-      </c>
-      <c r="M2" s="16">
-        <v>181364249</v>
-      </c>
+      <c r="K2" s="16"/>
+      <c r="L2" s="16"/>
+      <c r="M2" s="16"/>
       <c r="N2" s="16">
         <v>922530985</v>
       </c>
@@ -12721,9 +12693,7 @@
       <c r="S2" s="16">
         <v>1180658</v>
       </c>
-      <c r="T2" s="16">
-        <v>11421045</v>
-      </c>
+      <c r="T2" s="16"/>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
@@ -12749,18 +12719,12 @@
         <v>56988098</v>
       </c>
       <c r="I3" s="16">
-        <v>205449586</v>
+        <v>595105027</v>
       </c>
       <c r="J3" s="16"/>
-      <c r="K3" s="16">
-        <v>133527806</v>
-      </c>
-      <c r="L3" s="16">
-        <v>115810392</v>
-      </c>
-      <c r="M3" s="16">
-        <v>131009593</v>
-      </c>
+      <c r="K3" s="16"/>
+      <c r="L3" s="16"/>
+      <c r="M3" s="16"/>
       <c r="N3" s="16">
         <v>732838698</v>
       </c>
@@ -12779,9 +12743,7 @@
       <c r="S3" s="16">
         <v>1025235</v>
       </c>
-      <c r="T3" s="16">
-        <v>9307650</v>
-      </c>
+      <c r="T3" s="16"/>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4" s="10">
@@ -12807,18 +12769,12 @@
         <v>39997670</v>
       </c>
       <c r="I4" s="16">
-        <v>236969927</v>
+        <v>527861908</v>
       </c>
       <c r="J4" s="16"/>
-      <c r="K4" s="16">
-        <v>118157095</v>
-      </c>
-      <c r="L4" s="16">
-        <v>86736495</v>
-      </c>
-      <c r="M4" s="16">
-        <v>78432678</v>
-      </c>
+      <c r="K4" s="16"/>
+      <c r="L4" s="16"/>
+      <c r="M4" s="16"/>
       <c r="N4" s="16">
         <v>824414065</v>
       </c>
@@ -12837,9 +12793,7 @@
       <c r="S4" s="16">
         <v>776191</v>
       </c>
-      <c r="T4" s="16">
-        <v>7565713</v>
-      </c>
+      <c r="T4" s="16"/>
     </row>
     <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5" s="10">
@@ -12865,18 +12819,12 @@
         <v>16338705</v>
       </c>
       <c r="I5" s="11">
-        <v>210530636</v>
+        <v>366903196</v>
       </c>
       <c r="J5" s="11"/>
-      <c r="K5" s="11">
-        <v>79667647</v>
-      </c>
-      <c r="L5" s="11">
-        <v>40917600</v>
-      </c>
-      <c r="M5" s="11">
-        <v>32668164</v>
-      </c>
+      <c r="K5" s="11"/>
+      <c r="L5" s="11"/>
+      <c r="M5" s="11"/>
       <c r="N5" s="11">
         <v>762126521</v>
       </c>
@@ -12895,9 +12843,7 @@
       <c r="S5" s="11">
         <v>679333</v>
       </c>
-      <c r="T5" s="11">
-        <v>3119149</v>
-      </c>
+      <c r="T5" s="11"/>
     </row>
     <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
@@ -12923,18 +12869,12 @@
         <v>8274790</v>
       </c>
       <c r="I6" s="11">
-        <v>201802358</v>
+        <v>362655651</v>
       </c>
       <c r="J6" s="11"/>
-      <c r="K6" s="11">
-        <v>65164715</v>
-      </c>
-      <c r="L6" s="11">
-        <v>25533895</v>
-      </c>
-      <c r="M6" s="11">
-        <v>67881591</v>
-      </c>
+      <c r="K6" s="11"/>
+      <c r="L6" s="11"/>
+      <c r="M6" s="11"/>
       <c r="N6" s="11">
         <v>727133107</v>
       </c>
@@ -12953,9 +12893,7 @@
       <c r="S6" s="11">
         <v>574895</v>
       </c>
-      <c r="T6" s="11">
-        <v>2273092</v>
-      </c>
+      <c r="T6" s="11"/>
     </row>
     <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7" s="10">
@@ -12981,18 +12919,12 @@
         <v>3489735</v>
       </c>
       <c r="I7" s="11">
-        <v>189828300</v>
+        <v>400881914</v>
       </c>
       <c r="J7" s="11"/>
-      <c r="K7" s="11">
-        <v>53185938</v>
-      </c>
-      <c r="L7" s="11">
-        <v>20431913</v>
-      </c>
-      <c r="M7" s="11">
-        <v>135471653</v>
-      </c>
+      <c r="K7" s="11"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="11"/>
       <c r="N7" s="11">
         <v>641653473</v>
       </c>
@@ -13011,9 +12943,7 @@
       <c r="S7" s="11">
         <v>363305</v>
       </c>
-      <c r="T7" s="11">
-        <v>1964110</v>
-      </c>
+      <c r="T7" s="11"/>
     </row>
     <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8" s="10">
@@ -13039,18 +12969,12 @@
         <v>3298632</v>
       </c>
       <c r="I8" s="11">
-        <v>183365593</v>
+        <v>449136253</v>
       </c>
       <c r="J8" s="11"/>
-      <c r="K8" s="11">
-        <v>47193612</v>
-      </c>
-      <c r="L8" s="11">
-        <v>18448952</v>
-      </c>
-      <c r="M8" s="11">
-        <v>198504839</v>
-      </c>
+      <c r="K8" s="11"/>
+      <c r="L8" s="11"/>
+      <c r="M8" s="11"/>
       <c r="N8" s="11">
         <v>657628999</v>
       </c>
@@ -13069,9 +12993,7 @@
       <c r="S8" s="11">
         <v>690534</v>
       </c>
-      <c r="T8" s="11">
-        <v>1623257</v>
-      </c>
+      <c r="T8" s="11"/>
     </row>
     <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9" s="10">
@@ -13097,18 +13019,12 @@
         <v>3561524</v>
       </c>
       <c r="I9" s="11">
-        <v>171954749</v>
+        <v>434169999</v>
       </c>
       <c r="J9" s="11"/>
-      <c r="K9" s="11">
-        <v>44109109</v>
-      </c>
-      <c r="L9" s="11">
-        <v>16964203</v>
-      </c>
-      <c r="M9" s="11">
-        <v>199646393</v>
-      </c>
+      <c r="K9" s="11"/>
+      <c r="L9" s="11"/>
+      <c r="M9" s="11"/>
       <c r="N9" s="11">
         <v>631765337</v>
       </c>
@@ -13127,9 +13043,7 @@
       <c r="S9" s="11">
         <v>670057</v>
       </c>
-      <c r="T9" s="11">
-        <v>1495545</v>
-      </c>
+      <c r="T9" s="11"/>
     </row>
     <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
@@ -13155,18 +13069,12 @@
         <v>2163629</v>
       </c>
       <c r="I10" s="11">
-        <v>174000576</v>
+        <v>373483150</v>
       </c>
       <c r="J10" s="11"/>
-      <c r="K10" s="11">
-        <v>46270291</v>
-      </c>
-      <c r="L10" s="11">
-        <v>17193529</v>
-      </c>
-      <c r="M10" s="11">
-        <v>134611015</v>
-      </c>
+      <c r="K10" s="11"/>
+      <c r="L10" s="11"/>
+      <c r="M10" s="11"/>
       <c r="N10" s="11">
         <v>631363795</v>
       </c>
@@ -13185,9 +13093,7 @@
       <c r="S10" s="11">
         <v>673599</v>
       </c>
-      <c r="T10" s="11">
-        <v>1407739</v>
-      </c>
+      <c r="T10" s="11"/>
     </row>
     <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11" s="10">
@@ -13213,18 +13119,12 @@
         <v>14574059</v>
       </c>
       <c r="I11" s="11">
-        <v>193081334</v>
+        <v>337398392</v>
       </c>
       <c r="J11" s="11"/>
-      <c r="K11" s="11">
-        <v>61923837</v>
-      </c>
-      <c r="L11" s="11">
-        <v>25960144</v>
-      </c>
-      <c r="M11" s="11">
-        <v>54174288</v>
-      </c>
+      <c r="K11" s="11"/>
+      <c r="L11" s="11"/>
+      <c r="M11" s="11"/>
       <c r="N11" s="11">
         <v>721391799</v>
       </c>
@@ -13243,9 +13143,7 @@
       <c r="S11" s="11">
         <v>507273</v>
       </c>
-      <c r="T11" s="11">
-        <v>2258789</v>
-      </c>
+      <c r="T11" s="11"/>
     </row>
     <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12" s="10">
@@ -13271,18 +13169,12 @@
         <v>36431964</v>
       </c>
       <c r="I12" s="11">
-        <v>213335361</v>
+        <v>429218209</v>
       </c>
       <c r="J12" s="11"/>
-      <c r="K12" s="11">
-        <v>87606082</v>
-      </c>
-      <c r="L12" s="11">
-        <v>59151326</v>
-      </c>
-      <c r="M12" s="11">
-        <v>64066546</v>
-      </c>
+      <c r="K12" s="11"/>
+      <c r="L12" s="11"/>
+      <c r="M12" s="11"/>
       <c r="N12" s="11">
         <v>743647221</v>
       </c>
@@ -13301,9 +13193,7 @@
       <c r="S12" s="11">
         <v>419460</v>
       </c>
-      <c r="T12" s="11">
-        <v>5058894</v>
-      </c>
+      <c r="T12" s="11"/>
     </row>
     <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
@@ -13329,18 +13219,12 @@
         <v>66717098</v>
       </c>
       <c r="I13" s="11">
-        <v>252840932</v>
+        <v>672906895</v>
       </c>
       <c r="J13" s="11"/>
-      <c r="K13" s="11">
-        <v>143386961</v>
-      </c>
-      <c r="L13" s="11">
-        <v>125139856</v>
-      </c>
-      <c r="M13" s="11">
-        <v>141615279</v>
-      </c>
+      <c r="K13" s="11"/>
+      <c r="L13" s="11"/>
+      <c r="M13" s="11"/>
       <c r="N13" s="11">
         <v>826325218</v>
       </c>
@@ -13359,9 +13243,7 @@
       <c r="S13" s="11">
         <v>659786</v>
       </c>
-      <c r="T13" s="11">
-        <v>9923867</v>
-      </c>
+      <c r="T13" s="11"/>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
